--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Generali" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="KOMUNÁLNA poisťovňa" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Kooperativa (Bezstarostný domov" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Union" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Wüstenrot (W dobrom domov)" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="ČSOB Poisťovňa" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="UNIQA" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Union" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Wüstenrot (W dobrom domov)" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="ČSOB Poisťovňa" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="35">
   <si>
     <t xml:space="preserve">Allianz</t>
   </si>
@@ -93,6 +94,15 @@
   </si>
   <si>
     <t xml:space="preserve">Prima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLUS</t>
   </si>
   <si>
     <t xml:space="preserve">Union</t>
@@ -630,11 +640,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77064450"/>
-        <c:axId val="42146435"/>
+        <c:axId val="29901183"/>
+        <c:axId val="32847137"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77064450"/>
+        <c:axId val="29901183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -700,7 +710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42146435"/>
+        <c:crossAx val="32847137"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -708,7 +718,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42146435"/>
+        <c:axId val="32847137"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -784,7 +794,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77064450"/>
+        <c:crossAx val="29901183"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -885,7 +895,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B26</c:f>
+              <c:f>Generali!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -935,22 +945,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$27</c:f>
+              <c:f>Generali!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$27</c:f>
+              <c:f>Generali!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>77.55</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>77.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -963,7 +979,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C26</c:f>
+              <c:f>Generali!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1013,22 +1029,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$27</c:f>
+              <c:f>Generali!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$27</c:f>
+              <c:f>Generali!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>92.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -1041,7 +1063,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D26</c:f>
+              <c:f>Generali!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1091,22 +1113,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$27</c:f>
+              <c:f>Generali!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$27</c:f>
+              <c:f>Generali!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>73.19</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>73.19</c:v>
                 </c:pt>
               </c:numCache>
@@ -1122,11 +1150,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="17614710"/>
-        <c:axId val="2536544"/>
+        <c:axId val="13081840"/>
+        <c:axId val="33486115"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="17614710"/>
+        <c:axId val="13081840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1192,7 +1220,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2536544"/>
+        <c:crossAx val="33486115"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1200,7 +1228,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2536544"/>
+        <c:axId val="33486115"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1276,7 +1304,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17614710"/>
+        <c:crossAx val="13081840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1377,7 +1405,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B48</c:f>
+              <c:f>Generali!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1427,22 +1455,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$49</c:f>
+              <c:f>Generali!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$49</c:f>
+              <c:f>Generali!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>152.27</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>152.27</c:v>
                 </c:pt>
               </c:numCache>
@@ -1455,7 +1489,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C48</c:f>
+              <c:f>Generali!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1505,22 +1539,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$49</c:f>
+              <c:f>Generali!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$49</c:f>
+              <c:f>Generali!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>163.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>163.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1533,7 +1573,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D48</c:f>
+              <c:f>Generali!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1583,22 +1623,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$49</c:f>
+              <c:f>Generali!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$49</c:f>
+              <c:f>Generali!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>147.57</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>147.57</c:v>
                 </c:pt>
               </c:numCache>
@@ -1614,11 +1660,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4646463"/>
-        <c:axId val="32715799"/>
+        <c:axId val="61152449"/>
+        <c:axId val="12324515"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4646463"/>
+        <c:axId val="61152449"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1684,7 +1730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32715799"/>
+        <c:crossAx val="12324515"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1692,7 +1738,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32715799"/>
+        <c:axId val="12324515"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1768,7 +1814,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4646463"/>
+        <c:crossAx val="61152449"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1869,7 +1915,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B70</c:f>
+              <c:f>Generali!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1919,22 +1965,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$71</c:f>
+              <c:f>Generali!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$71</c:f>
+              <c:f>Generali!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>199.86</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>199.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -1947,7 +1999,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C70</c:f>
+              <c:f>Generali!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1997,22 +2049,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$71</c:f>
+              <c:f>Generali!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$71</c:f>
+              <c:f>Generali!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>211.29</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>211.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -2025,7 +2083,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D70</c:f>
+              <c:f>Generali!D73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2075,22 +2133,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$71</c:f>
+              <c:f>Generali!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$71</c:f>
+              <c:f>Generali!$D$74:$D$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>195.16</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>195.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -2106,11 +2170,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="11179216"/>
-        <c:axId val="30448941"/>
+        <c:axId val="51569093"/>
+        <c:axId val="43901180"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11179216"/>
+        <c:axId val="51569093"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2176,7 +2240,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30448941"/>
+        <c:crossAx val="43901180"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2184,7 +2248,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30448941"/>
+        <c:axId val="43901180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2260,7 +2324,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11179216"/>
+        <c:crossAx val="51569093"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2411,22 +2475,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>121.09</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>121.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -2489,22 +2559,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>98.77</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>98.77</c:v>
                 </c:pt>
               </c:numCache>
@@ -2567,22 +2643,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$5</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>86.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>86.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2598,11 +2680,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18457041"/>
-        <c:axId val="42544534"/>
+        <c:axId val="84607786"/>
+        <c:axId val="5930653"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18457041"/>
+        <c:axId val="84607786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2668,7 +2750,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42544534"/>
+        <c:crossAx val="5930653"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2676,7 +2758,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42544534"/>
+        <c:axId val="5930653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,7 +2834,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18457041"/>
+        <c:crossAx val="84607786"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2853,7 +2935,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B26</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2903,22 +2985,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>95.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -2931,7 +3019,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C26</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2981,22 +3069,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>79.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>79.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3009,7 +3103,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D26</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3059,22 +3153,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>69.52</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>69.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -3090,11 +3190,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="89162227"/>
-        <c:axId val="19246097"/>
+        <c:axId val="99048534"/>
+        <c:axId val="45542239"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="89162227"/>
+        <c:axId val="99048534"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3160,7 +3260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19246097"/>
+        <c:crossAx val="45542239"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3168,7 +3268,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19246097"/>
+        <c:axId val="45542239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3244,7 +3344,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89162227"/>
+        <c:crossAx val="99048534"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3345,7 +3445,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B48</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3395,22 +3495,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>145.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>145.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -3423,7 +3529,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C48</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3473,22 +3579,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>115.11</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>115.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -3501,7 +3613,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D48</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3551,22 +3663,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$49</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>92.59</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>92.59</c:v>
                 </c:pt>
               </c:numCache>
@@ -3582,11 +3700,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="15855578"/>
-        <c:axId val="47938892"/>
+        <c:axId val="16140624"/>
+        <c:axId val="17033608"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="15855578"/>
+        <c:axId val="16140624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3652,7 +3770,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47938892"/>
+        <c:crossAx val="17033608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3660,7 +3778,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47938892"/>
+        <c:axId val="17033608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3736,7 +3854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15855578"/>
+        <c:crossAx val="16140624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3837,7 +3955,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B70</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3887,22 +4005,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>213.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -3915,7 +4039,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C70</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3965,22 +4089,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>165.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>165.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -3993,7 +4123,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D70</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4043,22 +4173,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$71</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$74:$D$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>132.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4074,11 +4210,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90934417"/>
-        <c:axId val="88200106"/>
+        <c:axId val="6399888"/>
+        <c:axId val="11753463"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90934417"/>
+        <c:axId val="6399888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4144,7 +4280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88200106"/>
+        <c:crossAx val="11753463"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4152,7 +4288,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88200106"/>
+        <c:axId val="11753463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4228,7 +4364,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90934417"/>
+        <c:crossAx val="6399888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4379,22 +4515,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>138.66</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>138.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -4457,22 +4599,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>108.81</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>108.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -4535,22 +4683,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$5</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>93.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -4566,11 +4720,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10471287"/>
-        <c:axId val="49943121"/>
+        <c:axId val="59093658"/>
+        <c:axId val="72516643"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10471287"/>
+        <c:axId val="59093658"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4636,7 +4790,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49943121"/>
+        <c:crossAx val="72516643"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4644,7 +4798,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49943121"/>
+        <c:axId val="72516643"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4720,7 +4874,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10471287"/>
+        <c:crossAx val="59093658"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4821,7 +4975,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B26</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4871,22 +5025,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>106.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -4899,7 +5059,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C26</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4949,22 +5109,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>84.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>84.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -4977,7 +5143,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D26</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5027,22 +5193,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>73.49</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>73.49</c:v>
                 </c:pt>
               </c:numCache>
@@ -5058,11 +5230,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="38108456"/>
-        <c:axId val="92407486"/>
+        <c:axId val="7170341"/>
+        <c:axId val="97738631"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38108456"/>
+        <c:axId val="7170341"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5128,7 +5300,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92407486"/>
+        <c:crossAx val="97738631"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5136,7 +5308,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92407486"/>
+        <c:axId val="97738631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5212,7 +5384,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38108456"/>
+        <c:crossAx val="7170341"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5313,7 +5485,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B48</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5363,22 +5535,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>167.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>167.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -5391,7 +5569,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C48</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5441,22 +5619,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>128.08</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>128.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -5469,7 +5653,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D48</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5519,22 +5703,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$49</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>109.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>109.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -5550,11 +5740,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="95816017"/>
-        <c:axId val="72081408"/>
+        <c:axId val="78835011"/>
+        <c:axId val="34433826"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="95816017"/>
+        <c:axId val="78835011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5620,7 +5810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72081408"/>
+        <c:crossAx val="34433826"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5628,7 +5818,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72081408"/>
+        <c:axId val="34433826"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5704,7 +5894,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95816017"/>
+        <c:crossAx val="78835011"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6042,11 +6232,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7699370"/>
-        <c:axId val="7552744"/>
+        <c:axId val="71951031"/>
+        <c:axId val="35348413"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7699370"/>
+        <c:axId val="71951031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6112,7 +6302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7552744"/>
+        <c:crossAx val="35348413"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6120,7 +6310,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7552744"/>
+        <c:axId val="35348413"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6196,7 +6386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7699370"/>
+        <c:crossAx val="71951031"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6297,7 +6487,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B70</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6347,22 +6537,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>233.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>233.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6375,7 +6571,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C70</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6425,22 +6621,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>177.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>177.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6453,7 +6655,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D70</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6503,22 +6705,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$71</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$74:$D$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>148.98</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>148.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -6534,11 +6742,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="80695702"/>
-        <c:axId val="50838910"/>
+        <c:axId val="66202411"/>
+        <c:axId val="85851099"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="80695702"/>
+        <c:axId val="66202411"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6604,7 +6812,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50838910"/>
+        <c:crossAx val="85851099"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6612,7 +6820,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50838910"/>
+        <c:axId val="85851099"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6688,7 +6896,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80695702"/>
+        <c:crossAx val="66202411"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6789,11 +6997,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B4</c:f>
+              <c:f>UNIQA!B4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komplet (všetky pripoistenia)</c:v>
+                  <c:v>EXTRA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6839,23 +7047,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5</c:f>
+              <c:f>UNIQA!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$5</c:f>
+              <c:f>UNIQA!$B$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>151.45</c:v>
+                  <c:v>207.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6867,11 +7075,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C4</c:f>
+              <c:f>UNIQA!C4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Základné riziká</c:v>
+                  <c:v>PLUS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6917,23 +7125,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5</c:f>
+              <c:f>UNIQA!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$5</c:f>
+              <c:f>UNIQA!$C$5</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>49.98</c:v>
+                  <c:v>174.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6948,11 +7156,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="46221559"/>
-        <c:axId val="43107363"/>
+        <c:axId val="18670966"/>
+        <c:axId val="12727401"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="46221559"/>
+        <c:axId val="18670966"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7018,7 +7226,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43107363"/>
+        <c:crossAx val="12727401"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7026,7 +7234,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43107363"/>
+        <c:axId val="12727401"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7102,7 +7310,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46221559"/>
+        <c:crossAx val="18670966"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7203,11 +7411,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B26</c:f>
+              <c:f>UNIQA!B26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komplet (všetky pripoistenia)</c:v>
+                  <c:v>EXTRA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7253,23 +7461,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$27</c:f>
+              <c:f>UNIQA!$A$27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$27</c:f>
+              <c:f>UNIQA!$B$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>120.23</c:v>
+                  <c:v>164.09</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7281,11 +7489,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C26</c:f>
+              <c:f>UNIQA!C26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Základné riziká</c:v>
+                  <c:v>PLUS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7331,23 +7539,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$27</c:f>
+              <c:f>UNIQA!$A$27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$27</c:f>
+              <c:f>UNIQA!$C$27</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>39.68</c:v>
+                  <c:v>139.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7362,11 +7570,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="51470224"/>
-        <c:axId val="97665962"/>
+        <c:axId val="60850194"/>
+        <c:axId val="99499875"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="51470224"/>
+        <c:axId val="60850194"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7432,7 +7640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97665962"/>
+        <c:crossAx val="99499875"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7440,7 +7648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97665962"/>
+        <c:axId val="99499875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7516,7 +7724,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51470224"/>
+        <c:crossAx val="60850194"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7617,11 +7825,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B48</c:f>
+              <c:f>UNIQA!B48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komplet (všetky pripoistenia)</c:v>
+                  <c:v>EXTRA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7667,23 +7875,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$49</c:f>
+              <c:f>UNIQA!$A$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$49</c:f>
+              <c:f>UNIQA!$B$49</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>206.12</c:v>
+                  <c:v>234.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7695,11 +7903,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C48</c:f>
+              <c:f>UNIQA!C48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Základné riziká</c:v>
+                  <c:v>PLUS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7745,23 +7953,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$49</c:f>
+              <c:f>UNIQA!$A$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$49</c:f>
+              <c:f>UNIQA!$C$49</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>68.04</c:v>
+                  <c:v>183.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7776,11 +7984,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="63959632"/>
-        <c:axId val="65364068"/>
+        <c:axId val="55330828"/>
+        <c:axId val="88268298"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63959632"/>
+        <c:axId val="55330828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7846,7 +8054,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65364068"/>
+        <c:crossAx val="88268298"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7854,7 +8062,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65364068"/>
+        <c:axId val="88268298"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7930,7 +8138,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63959632"/>
+        <c:crossAx val="55330828"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8031,11 +8239,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B70</c:f>
+              <c:f>UNIQA!B70</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komplet (všetky pripoistenia)</c:v>
+                  <c:v>EXTRA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8081,23 +8289,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$71</c:f>
+              <c:f>UNIQA!$A$71</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$71</c:f>
+              <c:f>UNIQA!$B$71</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>286.39</c:v>
+                  <c:v>303.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8109,11 +8317,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C70</c:f>
+              <c:f>UNIQA!C70</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Základné riziká</c:v>
+                  <c:v>PLUS</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8159,23 +8367,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$71</c:f>
+              <c:f>UNIQA!$A$71</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$71</c:f>
+              <c:f>UNIQA!$C$71</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>94.53</c:v>
+                  <c:v>237.81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8190,11 +8398,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74491900"/>
-        <c:axId val="84053872"/>
+        <c:axId val="90295813"/>
+        <c:axId val="19395055"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74491900"/>
+        <c:axId val="90295813"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8260,7 +8468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84053872"/>
+        <c:crossAx val="19395055"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8268,7 +8476,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84053872"/>
+        <c:axId val="19395055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8344,7 +8552,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74491900"/>
+        <c:crossAx val="90295813"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8445,11 +8653,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B4</c:f>
+              <c:f>Union!B4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komfort</c:v>
+                  <c:v>Komplet (všetky pripoistenia)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8495,23 +8703,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5</c:f>
+              <c:f>Union!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$5</c:f>
+              <c:f>Union!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>144.96</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>151.45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>151.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8523,11 +8737,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C4</c:f>
+              <c:f>Union!C4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Premium</c:v>
+                  <c:v>Základné riziká</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8573,101 +8787,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5</c:f>
+              <c:f>Union!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$5</c:f>
+              <c:f>Union!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>167.64</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Standard</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="98b855"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:solidFill>
-                <a:srgbClr val="98b855"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$5</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>126.12</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>49.98</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8682,11 +8824,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="38845000"/>
-        <c:axId val="73903949"/>
+        <c:axId val="99030457"/>
+        <c:axId val="44592443"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38845000"/>
+        <c:axId val="99030457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8752,7 +8894,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73903949"/>
+        <c:crossAx val="44592443"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8760,7 +8902,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73903949"/>
+        <c:axId val="44592443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8836,7 +8978,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38845000"/>
+        <c:crossAx val="99030457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8937,11 +9079,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B26</c:f>
+              <c:f>Union!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komfort</c:v>
+                  <c:v>Komplet (všetky pripoistenia)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8987,23 +9129,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$27</c:f>
+              <c:f>Union!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$27</c:f>
+              <c:f>Union!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>114.96</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>120.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120.23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9015,11 +9163,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C26</c:f>
+              <c:f>Union!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Premium</c:v>
+                  <c:v>Základné riziká</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9065,101 +9213,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$27</c:f>
+              <c:f>Union!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$27</c:f>
+              <c:f>Union!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>132.84</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Standard</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="98b855"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:solidFill>
-                <a:srgbClr val="98b855"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$27</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$27</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>100.08</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9174,11 +9250,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18126353"/>
-        <c:axId val="93978975"/>
+        <c:axId val="61608934"/>
+        <c:axId val="3442506"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18126353"/>
+        <c:axId val="61608934"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9244,7 +9320,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93978975"/>
+        <c:crossAx val="3442506"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9252,7 +9328,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93978975"/>
+        <c:axId val="3442506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9328,7 +9404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18126353"/>
+        <c:crossAx val="61608934"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9429,11 +9505,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B48</c:f>
+              <c:f>Union!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Komfort</c:v>
+                  <c:v>Komplet (všetky pripoistenia)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9479,23 +9555,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$49</c:f>
+              <c:f>Union!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$49</c:f>
+              <c:f>Union!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>174.72</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>206.12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>206.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9507,11 +9589,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C48</c:f>
+              <c:f>Union!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Premium</c:v>
+                  <c:v>Základné riziká</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9557,101 +9639,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$49</c:f>
+              <c:f>Union!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$49</c:f>
+              <c:f>Union!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>194.76</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D48</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Standard</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="98b855"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:solidFill>
-                <a:srgbClr val="98b855"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$49</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$49</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>152.16</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>68.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68.04</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9666,11 +9676,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="679688"/>
-        <c:axId val="13105550"/>
+        <c:axId val="54714654"/>
+        <c:axId val="13069729"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="679688"/>
+        <c:axId val="54714654"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9736,7 +9746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13105550"/>
+        <c:crossAx val="13069729"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9744,7 +9754,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13105550"/>
+        <c:axId val="13069729"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9820,7 +9830,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679688"/>
+        <c:crossAx val="54714654"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9898,7 +9908,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Byt Bratislava</a:t>
+              <a:t>Dom Vlčkovce</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9921,11 +9931,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B4</c:f>
+              <c:f>Union!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Extra</c:v>
+                  <c:v>Komplet (všetky pripoistenia)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9971,23 +9981,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5</c:f>
+              <c:f>Union!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$5</c:f>
+              <c:f>Union!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>190.22</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>286.39</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>286.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9999,11 +10015,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C4</c:f>
+              <c:f>Union!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Klasik</c:v>
+                  <c:v>Základné riziká</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10049,101 +10065,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5</c:f>
+              <c:f>Union!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$5</c:f>
+              <c:f>Union!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>138.36</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Štandard</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="98b855"/>
-            </a:solidFill>
-            <a:ln w="28440">
-              <a:solidFill>
-                <a:srgbClr val="98b855"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15.10.2026</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$5</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>155.18</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>94.53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10158,11 +10102,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43879041"/>
-        <c:axId val="94823276"/>
+        <c:axId val="23942699"/>
+        <c:axId val="40422743"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43879041"/>
+        <c:axId val="23942699"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10228,7 +10172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94823276"/>
+        <c:crossAx val="40422743"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10236,7 +10180,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94823276"/>
+        <c:axId val="40422743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10312,7 +10256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43879041"/>
+        <c:crossAx val="23942699"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10390,7 +10334,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Byt Košice</a:t>
+              <a:t>Byt Bratislava</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10413,11 +10357,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B26</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Extra</c:v>
+                  <c:v>Komfort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10463,23 +10407,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>145.44</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>144.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>144.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10491,11 +10441,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C26</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Klasik</c:v>
+                  <c:v>Premium</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10541,23 +10491,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>105.6</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>167.64</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>167.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10569,11 +10525,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D26</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Štandard</c:v>
+                  <c:v>Standard</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10619,23 +10575,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>118.54</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>126.12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>126.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10650,11 +10612,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="14316963"/>
-        <c:axId val="44816288"/>
+        <c:axId val="46939691"/>
+        <c:axId val="43623553"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="14316963"/>
+        <c:axId val="46939691"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10720,7 +10682,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44816288"/>
+        <c:crossAx val="43623553"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10728,7 +10690,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44816288"/>
+        <c:axId val="43623553"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10804,7 +10766,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14316963"/>
+        <c:crossAx val="46939691"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11142,11 +11104,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29951003"/>
-        <c:axId val="36579940"/>
+        <c:axId val="38489796"/>
+        <c:axId val="83528887"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29951003"/>
+        <c:axId val="38489796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11212,7 +11174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36579940"/>
+        <c:crossAx val="83528887"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11220,7 +11182,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36579940"/>
+        <c:axId val="83528887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11296,7 +11258,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29951003"/>
+        <c:crossAx val="38489796"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11374,7 +11336,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Dom Malé Dvorníky</a:t>
+              <a:t>Byt Košice</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -11397,11 +11359,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B48</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Extra</c:v>
+                  <c:v>Komfort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11447,23 +11409,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>216.18</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>114.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>114.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11475,11 +11443,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C48</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Klasik</c:v>
+                  <c:v>Premium</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11525,23 +11493,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>157.93</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>132.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>132.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11553,11 +11527,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D48</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Štandard</c:v>
+                  <c:v>Standard</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11603,23 +11577,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$49</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>176.7</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>100.08</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11634,11 +11614,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30442923"/>
-        <c:axId val="59892007"/>
+        <c:axId val="53177987"/>
+        <c:axId val="11139750"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30442923"/>
+        <c:axId val="53177987"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11704,7 +11684,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59892007"/>
+        <c:crossAx val="11139750"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11712,7 +11692,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59892007"/>
+        <c:axId val="11139750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11788,7 +11768,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30442923"/>
+        <c:crossAx val="53177987"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11866,7 +11846,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Dom Vlčkovce</a:t>
+              <a:t>Dom Malé Dvorníky</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -11889,11 +11869,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B70</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Extra</c:v>
+                  <c:v>Komfort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11939,23 +11919,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>275.68</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>174.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>174.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11967,11 +11953,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C70</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Klasik</c:v>
+                  <c:v>Premium</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12017,23 +12003,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>202.39</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>194.76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>194.76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12045,11 +12037,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D70</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Štandard</c:v>
+                  <c:v>Standard</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12095,23 +12087,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$71</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>225.85</c:v>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>152.16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>152.16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12126,11 +12124,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52726347"/>
-        <c:axId val="24902568"/>
+        <c:axId val="75375664"/>
+        <c:axId val="37344692"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52726347"/>
+        <c:axId val="75375664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12196,7 +12194,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24902568"/>
+        <c:crossAx val="37344692"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12204,7 +12202,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24902568"/>
+        <c:axId val="37344692"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12280,7 +12278,2047 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52726347"/>
+        <c:crossAx val="75375664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Byt Bratislava</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!B4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Extra</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$B$5:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>190.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!C4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Klasik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$C$5:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>138.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>124.53</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!D4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Štandard</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$D$5:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>155.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>139.66</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="60292712"/>
+        <c:axId val="11393064"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="60292712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Dátum zberu</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="dd\.mm" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="11393064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="11393064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Cena (€)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="60292712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Byt Košice</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!B27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Extra</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$B$28:$B$29</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>145.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130.89</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!C27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Klasik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$C$28:$C$29</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>105.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!D27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Štandard</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$D$28:$D$29</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>118.54</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>106.69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="74006481"/>
+        <c:axId val="75175411"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="74006481"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Dátum zberu</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="dd\.mm" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="75175411"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="75175411"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Cena (€)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="74006481"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Dom Malé Dvorníky</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!B50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Extra</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$B$51:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>216.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>216.18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!C50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Klasik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$C$51:$C$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>157.93</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>157.93</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!D50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Štandard</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$D$51:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>176.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>176.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="71857467"/>
+        <c:axId val="15813900"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="71857467"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Dátum zberu</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="dd\.mm" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="15813900"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="15813900"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Cena (€)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="71857467"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Dom Vlčkovce</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!B73</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Extra</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$B$74:$B$75</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>275.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>306.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!C73</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Klasik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$C$74:$C$75</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>202.39</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>224.88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!D73</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Štandard</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ČSOB Poisťovňa'!$D$74:$D$75</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00" €"</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>225.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="38543789"/>
+        <c:axId val="81849880"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="38543789"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Dátum zberu</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="dd\.mm" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="81849880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="81849880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Cena (€)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00&quot; €&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="38543789"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12618,11 +14656,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="20500157"/>
-        <c:axId val="43395916"/>
+        <c:axId val="84633808"/>
+        <c:axId val="43610916"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="20500157"/>
+        <c:axId val="84633808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12688,7 +14726,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43395916"/>
+        <c:crossAx val="43610916"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12696,7 +14734,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43395916"/>
+        <c:axId val="43610916"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12772,7 +14810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20500157"/>
+        <c:crossAx val="84633808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12923,23 +14961,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5</c:f>
+              <c:f>Colonnade!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$5</c:f>
+              <c:f>Colonnade!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>151.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13001,23 +15045,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5</c:f>
+              <c:f>Colonnade!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$5</c:f>
+              <c:f>Colonnade!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>207.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13079,23 +15129,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5</c:f>
+              <c:f>Colonnade!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$5</c:f>
+              <c:f>Colonnade!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>201.92</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13110,11 +15166,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="305867"/>
-        <c:axId val="88245602"/>
+        <c:axId val="96760672"/>
+        <c:axId val="45324511"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="305867"/>
+        <c:axId val="96760672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13180,7 +15236,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88245602"/>
+        <c:crossAx val="45324511"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13188,7 +15244,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88245602"/>
+        <c:axId val="45324511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13264,7 +15320,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305867"/>
+        <c:crossAx val="96760672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13365,7 +15421,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B26</c:f>
+              <c:f>Colonnade!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13415,22 +15471,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$27</c:f>
+              <c:f>Colonnade!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$27</c:f>
+              <c:f>Colonnade!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>142.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>142.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -13443,7 +15505,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C26</c:f>
+              <c:f>Colonnade!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13493,22 +15555,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$27</c:f>
+              <c:f>Colonnade!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$27</c:f>
+              <c:f>Colonnade!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>191.67</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>191.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -13521,7 +15589,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D26</c:f>
+              <c:f>Colonnade!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13571,22 +15639,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$27</c:f>
+              <c:f>Colonnade!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$27</c:f>
+              <c:f>Colonnade!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>186.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>186.44</c:v>
                 </c:pt>
               </c:numCache>
@@ -13602,11 +15676,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39440097"/>
-        <c:axId val="2234611"/>
+        <c:axId val="22620760"/>
+        <c:axId val="32701870"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39440097"/>
+        <c:axId val="22620760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13672,7 +15746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2234611"/>
+        <c:crossAx val="32701870"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13680,7 +15754,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2234611"/>
+        <c:axId val="32701870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13756,7 +15830,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39440097"/>
+        <c:crossAx val="22620760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13857,7 +15931,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B48</c:f>
+              <c:f>Colonnade!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13907,22 +15981,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$49</c:f>
+              <c:f>Colonnade!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$49</c:f>
+              <c:f>Colonnade!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -13935,7 +16015,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C48</c:f>
+              <c:f>Colonnade!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13985,22 +16065,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$49</c:f>
+              <c:f>Colonnade!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$49</c:f>
+              <c:f>Colonnade!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -14013,7 +16099,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D48</c:f>
+              <c:f>Colonnade!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14063,22 +16149,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$49</c:f>
+              <c:f>Colonnade!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$49</c:f>
+              <c:f>Colonnade!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -14094,11 +16186,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10673465"/>
-        <c:axId val="54416003"/>
+        <c:axId val="76898441"/>
+        <c:axId val="62078999"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10673465"/>
+        <c:axId val="76898441"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14164,7 +16256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54416003"/>
+        <c:crossAx val="62078999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14172,7 +16264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54416003"/>
+        <c:axId val="62078999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14248,7 +16340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10673465"/>
+        <c:crossAx val="76898441"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14349,7 +16441,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B70</c:f>
+              <c:f>Colonnade!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14399,7 +16491,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$71</c:f>
+              <c:f>Colonnade!$A$74</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14410,7 +16502,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$71</c:f>
+              <c:f>Colonnade!$B$74</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
@@ -14427,7 +16519,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C70</c:f>
+              <c:f>Colonnade!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14477,7 +16569,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$71</c:f>
+              <c:f>Colonnade!$A$74</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14488,7 +16580,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$71</c:f>
+              <c:f>Colonnade!$C$74</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
@@ -14505,7 +16597,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D70</c:f>
+              <c:f>Colonnade!D73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14555,7 +16647,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$71</c:f>
+              <c:f>Colonnade!$A$74</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14566,7 +16658,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$71</c:f>
+              <c:f>Colonnade!$D$74</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="1"/>
@@ -14586,11 +16678,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96309088"/>
-        <c:axId val="41266236"/>
+        <c:axId val="59591244"/>
+        <c:axId val="3486112"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96309088"/>
+        <c:axId val="59591244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14656,7 +16748,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41266236"/>
+        <c:crossAx val="3486112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14664,7 +16756,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41266236"/>
+        <c:axId val="3486112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14740,7 +16832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96309088"/>
+        <c:crossAx val="59591244"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14891,22 +16983,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5</c:f>
+              <c:f>Generali!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$5</c:f>
+              <c:f>Generali!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>99.41</c:v>
                 </c:pt>
               </c:numCache>
@@ -14969,22 +17067,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5</c:f>
+              <c:f>Generali!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$5</c:f>
+              <c:f>Generali!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>114.74</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>114.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -15047,22 +17151,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5</c:f>
+              <c:f>Generali!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$5</c:f>
+              <c:f>Generali!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>94.81</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>94.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -15078,11 +17188,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37720995"/>
-        <c:axId val="65953613"/>
+        <c:axId val="33029475"/>
+        <c:axId val="56472175"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37720995"/>
+        <c:axId val="33029475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15148,7 +17258,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65953613"/>
+        <c:crossAx val="56472175"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15156,7 +17266,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65953613"/>
+        <c:axId val="56472175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15232,7 +17342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37720995"/>
+        <c:crossAx val="33029475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15445,13 +17555,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15460,7 +17570,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15475,14 +17585,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -15490,7 +17600,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15505,13 +17615,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15520,7 +17630,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15570,13 +17680,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15585,7 +17695,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15600,14 +17710,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -15615,7 +17725,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15630,13 +17740,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15645,7 +17755,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15695,13 +17805,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15710,7 +17820,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15725,14 +17835,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -15740,7 +17850,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15755,13 +17865,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15770,7 +17880,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15820,13 +17930,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15835,7 +17945,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15850,14 +17960,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -15865,7 +17975,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -15880,13 +17990,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -15895,7 +18005,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16038,13 +18148,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
@@ -16055,7 +18165,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="571680"/>
+        <a:off x="3571920" y="571680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16068,15 +18178,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -16085,7 +18195,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="3571920" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16098,16 +18208,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -16115,12 +18225,42 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="3571920" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="27" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3571920" y="13716000"/>
+        <a:ext cx="7199640" cy="3419640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -16146,7 +18286,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="27" name="Chart 1"/>
+        <xdr:cNvPr id="28" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -16165,22 +18305,22 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="28" name="Chart 2"/>
+        <xdr:cNvPr id="29" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16195,22 +18335,117 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="30" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4558680" y="9334440"/>
+        <a:ext cx="7199640" cy="3419640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="29" name="Chart 3"/>
+        <xdr:cNvPr id="31" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="571680"/>
+        <a:ext cx="7199640" cy="3419640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="32" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4558680" y="4952880"/>
+        <a:ext cx="7199640" cy="3419640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="33" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16225,22 +18460,22 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="30" name="Chart 4"/>
+        <xdr:cNvPr id="34" name="Chart 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -16594,7 +18829,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -16638,102 +18873,144 @@
         <v>201.92</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>12</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>142.75</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>191.67</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>186.44</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>12</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>186.44</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>182.53</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>246.96</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>240.14</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
@@ -16754,7 +19031,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -16798,102 +19075,158 @@
         <v>94.81</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>94.81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>15</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>77.55</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>92.26</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>73.19</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>15</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>73.19</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>152.27</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>163.7</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>147.57</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>199.86</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>211.29</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D75" s="5" t="n">
         <v>195.16</v>
       </c>
     </row>
@@ -16914,7 +19247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -16958,102 +19291,158 @@
         <v>86.02</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>121.09</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>86.02</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>19</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>95.79</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>79.6</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>69.52</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>19</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>69.52</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>145.65</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>115.11</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>92.59</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>213.4</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>165.4</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D75" s="5" t="n">
         <v>132.4</v>
       </c>
     </row>
@@ -17074,7 +19463,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -17118,102 +19507,158 @@
         <v>93.73</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>93.73</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>21</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>106.3</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>84.8</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>73.49</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>21</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>73.49</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>167.04</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>128.08</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>109.23</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>233.26</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>177.26</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D75" s="5" t="n">
         <v>148.98</v>
       </c>
     </row>
@@ -17263,13 +19708,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>151.45</v>
+        <v>207.75</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49.98</v>
+        <v>174.58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17290,13 +19735,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>120.23</v>
+        <v>164.09</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>39.68</v>
+        <v>139.42</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17317,13 +19762,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>206.12</v>
+        <v>234.99</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>68.04</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17344,13 +19789,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>286.39</v>
+        <v>303.1</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>94.53</v>
+        <v>237.81</v>
       </c>
     </row>
   </sheetData>
@@ -17370,10 +19815,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17396,98 +19841,141 @@
       <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>46310</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>144.96</v>
+        <v>151.45</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>167.64</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>126.12</v>
+        <v>49.98</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>49.98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>15</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>100.08</v>
+      <c r="B28" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>15</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>152.16</v>
+      <c r="B51" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>68.04</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>28</v>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>94.53</v>
       </c>
     </row>
   </sheetData>
@@ -17507,7 +19995,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -17515,7 +20003,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17528,13 +20016,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17542,6 +20030,185 @@
         <v>46310</v>
       </c>
       <c r="B5" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>126.12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>126.12</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>190.22</v>
       </c>
       <c r="C5" s="5" t="n">
@@ -17551,103 +20218,159 @@
         <v>155.18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>124.53</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>139.66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>31</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>145.44</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>105.6</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>118.54</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>31</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>130.89</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>106.69</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>216.18</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>157.93</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>176.7</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>31</v>
+      <c r="C73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>275.68</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>202.39</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
         <v>225.85</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>250.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -453,22 +453,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5</c:f>
+              <c:f>Allianz!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$5</c:f>
+              <c:f>Allianz!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>53.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -531,22 +537,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5</c:f>
+              <c:f>Allianz!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$5</c:f>
+              <c:f>Allianz!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>112.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>112.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -609,22 +621,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5</c:f>
+              <c:f>Allianz!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$5</c:f>
+              <c:f>Allianz!$D$5:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>145.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>145.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -640,11 +658,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29901183"/>
-        <c:axId val="32847137"/>
+        <c:axId val="93605726"/>
+        <c:axId val="70980622"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29901183"/>
+        <c:axId val="93605726"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -710,7 +728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32847137"/>
+        <c:crossAx val="70980622"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -718,7 +736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32847137"/>
+        <c:axId val="70980622"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -794,7 +812,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29901183"/>
+        <c:crossAx val="93605726"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -895,7 +913,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B27</c:f>
+              <c:f>Generali!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -945,28 +963,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$28:$A$29</c:f>
+              <c:f>Generali!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$28:$B$29</c:f>
+              <c:f>Generali!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>77.55</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>77.55</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>77.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -979,7 +1003,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C27</c:f>
+              <c:f>Generali!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1029,28 +1053,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$28:$A$29</c:f>
+              <c:f>Generali!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$28:$C$29</c:f>
+              <c:f>Generali!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>92.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>92.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -1063,7 +1093,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D27</c:f>
+              <c:f>Generali!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1113,28 +1143,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$28:$A$29</c:f>
+              <c:f>Generali!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$28:$D$29</c:f>
+              <c:f>Generali!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>73.19</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>73.19</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>73.19</c:v>
                 </c:pt>
               </c:numCache>
@@ -1150,11 +1186,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="13081840"/>
-        <c:axId val="33486115"/>
+        <c:axId val="96082633"/>
+        <c:axId val="41740890"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="13081840"/>
+        <c:axId val="96082633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1220,7 +1256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33486115"/>
+        <c:crossAx val="41740890"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1228,7 +1264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33486115"/>
+        <c:axId val="41740890"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1304,7 +1340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13081840"/>
+        <c:crossAx val="96082633"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1405,7 +1441,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B50</c:f>
+              <c:f>Generali!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1455,28 +1491,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$51:$A$52</c:f>
+              <c:f>Generali!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$51:$B$52</c:f>
+              <c:f>Generali!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>152.27</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>152.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>152.27</c:v>
                 </c:pt>
               </c:numCache>
@@ -1489,7 +1531,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C50</c:f>
+              <c:f>Generali!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1539,28 +1581,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$51:$A$52</c:f>
+              <c:f>Generali!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$51:$C$52</c:f>
+              <c:f>Generali!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>163.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>163.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>163.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1573,7 +1621,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D50</c:f>
+              <c:f>Generali!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1623,28 +1671,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$51:$A$52</c:f>
+              <c:f>Generali!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$51:$D$52</c:f>
+              <c:f>Generali!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>147.57</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>147.57</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>147.57</c:v>
                 </c:pt>
               </c:numCache>
@@ -1660,11 +1714,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61152449"/>
-        <c:axId val="12324515"/>
+        <c:axId val="6284379"/>
+        <c:axId val="78665736"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61152449"/>
+        <c:axId val="6284379"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12324515"/>
+        <c:crossAx val="78665736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1738,7 +1792,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12324515"/>
+        <c:axId val="78665736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1814,7 +1868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61152449"/>
+        <c:crossAx val="6284379"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1915,7 +1969,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B73</c:f>
+              <c:f>Generali!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1965,28 +2019,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$74:$A$75</c:f>
+              <c:f>Generali!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$74:$B$75</c:f>
+              <c:f>Generali!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>199.86</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>199.86</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>199.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -1999,7 +2059,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C73</c:f>
+              <c:f>Generali!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2049,28 +2109,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$74:$A$75</c:f>
+              <c:f>Generali!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$74:$C$75</c:f>
+              <c:f>Generali!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>211.29</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>211.29</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>211.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -2083,7 +2149,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D73</c:f>
+              <c:f>Generali!D76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2133,28 +2199,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$74:$A$75</c:f>
+              <c:f>Generali!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$74:$D$75</c:f>
+              <c:f>Generali!$D$77:$D$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>195.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>195.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>195.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -2170,11 +2242,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="51569093"/>
-        <c:axId val="43901180"/>
+        <c:axId val="91770468"/>
+        <c:axId val="1642020"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="51569093"/>
+        <c:axId val="91770468"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2240,7 +2312,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43901180"/>
+        <c:crossAx val="1642020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2248,7 +2320,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43901180"/>
+        <c:axId val="1642020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2324,7 +2396,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51569093"/>
+        <c:crossAx val="91770468"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2475,28 +2547,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>121.09</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>121.09</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>121.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -2559,28 +2637,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>98.77</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>98.77</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>98.77</c:v>
                 </c:pt>
               </c:numCache>
@@ -2643,28 +2727,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$6</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>86.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>86.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>86.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2680,11 +2770,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84607786"/>
-        <c:axId val="5930653"/>
+        <c:axId val="53769473"/>
+        <c:axId val="83058260"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84607786"/>
+        <c:axId val="53769473"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2750,7 +2840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5930653"/>
+        <c:crossAx val="83058260"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2758,7 +2848,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5930653"/>
+        <c:axId val="83058260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2834,7 +2924,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84607786"/>
+        <c:crossAx val="53769473"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2935,7 +3025,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2985,28 +3075,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$28:$B$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>95.79</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>95.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -3019,7 +3115,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3069,28 +3165,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$28:$C$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>79.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>79.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>79.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3103,7 +3205,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D27</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3153,28 +3255,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$28:$D$29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>69.52</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>69.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>69.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -3190,11 +3298,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="99048534"/>
-        <c:axId val="45542239"/>
+        <c:axId val="54230094"/>
+        <c:axId val="44638701"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="99048534"/>
+        <c:axId val="54230094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3260,7 +3368,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45542239"/>
+        <c:crossAx val="44638701"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3268,7 +3376,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45542239"/>
+        <c:axId val="44638701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3344,7 +3452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99048534"/>
+        <c:crossAx val="54230094"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3445,7 +3553,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B50</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3495,28 +3603,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$51:$B$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>145.65</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>145.65</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>145.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -3529,7 +3643,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C50</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3579,28 +3693,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$51:$C$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>115.11</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>115.11</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>115.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -3613,7 +3733,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D50</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3663,28 +3783,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$51:$D$52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>92.59</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>92.59</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>92.59</c:v>
                 </c:pt>
               </c:numCache>
@@ -3700,11 +3826,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16140624"/>
-        <c:axId val="17033608"/>
+        <c:axId val="55305049"/>
+        <c:axId val="94694092"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16140624"/>
+        <c:axId val="55305049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3770,7 +3896,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17033608"/>
+        <c:crossAx val="94694092"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3778,7 +3904,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17033608"/>
+        <c:axId val="94694092"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3854,7 +3980,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16140624"/>
+        <c:crossAx val="55305049"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3955,7 +4081,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4005,28 +4131,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$74:$B$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>213.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>213.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4039,7 +4171,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4089,28 +4221,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$74:$C$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>165.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>165.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>165.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4123,7 +4261,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4173,28 +4311,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$74:$D$75</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$77:$D$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>132.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>132.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4210,11 +4354,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="6399888"/>
-        <c:axId val="11753463"/>
+        <c:axId val="77515369"/>
+        <c:axId val="62101554"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6399888"/>
+        <c:axId val="77515369"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4280,7 +4424,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11753463"/>
+        <c:crossAx val="62101554"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4288,7 +4432,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11753463"/>
+        <c:axId val="62101554"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4364,7 +4508,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6399888"/>
+        <c:crossAx val="77515369"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4515,28 +4659,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>138.66</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>138.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>138.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -4599,28 +4749,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>108.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>108.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>108.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -4683,28 +4839,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$6</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>93.73</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>93.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -4720,11 +4882,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="59093658"/>
-        <c:axId val="72516643"/>
+        <c:axId val="11419182"/>
+        <c:axId val="87243752"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="59093658"/>
+        <c:axId val="11419182"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4790,7 +4952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72516643"/>
+        <c:crossAx val="87243752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4798,7 +4960,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72516643"/>
+        <c:axId val="87243752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4874,7 +5036,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59093658"/>
+        <c:crossAx val="11419182"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4975,7 +5137,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5025,28 +5187,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$28:$B$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>106.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>106.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -5059,7 +5227,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5109,28 +5277,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$28:$C$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>84.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>84.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>84.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -5143,7 +5317,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D27</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5193,28 +5367,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$28:$A$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$28:$D$29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>73.49</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>73.49</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>73.49</c:v>
                 </c:pt>
               </c:numCache>
@@ -5230,11 +5410,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7170341"/>
-        <c:axId val="97738631"/>
+        <c:axId val="13199939"/>
+        <c:axId val="24189179"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7170341"/>
+        <c:axId val="13199939"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5300,7 +5480,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97738631"/>
+        <c:crossAx val="24189179"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5308,7 +5488,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97738631"/>
+        <c:axId val="24189179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5384,7 +5564,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7170341"/>
+        <c:crossAx val="13199939"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5485,7 +5665,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B50</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5535,28 +5715,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$51:$B$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>167.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>167.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>167.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -5569,7 +5755,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C50</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5619,28 +5805,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$51:$C$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>128.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>128.08</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>128.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -5653,7 +5845,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D50</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5703,28 +5895,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$51:$A$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$51:$D$52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>109.23</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>109.23</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>109.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -5740,11 +5938,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78835011"/>
-        <c:axId val="34433826"/>
+        <c:axId val="69807201"/>
+        <c:axId val="86721379"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78835011"/>
+        <c:axId val="69807201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5810,7 +6008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34433826"/>
+        <c:crossAx val="86721379"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5818,7 +6016,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34433826"/>
+        <c:axId val="86721379"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5894,7 +6092,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78835011"/>
+        <c:crossAx val="69807201"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5995,7 +6193,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B26</c:f>
+              <c:f>Allianz!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6045,22 +6243,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$27</c:f>
+              <c:f>Allianz!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$27</c:f>
+              <c:f>Allianz!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>49.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>49.36</c:v>
                 </c:pt>
               </c:numCache>
@@ -6073,7 +6277,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C26</c:f>
+              <c:f>Allianz!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6123,22 +6327,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$27</c:f>
+              <c:f>Allianz!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$27</c:f>
+              <c:f>Allianz!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>93.24</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>93.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -6151,7 +6361,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D26</c:f>
+              <c:f>Allianz!D27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6201,22 +6411,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$27</c:f>
+              <c:f>Allianz!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$27</c:f>
+              <c:f>Allianz!$D$28:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>119.52</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>119.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -6232,11 +6448,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71951031"/>
-        <c:axId val="35348413"/>
+        <c:axId val="55006156"/>
+        <c:axId val="42752409"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71951031"/>
+        <c:axId val="55006156"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6302,7 +6518,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35348413"/>
+        <c:crossAx val="42752409"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6310,7 +6526,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35348413"/>
+        <c:axId val="42752409"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6386,7 +6602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71951031"/>
+        <c:crossAx val="55006156"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6487,7 +6703,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6537,28 +6753,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$74:$B$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>233.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>233.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>233.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6571,7 +6793,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6621,28 +6843,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$74:$C$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>177.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>177.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>177.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6655,7 +6883,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6705,28 +6933,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$74:$A$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$74:$D$75</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$77:$D$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>148.98</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>148.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>148.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -6742,11 +6976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66202411"/>
-        <c:axId val="85851099"/>
+        <c:axId val="58259293"/>
+        <c:axId val="81634202"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="66202411"/>
+        <c:axId val="58259293"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6812,7 +7046,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85851099"/>
+        <c:crossAx val="81634202"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6820,7 +7054,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85851099"/>
+        <c:axId val="81634202"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6896,7 +7130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66202411"/>
+        <c:crossAx val="58259293"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7047,22 +7281,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5</c:f>
+              <c:f>UNIQA!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$5</c:f>
+              <c:f>UNIQA!$B$5:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>207.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>207.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -7125,22 +7365,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5</c:f>
+              <c:f>UNIQA!$A$5:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$5</c:f>
+              <c:f>UNIQA!$C$5:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>174.58</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>174.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -7156,11 +7402,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18670966"/>
-        <c:axId val="12727401"/>
+        <c:axId val="1473529"/>
+        <c:axId val="14869742"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18670966"/>
+        <c:axId val="1473529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7226,7 +7472,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12727401"/>
+        <c:crossAx val="14869742"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7234,7 +7480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12727401"/>
+        <c:axId val="14869742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7310,7 +7556,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18670966"/>
+        <c:crossAx val="1473529"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7411,7 +7657,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B26</c:f>
+              <c:f>UNIQA!B27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7461,22 +7707,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$27</c:f>
+              <c:f>UNIQA!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$27</c:f>
+              <c:f>UNIQA!$B$28:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>164.09</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>164.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -7489,7 +7741,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C26</c:f>
+              <c:f>UNIQA!C27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7539,22 +7791,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$27</c:f>
+              <c:f>UNIQA!$A$28:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$27</c:f>
+              <c:f>UNIQA!$C$28:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>139.42</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>139.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -7570,11 +7828,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60850194"/>
-        <c:axId val="99499875"/>
+        <c:axId val="40628064"/>
+        <c:axId val="40932873"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60850194"/>
+        <c:axId val="40628064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7640,7 +7898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99499875"/>
+        <c:crossAx val="40932873"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7648,7 +7906,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99499875"/>
+        <c:axId val="40932873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7724,7 +7982,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60850194"/>
+        <c:crossAx val="40628064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7825,7 +8083,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B48</c:f>
+              <c:f>UNIQA!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7875,22 +8133,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$49</c:f>
+              <c:f>UNIQA!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$49</c:f>
+              <c:f>UNIQA!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>234.99</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>234.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -7903,7 +8167,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C48</c:f>
+              <c:f>UNIQA!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7953,22 +8217,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$49</c:f>
+              <c:f>UNIQA!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$49</c:f>
+              <c:f>UNIQA!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>183.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>183.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -7984,11 +8254,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="55330828"/>
-        <c:axId val="88268298"/>
+        <c:axId val="91731846"/>
+        <c:axId val="48549925"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="55330828"/>
+        <c:axId val="91731846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8054,7 +8324,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88268298"/>
+        <c:crossAx val="48549925"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8062,7 +8332,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88268298"/>
+        <c:axId val="48549925"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8138,7 +8408,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55330828"/>
+        <c:crossAx val="91731846"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8239,7 +8509,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B70</c:f>
+              <c:f>UNIQA!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8289,22 +8559,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$71</c:f>
+              <c:f>UNIQA!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$71</c:f>
+              <c:f>UNIQA!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>303.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>303.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8317,7 +8593,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C70</c:f>
+              <c:f>UNIQA!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8367,22 +8643,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$71</c:f>
+              <c:f>UNIQA!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$71</c:f>
+              <c:f>UNIQA!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>237.81</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>237.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -8398,11 +8680,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90295813"/>
-        <c:axId val="19395055"/>
+        <c:axId val="28461933"/>
+        <c:axId val="39954223"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90295813"/>
+        <c:axId val="28461933"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8468,7 +8750,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19395055"/>
+        <c:crossAx val="39954223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8476,7 +8758,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19395055"/>
+        <c:axId val="39954223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8552,7 +8834,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90295813"/>
+        <c:crossAx val="28461933"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8703,28 +8985,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$6</c:f>
+              <c:f>Union!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$5:$B$6</c:f>
+              <c:f>Union!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>151.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>151.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>151.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -8787,28 +9075,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$6</c:f>
+              <c:f>Union!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$5:$C$6</c:f>
+              <c:f>Union!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>49.98</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>49.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>49.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -8824,11 +9118,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="99030457"/>
-        <c:axId val="44592443"/>
+        <c:axId val="21974709"/>
+        <c:axId val="19117836"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="99030457"/>
+        <c:axId val="21974709"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8894,7 +9188,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44592443"/>
+        <c:crossAx val="19117836"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8902,7 +9196,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44592443"/>
+        <c:axId val="19117836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8978,7 +9272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99030457"/>
+        <c:crossAx val="21974709"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9079,7 +9373,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B27</c:f>
+              <c:f>Union!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9129,29 +9423,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$28:$A$29</c:f>
+              <c:f>Union!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$28:$B$29</c:f>
+              <c:f>Union!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>120.23</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120.23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9163,7 +9463,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C27</c:f>
+              <c:f>Union!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9213,28 +9513,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$28:$A$29</c:f>
+              <c:f>Union!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$28:$C$29</c:f>
+              <c:f>Union!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>39.68</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
@@ -9250,11 +9556,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61608934"/>
-        <c:axId val="3442506"/>
+        <c:axId val="8853971"/>
+        <c:axId val="1518193"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61608934"/>
+        <c:axId val="8853971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9320,7 +9626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3442506"/>
+        <c:crossAx val="1518193"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9328,7 +9634,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3442506"/>
+        <c:axId val="1518193"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9404,7 +9710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61608934"/>
+        <c:crossAx val="8853971"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9505,7 +9811,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B50</c:f>
+              <c:f>Union!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9555,28 +9861,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$51:$A$52</c:f>
+              <c:f>Union!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$51:$B$52</c:f>
+              <c:f>Union!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>206.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>206.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>206.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -9589,7 +9901,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C50</c:f>
+              <c:f>Union!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9639,28 +9951,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$51:$A$52</c:f>
+              <c:f>Union!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$51:$C$52</c:f>
+              <c:f>Union!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>68.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>68.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>68.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -9676,11 +9994,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54714654"/>
-        <c:axId val="13069729"/>
+        <c:axId val="37124757"/>
+        <c:axId val="95285539"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54714654"/>
+        <c:axId val="37124757"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9746,7 +10064,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13069729"/>
+        <c:crossAx val="95285539"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9754,7 +10072,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13069729"/>
+        <c:axId val="95285539"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9830,7 +10148,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54714654"/>
+        <c:crossAx val="37124757"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9931,7 +10249,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B73</c:f>
+              <c:f>Union!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9981,28 +10299,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$74:$A$75</c:f>
+              <c:f>Union!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$74:$B$75</c:f>
+              <c:f>Union!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>286.39</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>286.39</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>286.39</c:v>
                 </c:pt>
               </c:numCache>
@@ -10015,7 +10339,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C73</c:f>
+              <c:f>Union!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10065,28 +10389,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$74:$A$75</c:f>
+              <c:f>Union!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$74:$C$75</c:f>
+              <c:f>Union!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>94.53</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94.53</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>94.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -10102,11 +10432,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23942699"/>
-        <c:axId val="40422743"/>
+        <c:axId val="31512300"/>
+        <c:axId val="64116723"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="23942699"/>
+        <c:axId val="31512300"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10172,7 +10502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40422743"/>
+        <c:crossAx val="64116723"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10180,7 +10510,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40422743"/>
+        <c:axId val="64116723"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10256,7 +10586,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23942699"/>
+        <c:crossAx val="31512300"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10407,28 +10737,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>144.96</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>144.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>144.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -10491,28 +10827,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>167.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>167.64</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>167.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -10575,28 +10917,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$6</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>126.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>126.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>126.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -10612,11 +10960,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="46939691"/>
-        <c:axId val="43623553"/>
+        <c:axId val="90897879"/>
+        <c:axId val="40694075"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="46939691"/>
+        <c:axId val="90897879"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10682,7 +11030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43623553"/>
+        <c:crossAx val="40694075"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10690,7 +11038,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43623553"/>
+        <c:axId val="40694075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10766,7 +11114,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46939691"/>
+        <c:crossAx val="90897879"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10867,7 +11215,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B48</c:f>
+              <c:f>Allianz!B50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10917,22 +11265,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$49</c:f>
+              <c:f>Allianz!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$49</c:f>
+              <c:f>Allianz!$B$51:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>117.24</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>117.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -10945,7 +11299,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C48</c:f>
+              <c:f>Allianz!C50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10995,22 +11349,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$49</c:f>
+              <c:f>Allianz!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$49</c:f>
+              <c:f>Allianz!$C$51:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>159</c:v>
                 </c:pt>
               </c:numCache>
@@ -11023,7 +11383,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D48</c:f>
+              <c:f>Allianz!D50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11073,22 +11433,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$49</c:f>
+              <c:f>Allianz!$A$51:$A$52</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$49</c:f>
+              <c:f>Allianz!$D$51:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>206.64</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>206.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -11104,11 +11470,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="38489796"/>
-        <c:axId val="83528887"/>
+        <c:axId val="92944617"/>
+        <c:axId val="89740127"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38489796"/>
+        <c:axId val="92944617"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11174,7 +11540,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83528887"/>
+        <c:crossAx val="89740127"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11182,7 +11548,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83528887"/>
+        <c:axId val="89740127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11258,7 +11624,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38489796"/>
+        <c:crossAx val="92944617"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11359,7 +11725,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11409,28 +11775,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$28:$B$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>114.96</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>114.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>114.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -11443,7 +11815,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11493,28 +11865,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$28:$C$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>132.84</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>132.84</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>132.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -11527,7 +11905,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D27</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11577,28 +11955,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$28:$A$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$28:$D$29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>100.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>100.08</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>100.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -11614,11 +11998,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53177987"/>
-        <c:axId val="11139750"/>
+        <c:axId val="83869518"/>
+        <c:axId val="47483447"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53177987"/>
+        <c:axId val="83869518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11684,7 +12068,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11139750"/>
+        <c:crossAx val="47483447"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11692,7 +12076,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11139750"/>
+        <c:axId val="47483447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11768,7 +12152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53177987"/>
+        <c:crossAx val="83869518"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11869,7 +12253,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B50</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11919,28 +12303,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$51:$B$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>174.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>174.72</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>174.72</c:v>
                 </c:pt>
               </c:numCache>
@@ -11953,7 +12343,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C50</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12003,28 +12393,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$51:$C$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>194.76</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>194.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>194.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -12037,7 +12433,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D50</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12087,28 +12483,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$51:$A$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$51:$D$52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>152.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>152.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>152.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -12124,11 +12526,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75375664"/>
-        <c:axId val="37344692"/>
+        <c:axId val="12030464"/>
+        <c:axId val="37849185"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75375664"/>
+        <c:axId val="12030464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12194,7 +12596,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37344692"/>
+        <c:crossAx val="37849185"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12202,7 +12604,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37344692"/>
+        <c:axId val="37849185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12278,7 +12680,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75375664"/>
+        <c:crossAx val="12030464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12429,29 +12831,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$5:$B$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>190.22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>171.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12513,29 +12921,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$5:$C$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>138.36</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>124.53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12597,29 +13011,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$5:$D$6</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>155.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>139.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12634,11 +13054,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60292712"/>
-        <c:axId val="11393064"/>
+        <c:axId val="8462167"/>
+        <c:axId val="46228431"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60292712"/>
+        <c:axId val="8462167"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12704,7 +13124,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11393064"/>
+        <c:crossAx val="46228431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12712,7 +13132,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11393064"/>
+        <c:axId val="46228431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12788,7 +13208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60292712"/>
+        <c:crossAx val="8462167"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12889,7 +13309,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B27</c:f>
+              <c:f>'ČSOB Poisťovňa'!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12939,7 +13359,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -12953,7 +13373,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$28:$B$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$29:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -12973,7 +13393,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C27</c:f>
+              <c:f>'ČSOB Poisťovňa'!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13023,7 +13443,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13037,7 +13457,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$28:$C$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$29:$C$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13057,7 +13477,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D27</c:f>
+              <c:f>'ČSOB Poisťovňa'!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13107,7 +13527,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$28:$A$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13121,7 +13541,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$28:$D$29</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$29:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13144,11 +13564,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74006481"/>
-        <c:axId val="75175411"/>
+        <c:axId val="98214665"/>
+        <c:axId val="88490572"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74006481"/>
+        <c:axId val="98214665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13214,7 +13634,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75175411"/>
+        <c:crossAx val="88490572"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13222,7 +13642,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75175411"/>
+        <c:axId val="88490572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13298,7 +13718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74006481"/>
+        <c:crossAx val="98214665"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13399,7 +13819,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B50</c:f>
+              <c:f>'ČSOB Poisťovňa'!B51</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13449,28 +13869,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$51:$B$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$52:$B$54</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>216.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>216.18</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>216.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -13483,7 +13909,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C50</c:f>
+              <c:f>'ČSOB Poisťovňa'!C51</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13533,28 +13959,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$51:$C$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$52:$C$54</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>157.93</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>157.93</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>157.93</c:v>
                 </c:pt>
               </c:numCache>
@@ -13567,7 +13999,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D50</c:f>
+              <c:f>'ČSOB Poisťovňa'!D51</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13617,28 +14049,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$51:$A$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$51:$D$52</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$52:$D$54</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>176.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>176.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>176.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -13654,11 +14092,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71857467"/>
-        <c:axId val="15813900"/>
+        <c:axId val="60081601"/>
+        <c:axId val="23674917"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71857467"/>
+        <c:axId val="60081601"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13724,7 +14162,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15813900"/>
+        <c:crossAx val="23674917"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13732,7 +14170,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15813900"/>
+        <c:axId val="23674917"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13808,7 +14246,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71857467"/>
+        <c:crossAx val="60081601"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13909,7 +14347,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B73</c:f>
+              <c:f>'ČSOB Poisťovňa'!B75</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13959,28 +14397,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$74:$B$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$76:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>275.68</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>306.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>306.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -13993,7 +14437,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C73</c:f>
+              <c:f>'ČSOB Poisťovňa'!C75</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14043,28 +14487,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$74:$C$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$76:$C$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>202.39</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>224.88</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>224.88</c:v>
                 </c:pt>
               </c:numCache>
@@ -14077,7 +14527,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D73</c:f>
+              <c:f>'ČSOB Poisťovňa'!D75</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14127,28 +14577,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$74:$A$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$74:$D$75</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$76:$D$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>225.85</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>250.95</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>250.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -14164,11 +14620,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="38543789"/>
-        <c:axId val="81849880"/>
+        <c:axId val="19229011"/>
+        <c:axId val="30599641"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38543789"/>
+        <c:axId val="19229011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14234,7 +14690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81849880"/>
+        <c:crossAx val="30599641"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14242,7 +14698,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81849880"/>
+        <c:axId val="30599641"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14318,7 +14774,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38543789"/>
+        <c:crossAx val="19229011"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14419,7 +14875,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B70</c:f>
+              <c:f>Allianz!B73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14469,22 +14925,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$71</c:f>
+              <c:f>Allianz!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$71</c:f>
+              <c:f>Allianz!$B$74:$B$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>158.64</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>158.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -14497,7 +14959,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C70</c:f>
+              <c:f>Allianz!C73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14547,22 +15009,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$71</c:f>
+              <c:f>Allianz!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$71</c:f>
+              <c:f>Allianz!$C$74:$C$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>216.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>216.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -14575,7 +15043,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D70</c:f>
+              <c:f>Allianz!D73</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14625,22 +15093,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$71</c:f>
+              <c:f>Allianz!$A$74:$A$75</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$71</c:f>
+              <c:f>Allianz!$D$74:$D$75</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>277.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>277.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -14656,11 +15130,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84633808"/>
-        <c:axId val="43610916"/>
+        <c:axId val="24402108"/>
+        <c:axId val="71741683"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84633808"/>
+        <c:axId val="24402108"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14726,7 +15200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43610916"/>
+        <c:crossAx val="71741683"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14734,7 +15208,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43610916"/>
+        <c:axId val="71741683"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14810,7 +15284,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84633808"/>
+        <c:crossAx val="24402108"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14961,28 +15435,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$6</c:f>
+              <c:f>Colonnade!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$5:$B$6</c:f>
+              <c:f>Colonnade!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>151.84</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -15045,28 +15525,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$6</c:f>
+              <c:f>Colonnade!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$5:$C$6</c:f>
+              <c:f>Colonnade!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>207.85</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -15129,28 +15615,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$6</c:f>
+              <c:f>Colonnade!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$5:$D$6</c:f>
+              <c:f>Colonnade!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>201.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -15166,11 +15658,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96760672"/>
-        <c:axId val="45324511"/>
+        <c:axId val="9645608"/>
+        <c:axId val="73666824"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96760672"/>
+        <c:axId val="9645608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15236,7 +15728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45324511"/>
+        <c:crossAx val="73666824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15244,7 +15736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45324511"/>
+        <c:axId val="73666824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15320,7 +15812,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96760672"/>
+        <c:crossAx val="9645608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15421,7 +15913,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B27</c:f>
+              <c:f>Colonnade!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15471,28 +15963,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$28:$A$29</c:f>
+              <c:f>Colonnade!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$28:$B$29</c:f>
+              <c:f>Colonnade!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>142.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>142.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>142.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -15505,7 +16003,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C27</c:f>
+              <c:f>Colonnade!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15555,28 +16053,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$28:$A$29</c:f>
+              <c:f>Colonnade!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$28:$C$29</c:f>
+              <c:f>Colonnade!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>191.67</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>191.67</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>191.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -15589,7 +16093,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D27</c:f>
+              <c:f>Colonnade!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15639,28 +16143,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$28:$A$29</c:f>
+              <c:f>Colonnade!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$28:$D$29</c:f>
+              <c:f>Colonnade!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>186.44</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>186.44</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>186.44</c:v>
                 </c:pt>
               </c:numCache>
@@ -15676,11 +16186,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="22620760"/>
-        <c:axId val="32701870"/>
+        <c:axId val="4284085"/>
+        <c:axId val="33837936"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="22620760"/>
+        <c:axId val="4284085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15746,7 +16256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32701870"/>
+        <c:crossAx val="33837936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15754,7 +16264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32701870"/>
+        <c:axId val="33837936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15830,7 +16340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22620760"/>
+        <c:crossAx val="4284085"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15931,7 +16441,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B50</c:f>
+              <c:f>Colonnade!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15981,28 +16491,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$51:$A$52</c:f>
+              <c:f>Colonnade!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$51:$B$52</c:f>
+              <c:f>Colonnade!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>182.53</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -16015,7 +16531,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C50</c:f>
+              <c:f>Colonnade!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16065,28 +16581,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$51:$A$52</c:f>
+              <c:f>Colonnade!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$51:$C$52</c:f>
+              <c:f>Colonnade!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>246.96</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -16099,7 +16621,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D50</c:f>
+              <c:f>Colonnade!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16149,28 +16671,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$51:$A$52</c:f>
+              <c:f>Colonnade!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$51:$D$52</c:f>
+              <c:f>Colonnade!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>240.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -16186,11 +16714,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="76898441"/>
-        <c:axId val="62078999"/>
+        <c:axId val="43876004"/>
+        <c:axId val="62408275"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="76898441"/>
+        <c:axId val="43876004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16256,7 +16784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62078999"/>
+        <c:crossAx val="62408275"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16264,7 +16792,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62078999"/>
+        <c:axId val="62408275"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16340,7 +16868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76898441"/>
+        <c:crossAx val="43876004"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16441,7 +16969,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B73</c:f>
+              <c:f>Colonnade!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16491,22 +17019,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$74</c:f>
+              <c:f>Colonnade!$A$77:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$74</c:f>
+              <c:f>Colonnade!$B$77:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>254.31</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>254.31</c:v>
                 </c:pt>
               </c:numCache>
@@ -16519,7 +17053,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C73</c:f>
+              <c:f>Colonnade!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16569,22 +17103,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$74</c:f>
+              <c:f>Colonnade!$A$77:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$74</c:f>
+              <c:f>Colonnade!$C$77:$C$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>347.42</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>347.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -16597,7 +17137,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D73</c:f>
+              <c:f>Colonnade!D76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16647,22 +17187,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$74</c:f>
+              <c:f>Colonnade!$A$77:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$74</c:f>
+              <c:f>Colonnade!$D$77:$D$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>337.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>337.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -16678,11 +17224,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="59591244"/>
-        <c:axId val="3486112"/>
+        <c:axId val="74191444"/>
+        <c:axId val="39705626"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="59591244"/>
+        <c:axId val="74191444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16748,7 +17294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3486112"/>
+        <c:crossAx val="39705626"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16756,7 +17302,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3486112"/>
+        <c:axId val="39705626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16832,7 +17378,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59591244"/>
+        <c:crossAx val="74191444"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16983,28 +17529,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$6</c:f>
+              <c:f>Generali!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$5:$B$6</c:f>
+              <c:f>Generali!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>99.41</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>99.41</c:v>
                 </c:pt>
               </c:numCache>
@@ -17067,28 +17619,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$6</c:f>
+              <c:f>Generali!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$5:$C$6</c:f>
+              <c:f>Generali!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>114.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>114.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>114.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -17151,28 +17709,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$6</c:f>
+              <c:f>Generali!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$5:$D$6</c:f>
+              <c:f>Generali!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>94.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>94.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -17188,11 +17752,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="33029475"/>
-        <c:axId val="56472175"/>
+        <c:axId val="12369964"/>
+        <c:axId val="29715744"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33029475"/>
+        <c:axId val="12369964"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17258,7 +17822,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56472175"/>
+        <c:crossAx val="29715744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17266,7 +17830,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56472175"/>
+        <c:axId val="29715744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17342,7 +17906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33029475"/>
+        <c:crossAx val="12369964"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17430,13 +17994,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -17445,7 +18009,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4762440"/>
+        <a:off x="4558680" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17460,14 +18024,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17475,7 +18039,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="8953560"/>
+        <a:off x="4558680" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17490,13 +18054,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -17505,7 +18069,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13144680"/>
+        <a:off x="4558680" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17555,14 +18119,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17570,7 +18134,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17585,14 +18149,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17600,7 +18164,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17615,13 +18179,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -17630,7 +18194,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17680,14 +18244,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17695,7 +18259,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17710,14 +18274,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17725,7 +18289,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17740,13 +18304,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -17755,7 +18319,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17805,14 +18369,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17820,7 +18384,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17835,14 +18399,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17850,7 +18414,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17865,13 +18429,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -17880,7 +18444,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17930,14 +18494,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17945,7 +18509,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17960,14 +18524,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -17975,7 +18539,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -17990,13 +18554,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18005,7 +18569,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18055,13 +18619,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18070,7 +18634,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="4762440"/>
+        <a:off x="3571920" y="4952880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18085,14 +18649,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18100,7 +18664,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="8953560"/>
+        <a:off x="3571920" y="9334440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18115,13 +18679,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18130,7 +18694,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="13144680"/>
+        <a:off x="3571920" y="13716000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18180,14 +18744,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18195,7 +18759,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="4952880"/>
+        <a:off x="3571920" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18210,14 +18774,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18225,7 +18789,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="9334440"/>
+        <a:off x="3571920" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18240,13 +18804,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18255,7 +18819,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="13716000"/>
+        <a:off x="3571920" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18305,14 +18869,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18320,7 +18884,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18335,14 +18899,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18350,7 +18914,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18400,14 +18964,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18415,7 +18979,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18430,13 +18994,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18445,7 +19009,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9524880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18460,14 +19024,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18475,7 +19039,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14096880"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18669,7 +19233,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -18713,102 +19277,158 @@
         <v>145.2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>145.2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>49.36</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>93.24</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>119.52</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>119.52</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>117.24</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>159</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>206.64</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>158.64</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>216.84</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D74" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D75" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
@@ -18829,7 +19449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -18887,42 +19507,42 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>12</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>142.75</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>191.67</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>186.44</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>142.75</v>
@@ -18934,83 +19554,139 @@
         <v>186.44</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>186.44</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>12</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>186.44</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>240.14</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>182.53</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>246.96</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>240.14</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B77" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C77" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D74" s="5" t="n">
+      <c r="D77" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D78" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
@@ -19031,7 +19707,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19089,42 +19765,42 @@
         <v>94.81</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>94.81</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>15</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>77.55</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>92.26</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>73.19</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>77.55</v>
@@ -19136,97 +19812,153 @@
         <v>73.19</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>73.19</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>15</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>73.19</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>147.57</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>152.27</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>163.7</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>147.57</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>195.16</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>147.57</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>199.86</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>211.29</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D78" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D79" s="5" t="n">
         <v>195.16</v>
       </c>
     </row>
@@ -19247,7 +19979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19305,42 +20037,42 @@
         <v>86.02</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>121.09</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>86.02</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>19</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>95.79</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>79.6</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>69.52</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>95.79</v>
@@ -19352,97 +20084,153 @@
         <v>69.52</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>69.52</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>19</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>69.52</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>92.59</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>145.65</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>115.11</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>92.59</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>132.4</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>92.59</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>213.4</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>165.4</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D78" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D79" s="5" t="n">
         <v>132.4</v>
       </c>
     </row>
@@ -19463,7 +20251,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19521,42 +20309,42 @@
         <v>93.73</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>93.73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>21</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>73.49</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>106.3</v>
@@ -19568,97 +20356,153 @@
         <v>73.49</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>73.49</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>21</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>73.49</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>109.23</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>167.04</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>128.08</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>109.23</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>148.98</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>109.23</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>233.26</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>177.26</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D78" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D79" s="5" t="n">
         <v>148.98</v>
       </c>
     </row>
@@ -19679,7 +20523,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -19717,84 +20561,128 @@
         <v>174.58</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>174.58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>24</v>
+      <c r="A26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>164.09</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>139.42</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>24</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>139.42</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>234.99</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>183.95</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B74" s="5" t="n">
         <v>303.1</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C75" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
@@ -19815,7 +20703,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -19864,36 +20752,36 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>49.98</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>27</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>120.23</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>39.68</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>120.23</v>
@@ -19902,79 +20790,123 @@
         <v>39.68</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>27</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>68.04</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>206.12</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>68.04</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>94.53</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>68.04</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>286.39</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C79" s="5" t="n">
         <v>94.53</v>
       </c>
     </row>
@@ -19995,7 +20927,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20053,42 +20985,42 @@
         <v>126.12</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>126.12</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>15</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>100.08</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>114.96</v>
@@ -20100,60 +21032,102 @@
         <v>100.08</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>100.08</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>15</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>100.08</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>152.16</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>174.72</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>194.76</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>152.16</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
         <v>31</v>
       </c>
     </row>
@@ -20174,7 +21148,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20232,89 +21206,89 @@
         <v>139.66</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>138.36</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>155.18</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>34</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>145.44</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>118.54</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>145.44</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>118.54</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B30" s="5" t="n">
         <v>130.89</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="5" t="n">
         <v>95.05</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D30" s="5" t="n">
         <v>106.69</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>34</v>
+      <c r="A50" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>216.18</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>176.7</v>
+      <c r="A51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B52" s="5" t="n">
         <v>216.18</v>
@@ -20326,50 +21300,92 @@
         <v>176.7</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>176.7</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>34</v>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>176.7</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>275.68</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>202.39</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>225.85</v>
+      <c r="A74" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>275.68</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>202.39</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>225.85</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B77" s="5" t="n">
         <v>306.32</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C77" s="5" t="n">
         <v>224.88</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D77" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D78" s="5" t="n">
         <v>250.95</v>
       </c>
     </row>

--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -453,28 +453,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$6</c:f>
+              <c:f>Allianz!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$5:$B$6</c:f>
+              <c:f>Allianz!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>53.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>53.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -537,28 +543,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$6</c:f>
+              <c:f>Allianz!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$5:$C$6</c:f>
+              <c:f>Allianz!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>112.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>112.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>112.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -621,28 +633,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$6</c:f>
+              <c:f>Allianz!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$5:$D$6</c:f>
+              <c:f>Allianz!$D$5:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>145.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>145.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>145.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -658,11 +676,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="93605726"/>
-        <c:axId val="70980622"/>
+        <c:axId val="23082319"/>
+        <c:axId val="4146747"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="93605726"/>
+        <c:axId val="23082319"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -728,7 +746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70980622"/>
+        <c:crossAx val="4146747"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -736,7 +754,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70980622"/>
+        <c:axId val="4146747"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -812,7 +830,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93605726"/>
+        <c:crossAx val="23082319"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -913,7 +931,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B28</c:f>
+              <c:f>Generali!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -963,9 +981,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$29:$A$31</c:f>
+              <c:f>Generali!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -974,16 +992,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$29:$B$31</c:f>
+              <c:f>Generali!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>77.55</c:v>
                 </c:pt>
@@ -991,6 +1012,9 @@
                   <c:v>77.55</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>77.55</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>77.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -1003,7 +1027,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C28</c:f>
+              <c:f>Generali!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1053,9 +1077,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$29:$A$31</c:f>
+              <c:f>Generali!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1064,16 +1088,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$29:$C$31</c:f>
+              <c:f>Generali!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>92.26</c:v>
                 </c:pt>
@@ -1081,6 +1108,9 @@
                   <c:v>92.26</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>92.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -1093,7 +1123,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D28</c:f>
+              <c:f>Generali!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1143,9 +1173,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$29:$A$31</c:f>
+              <c:f>Generali!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1154,16 +1184,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$29:$D$31</c:f>
+              <c:f>Generali!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>73.19</c:v>
                 </c:pt>
@@ -1171,6 +1204,9 @@
                   <c:v>73.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>73.19</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>73.19</c:v>
                 </c:pt>
               </c:numCache>
@@ -1186,11 +1222,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96082633"/>
-        <c:axId val="41740890"/>
+        <c:axId val="523889"/>
+        <c:axId val="94057214"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96082633"/>
+        <c:axId val="523889"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1256,7 +1292,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41740890"/>
+        <c:crossAx val="94057214"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1264,7 +1300,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41740890"/>
+        <c:axId val="94057214"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1340,7 +1376,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96082633"/>
+        <c:crossAx val="523889"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1441,7 +1477,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B52</c:f>
+              <c:f>Generali!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1491,9 +1527,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$53:$A$55</c:f>
+              <c:f>Generali!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1502,16 +1538,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$53:$B$55</c:f>
+              <c:f>Generali!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>152.27</c:v>
                 </c:pt>
@@ -1519,6 +1558,9 @@
                   <c:v>152.27</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>152.27</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>152.27</c:v>
                 </c:pt>
               </c:numCache>
@@ -1531,7 +1573,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C52</c:f>
+              <c:f>Generali!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1581,9 +1623,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$53:$A$55</c:f>
+              <c:f>Generali!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1592,16 +1634,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$53:$C$55</c:f>
+              <c:f>Generali!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>163.7</c:v>
                 </c:pt>
@@ -1609,6 +1654,9 @@
                   <c:v>163.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>163.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>163.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1621,7 +1669,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D52</c:f>
+              <c:f>Generali!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1671,9 +1719,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$53:$A$55</c:f>
+              <c:f>Generali!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1682,16 +1730,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$53:$D$55</c:f>
+              <c:f>Generali!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>147.57</c:v>
                 </c:pt>
@@ -1699,6 +1750,9 @@
                   <c:v>147.57</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>147.57</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>147.57</c:v>
                 </c:pt>
               </c:numCache>
@@ -1714,11 +1768,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="6284379"/>
-        <c:axId val="78665736"/>
+        <c:axId val="63323059"/>
+        <c:axId val="26802725"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6284379"/>
+        <c:axId val="63323059"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1784,7 +1838,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78665736"/>
+        <c:crossAx val="26802725"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1792,7 +1846,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78665736"/>
+        <c:axId val="26802725"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1868,7 +1922,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6284379"/>
+        <c:crossAx val="63323059"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1969,7 +2023,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B76</c:f>
+              <c:f>Generali!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2019,9 +2073,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$77:$A$79</c:f>
+              <c:f>Generali!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2030,16 +2084,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$77:$B$79</c:f>
+              <c:f>Generali!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>199.86</c:v>
                 </c:pt>
@@ -2047,6 +2104,9 @@
                   <c:v>199.86</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>199.86</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>199.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2059,7 +2119,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C76</c:f>
+              <c:f>Generali!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2109,9 +2169,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$77:$A$79</c:f>
+              <c:f>Generali!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2120,16 +2180,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$77:$C$79</c:f>
+              <c:f>Generali!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>211.29</c:v>
                 </c:pt>
@@ -2137,6 +2200,9 @@
                   <c:v>211.29</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>211.29</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>211.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -2149,7 +2215,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D76</c:f>
+              <c:f>Generali!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2199,9 +2265,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$77:$A$79</c:f>
+              <c:f>Generali!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2210,16 +2276,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$77:$D$79</c:f>
+              <c:f>Generali!$D$80:$D$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>195.16</c:v>
                 </c:pt>
@@ -2227,6 +2296,9 @@
                   <c:v>195.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>195.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>195.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -2242,11 +2314,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="91770468"/>
-        <c:axId val="1642020"/>
+        <c:axId val="14601181"/>
+        <c:axId val="60417954"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91770468"/>
+        <c:axId val="14601181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2312,7 +2384,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1642020"/>
+        <c:crossAx val="60417954"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2320,7 +2392,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1642020"/>
+        <c:axId val="60417954"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2396,7 +2468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91770468"/>
+        <c:crossAx val="14601181"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2547,9 +2619,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2558,16 +2630,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>121.09</c:v>
                 </c:pt>
@@ -2575,6 +2650,9 @@
                   <c:v>121.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>121.09</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>121.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -2637,9 +2715,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2648,16 +2726,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>98.77</c:v>
                 </c:pt>
@@ -2665,6 +2746,9 @@
                   <c:v>98.77</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>98.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>98.77</c:v>
                 </c:pt>
               </c:numCache>
@@ -2727,9 +2811,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2738,16 +2822,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$7</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>86.02</c:v>
                 </c:pt>
@@ -2755,6 +2842,9 @@
                   <c:v>86.02</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>86.02</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>86.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2770,11 +2860,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53769473"/>
-        <c:axId val="83058260"/>
+        <c:axId val="18049871"/>
+        <c:axId val="89079058"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53769473"/>
+        <c:axId val="18049871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2840,7 +2930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83058260"/>
+        <c:crossAx val="89079058"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2848,7 +2938,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83058260"/>
+        <c:axId val="89079058"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2924,7 +3014,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53769473"/>
+        <c:crossAx val="18049871"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3025,7 +3115,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B28</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3075,9 +3165,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3086,16 +3176,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$29:$B$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>95.79</c:v>
                 </c:pt>
@@ -3103,6 +3196,9 @@
                   <c:v>95.79</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>95.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -3115,7 +3211,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C28</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3165,9 +3261,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3176,16 +3272,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$29:$C$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>79.6</c:v>
                 </c:pt>
@@ -3193,6 +3292,9 @@
                   <c:v>79.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>79.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>79.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3205,7 +3307,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D28</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3255,9 +3357,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$29:$A$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3266,16 +3368,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$29:$D$31</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>69.52</c:v>
                 </c:pt>
@@ -3283,6 +3388,9 @@
                   <c:v>69.52</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>69.52</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>69.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -3298,11 +3406,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54230094"/>
-        <c:axId val="44638701"/>
+        <c:axId val="82009558"/>
+        <c:axId val="96464905"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54230094"/>
+        <c:axId val="82009558"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3368,7 +3476,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44638701"/>
+        <c:crossAx val="96464905"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3376,7 +3484,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44638701"/>
+        <c:axId val="96464905"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3452,7 +3560,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54230094"/>
+        <c:crossAx val="82009558"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3553,7 +3661,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3603,9 +3711,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3614,16 +3722,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$53:$B$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>145.65</c:v>
                 </c:pt>
@@ -3631,6 +3742,9 @@
                   <c:v>145.65</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>145.65</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>145.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -3643,7 +3757,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3693,9 +3807,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3704,16 +3818,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$53:$C$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>115.11</c:v>
                 </c:pt>
@@ -3721,6 +3838,9 @@
                   <c:v>115.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>115.11</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>115.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -3733,7 +3853,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D52</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3783,9 +3903,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$53:$A$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3794,16 +3914,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$53:$D$55</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>92.59</c:v>
                 </c:pt>
@@ -3811,6 +3934,9 @@
                   <c:v>92.59</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>92.59</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>92.59</c:v>
                 </c:pt>
               </c:numCache>
@@ -3826,11 +3952,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="55305049"/>
-        <c:axId val="94694092"/>
+        <c:axId val="27922393"/>
+        <c:axId val="50716858"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="55305049"/>
+        <c:axId val="27922393"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3896,7 +4022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94694092"/>
+        <c:crossAx val="50716858"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3904,7 +4030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94694092"/>
+        <c:axId val="50716858"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3980,7 +4106,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55305049"/>
+        <c:crossAx val="27922393"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4081,7 +4207,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B76</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4131,9 +4257,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4142,16 +4268,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$77:$B$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>213.4</c:v>
                 </c:pt>
@@ -4159,6 +4288,9 @@
                   <c:v>213.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>213.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4171,7 +4303,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C76</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4221,9 +4353,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4232,16 +4364,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$77:$C$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>165.4</c:v>
                 </c:pt>
@@ -4249,6 +4384,9 @@
                   <c:v>165.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>165.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>165.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4261,7 +4399,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D76</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4311,9 +4449,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$77:$A$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4322,16 +4460,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$77:$D$79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$80:$D$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>132.4</c:v>
                 </c:pt>
@@ -4339,6 +4480,9 @@
                   <c:v>132.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>132.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4354,11 +4498,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77515369"/>
-        <c:axId val="62101554"/>
+        <c:axId val="16414795"/>
+        <c:axId val="60859991"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77515369"/>
+        <c:axId val="16414795"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4424,7 +4568,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62101554"/>
+        <c:crossAx val="60859991"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4432,7 +4576,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62101554"/>
+        <c:axId val="60859991"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4508,7 +4652,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77515369"/>
+        <c:crossAx val="16414795"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4659,9 +4803,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4670,16 +4814,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>138.66</c:v>
                 </c:pt>
@@ -4687,6 +4834,9 @@
                   <c:v>138.66</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>138.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>138.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -4749,9 +4899,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4760,16 +4910,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>108.81</c:v>
                 </c:pt>
@@ -4777,6 +4930,9 @@
                   <c:v>108.81</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>108.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>108.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -4839,9 +4995,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4850,16 +5006,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$7</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>93.73</c:v>
                 </c:pt>
@@ -4867,6 +5026,9 @@
                   <c:v>93.73</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>93.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -4882,11 +5044,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="11419182"/>
-        <c:axId val="87243752"/>
+        <c:axId val="66113197"/>
+        <c:axId val="79943059"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11419182"/>
+        <c:axId val="66113197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4952,7 +5114,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87243752"/>
+        <c:crossAx val="79943059"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4960,7 +5122,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87243752"/>
+        <c:axId val="79943059"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5036,7 +5198,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11419182"/>
+        <c:crossAx val="66113197"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5137,7 +5299,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B28</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5187,9 +5349,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5198,16 +5360,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$29:$B$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>106.3</c:v>
                 </c:pt>
@@ -5215,6 +5380,9 @@
                   <c:v>106.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>106.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -5227,7 +5395,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C28</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5277,9 +5445,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5288,16 +5456,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$29:$C$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>84.8</c:v>
                 </c:pt>
@@ -5305,6 +5476,9 @@
                   <c:v>84.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>84.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>84.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -5317,7 +5491,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D28</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5367,9 +5541,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$29:$A$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5378,16 +5552,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$29:$D$31</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>73.49</c:v>
                 </c:pt>
@@ -5395,6 +5572,9 @@
                   <c:v>73.49</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>73.49</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>73.49</c:v>
                 </c:pt>
               </c:numCache>
@@ -5410,11 +5590,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="13199939"/>
-        <c:axId val="24189179"/>
+        <c:axId val="33849121"/>
+        <c:axId val="22197276"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="13199939"/>
+        <c:axId val="33849121"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5480,7 +5660,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24189179"/>
+        <c:crossAx val="22197276"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5488,7 +5668,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24189179"/>
+        <c:axId val="22197276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5564,7 +5744,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13199939"/>
+        <c:crossAx val="33849121"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5665,7 +5845,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5715,9 +5895,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5726,16 +5906,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$53:$B$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>167.04</c:v>
                 </c:pt>
@@ -5743,6 +5926,9 @@
                   <c:v>167.04</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>167.04</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>167.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -5755,7 +5941,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5805,9 +5991,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5816,16 +6002,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$53:$C$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>128.08</c:v>
                 </c:pt>
@@ -5833,6 +6022,9 @@
                   <c:v>128.08</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>128.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>128.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -5845,7 +6037,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D52</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5895,9 +6087,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$53:$A$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5906,16 +6098,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$53:$D$55</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>109.23</c:v>
                 </c:pt>
@@ -5923,6 +6118,9 @@
                   <c:v>109.23</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>109.23</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>109.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -5938,11 +6136,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69807201"/>
-        <c:axId val="86721379"/>
+        <c:axId val="4779098"/>
+        <c:axId val="66346110"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69807201"/>
+        <c:axId val="4779098"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6008,7 +6206,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86721379"/>
+        <c:crossAx val="66346110"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6016,7 +6214,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86721379"/>
+        <c:axId val="66346110"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6092,7 +6290,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69807201"/>
+        <c:crossAx val="4779098"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6193,7 +6391,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B27</c:f>
+              <c:f>Allianz!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6243,28 +6441,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$28:$A$29</c:f>
+              <c:f>Allianz!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$28:$B$29</c:f>
+              <c:f>Allianz!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>49.36</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>49.36</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>49.36</c:v>
                 </c:pt>
               </c:numCache>
@@ -6277,7 +6481,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C27</c:f>
+              <c:f>Allianz!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6327,28 +6531,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$28:$A$29</c:f>
+              <c:f>Allianz!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$28:$C$29</c:f>
+              <c:f>Allianz!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>93.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>93.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>93.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -6361,7 +6571,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D27</c:f>
+              <c:f>Allianz!D28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6411,28 +6621,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$28:$A$29</c:f>
+              <c:f>Allianz!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$28:$D$29</c:f>
+              <c:f>Allianz!$D$29:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>119.52</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>119.52</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>119.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -6448,11 +6664,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="55006156"/>
-        <c:axId val="42752409"/>
+        <c:axId val="26142752"/>
+        <c:axId val="61415878"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="55006156"/>
+        <c:axId val="26142752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6518,7 +6734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42752409"/>
+        <c:crossAx val="61415878"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6526,7 +6742,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42752409"/>
+        <c:axId val="61415878"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6602,7 +6818,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55006156"/>
+        <c:crossAx val="26142752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6703,7 +6919,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B76</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6753,9 +6969,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6764,16 +6980,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$77:$B$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>233.26</c:v>
                 </c:pt>
@@ -6781,6 +7000,9 @@
                   <c:v>233.26</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>233.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>233.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6793,7 +7015,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C76</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6843,9 +7065,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6854,16 +7076,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$77:$C$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>177.26</c:v>
                 </c:pt>
@@ -6871,6 +7096,9 @@
                   <c:v>177.26</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>177.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>177.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -6883,7 +7111,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D76</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6933,9 +7161,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$77:$A$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6944,16 +7172,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$77:$D$79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$80:$D$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>148.98</c:v>
                 </c:pt>
@@ -6961,6 +7192,9 @@
                   <c:v>148.98</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>148.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>148.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -6976,11 +7210,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58259293"/>
-        <c:axId val="81634202"/>
+        <c:axId val="6492239"/>
+        <c:axId val="407309"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58259293"/>
+        <c:axId val="6492239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7046,7 +7280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81634202"/>
+        <c:crossAx val="407309"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7054,7 +7288,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81634202"/>
+        <c:axId val="407309"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7130,7 +7364,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58259293"/>
+        <c:crossAx val="6492239"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7281,28 +7515,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$6</c:f>
+              <c:f>UNIQA!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$5:$B$6</c:f>
+              <c:f>UNIQA!$B$5:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>207.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>207.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>207.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -7365,28 +7605,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$6</c:f>
+              <c:f>UNIQA!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$5:$C$6</c:f>
+              <c:f>UNIQA!$C$5:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>174.58</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>174.58</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>174.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -7402,11 +7648,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="1473529"/>
-        <c:axId val="14869742"/>
+        <c:axId val="86683026"/>
+        <c:axId val="4134480"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1473529"/>
+        <c:axId val="86683026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7472,7 +7718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14869742"/>
+        <c:crossAx val="4134480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7480,7 +7726,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14869742"/>
+        <c:axId val="4134480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7556,7 +7802,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1473529"/>
+        <c:crossAx val="86683026"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7657,7 +7903,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B27</c:f>
+              <c:f>UNIQA!B28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7707,28 +7953,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$28:$A$29</c:f>
+              <c:f>UNIQA!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$28:$B$29</c:f>
+              <c:f>UNIQA!$B$29:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>164.09</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>164.09</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>164.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -7741,7 +7993,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C27</c:f>
+              <c:f>UNIQA!C28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7791,28 +8043,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$28:$A$29</c:f>
+              <c:f>UNIQA!$A$29:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$28:$C$29</c:f>
+              <c:f>UNIQA!$C$29:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>139.42</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>139.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>139.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -7828,11 +8086,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40628064"/>
-        <c:axId val="40932873"/>
+        <c:axId val="89564202"/>
+        <c:axId val="48120734"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40628064"/>
+        <c:axId val="89564202"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7898,7 +8156,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40932873"/>
+        <c:crossAx val="48120734"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7906,7 +8164,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40932873"/>
+        <c:axId val="48120734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7982,7 +8240,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40628064"/>
+        <c:crossAx val="89564202"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8083,7 +8341,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B50</c:f>
+              <c:f>UNIQA!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8133,28 +8391,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$51:$A$52</c:f>
+              <c:f>UNIQA!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$51:$B$52</c:f>
+              <c:f>UNIQA!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>234.99</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>234.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>234.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -8167,7 +8431,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C50</c:f>
+              <c:f>UNIQA!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8217,28 +8481,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$51:$A$52</c:f>
+              <c:f>UNIQA!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$51:$C$52</c:f>
+              <c:f>UNIQA!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>183.95</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>183.95</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>183.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -8254,11 +8524,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="91731846"/>
-        <c:axId val="48549925"/>
+        <c:axId val="75981845"/>
+        <c:axId val="10855855"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91731846"/>
+        <c:axId val="75981845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8324,7 +8594,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48549925"/>
+        <c:crossAx val="10855855"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8332,7 +8602,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48549925"/>
+        <c:axId val="10855855"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8408,7 +8678,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91731846"/>
+        <c:crossAx val="75981845"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8509,7 +8779,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B73</c:f>
+              <c:f>UNIQA!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8559,28 +8829,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$74:$A$75</c:f>
+              <c:f>UNIQA!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$74:$B$75</c:f>
+              <c:f>UNIQA!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>303.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>303.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>303.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8593,7 +8869,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C73</c:f>
+              <c:f>UNIQA!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8643,28 +8919,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$74:$A$75</c:f>
+              <c:f>UNIQA!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$74:$C$75</c:f>
+              <c:f>UNIQA!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>237.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>237.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>237.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -8680,11 +8962,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="28461933"/>
-        <c:axId val="39954223"/>
+        <c:axId val="63493716"/>
+        <c:axId val="23412356"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28461933"/>
+        <c:axId val="63493716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8750,7 +9032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39954223"/>
+        <c:crossAx val="23412356"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8758,7 +9040,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39954223"/>
+        <c:axId val="23412356"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8834,7 +9116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28461933"/>
+        <c:crossAx val="63493716"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8985,9 +9267,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$7</c:f>
+              <c:f>Union!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -8996,16 +9278,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$5:$B$7</c:f>
+              <c:f>Union!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>151.45</c:v>
                 </c:pt>
@@ -9013,6 +9298,9 @@
                   <c:v>151.45</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>151.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>151.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -9075,9 +9363,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$7</c:f>
+              <c:f>Union!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9086,16 +9374,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$5:$C$7</c:f>
+              <c:f>Union!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>49.98</c:v>
                 </c:pt>
@@ -9103,6 +9394,9 @@
                   <c:v>49.98</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>49.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>49.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -9118,11 +9412,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21974709"/>
-        <c:axId val="19117836"/>
+        <c:axId val="40049227"/>
+        <c:axId val="50826481"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21974709"/>
+        <c:axId val="40049227"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9188,7 +9482,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19117836"/>
+        <c:crossAx val="50826481"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9196,7 +9490,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19117836"/>
+        <c:axId val="50826481"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9272,7 +9566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21974709"/>
+        <c:crossAx val="40049227"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9373,7 +9667,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B28</c:f>
+              <c:f>Union!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9423,9 +9717,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$29:$A$31</c:f>
+              <c:f>Union!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9434,16 +9728,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$29:$B$31</c:f>
+              <c:f>Union!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>120.23</c:v>
                 </c:pt>
@@ -9452,6 +9749,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120.23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9463,7 +9763,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C28</c:f>
+              <c:f>Union!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9513,9 +9813,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$29:$A$31</c:f>
+              <c:f>Union!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9524,16 +9824,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$29:$C$31</c:f>
+              <c:f>Union!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>39.68</c:v>
                 </c:pt>
@@ -9541,6 +9844,9 @@
                   <c:v>39.68</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
@@ -9556,11 +9862,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="8853971"/>
-        <c:axId val="1518193"/>
+        <c:axId val="77247242"/>
+        <c:axId val="55003750"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8853971"/>
+        <c:axId val="77247242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9626,7 +9932,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1518193"/>
+        <c:crossAx val="55003750"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9634,7 +9940,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1518193"/>
+        <c:axId val="55003750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9710,7 +10016,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8853971"/>
+        <c:crossAx val="77247242"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9811,7 +10117,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B52</c:f>
+              <c:f>Union!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9861,9 +10167,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$53:$A$55</c:f>
+              <c:f>Union!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9872,16 +10178,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$53:$B$55</c:f>
+              <c:f>Union!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>206.12</c:v>
                 </c:pt>
@@ -9889,6 +10198,9 @@
                   <c:v>206.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>206.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>206.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -9901,7 +10213,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C52</c:f>
+              <c:f>Union!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9951,9 +10263,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$53:$A$55</c:f>
+              <c:f>Union!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9962,16 +10274,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$53:$C$55</c:f>
+              <c:f>Union!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>68.04</c:v>
                 </c:pt>
@@ -9979,6 +10294,9 @@
                   <c:v>68.04</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>68.04</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>68.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -9994,11 +10312,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37124757"/>
-        <c:axId val="95285539"/>
+        <c:axId val="30214398"/>
+        <c:axId val="55481567"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37124757"/>
+        <c:axId val="30214398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10064,7 +10382,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95285539"/>
+        <c:crossAx val="55481567"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10072,7 +10390,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95285539"/>
+        <c:axId val="55481567"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10148,7 +10466,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37124757"/>
+        <c:crossAx val="30214398"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10249,7 +10567,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B76</c:f>
+              <c:f>Union!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10299,9 +10617,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$77:$A$79</c:f>
+              <c:f>Union!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10310,16 +10628,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$77:$B$79</c:f>
+              <c:f>Union!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>286.39</c:v>
                 </c:pt>
@@ -10327,6 +10648,9 @@
                   <c:v>286.39</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>286.39</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>286.39</c:v>
                 </c:pt>
               </c:numCache>
@@ -10339,7 +10663,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C76</c:f>
+              <c:f>Union!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10389,9 +10713,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$77:$A$79</c:f>
+              <c:f>Union!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10400,16 +10724,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$77:$C$79</c:f>
+              <c:f>Union!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>94.53</c:v>
                 </c:pt>
@@ -10417,6 +10744,9 @@
                   <c:v>94.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>94.53</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>94.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -10432,11 +10762,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31512300"/>
-        <c:axId val="64116723"/>
+        <c:axId val="69701317"/>
+        <c:axId val="76378581"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31512300"/>
+        <c:axId val="69701317"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10502,7 +10832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64116723"/>
+        <c:crossAx val="76378581"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10510,7 +10840,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64116723"/>
+        <c:axId val="76378581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10586,7 +10916,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31512300"/>
+        <c:crossAx val="69701317"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10737,9 +11067,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10748,16 +11078,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>144.96</c:v>
                 </c:pt>
@@ -10765,6 +11098,9 @@
                   <c:v>144.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>144.96</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>144.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -10827,9 +11163,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10838,16 +11174,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>167.64</c:v>
                 </c:pt>
@@ -10855,6 +11194,9 @@
                   <c:v>167.64</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>167.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>167.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -10917,9 +11259,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10928,16 +11270,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$7</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>126.12</c:v>
                 </c:pt>
@@ -10945,6 +11290,9 @@
                   <c:v>126.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>126.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>126.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -10960,11 +11308,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90897879"/>
-        <c:axId val="40694075"/>
+        <c:axId val="84466916"/>
+        <c:axId val="30788573"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90897879"/>
+        <c:axId val="84466916"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11030,7 +11378,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40694075"/>
+        <c:crossAx val="30788573"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11038,7 +11386,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40694075"/>
+        <c:axId val="30788573"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11114,7 +11462,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90897879"/>
+        <c:crossAx val="84466916"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11215,7 +11563,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B50</c:f>
+              <c:f>Allianz!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11265,28 +11613,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$51:$A$52</c:f>
+              <c:f>Allianz!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$51:$B$52</c:f>
+              <c:f>Allianz!$B$53:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>117.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>117.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>117.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -11299,7 +11653,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C50</c:f>
+              <c:f>Allianz!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11349,28 +11703,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$51:$A$52</c:f>
+              <c:f>Allianz!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$51:$C$52</c:f>
+              <c:f>Allianz!$C$53:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>159</c:v>
                 </c:pt>
               </c:numCache>
@@ -11383,7 +11743,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D50</c:f>
+              <c:f>Allianz!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11433,28 +11793,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$51:$A$52</c:f>
+              <c:f>Allianz!$A$53:$A$55</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$51:$D$52</c:f>
+              <c:f>Allianz!$D$53:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>206.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>206.64</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>206.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -11470,11 +11836,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="92944617"/>
-        <c:axId val="89740127"/>
+        <c:axId val="68332515"/>
+        <c:axId val="96053618"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="92944617"/>
+        <c:axId val="68332515"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11540,7 +11906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89740127"/>
+        <c:crossAx val="96053618"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11548,7 +11914,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89740127"/>
+        <c:axId val="96053618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11624,7 +11990,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92944617"/>
+        <c:crossAx val="68332515"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11725,7 +12091,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B28</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11775,9 +12141,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11786,16 +12152,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$29:$B$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>114.96</c:v>
                 </c:pt>
@@ -11803,6 +12172,9 @@
                   <c:v>114.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>114.96</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>114.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -11815,7 +12187,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C28</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11865,9 +12237,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11876,16 +12248,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$29:$C$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>132.84</c:v>
                 </c:pt>
@@ -11893,6 +12268,9 @@
                   <c:v>132.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>132.84</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>132.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -11905,7 +12283,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D28</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11955,9 +12333,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$29:$A$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11966,16 +12344,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$29:$D$31</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>100.08</c:v>
                 </c:pt>
@@ -11983,6 +12364,9 @@
                   <c:v>100.08</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>100.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>100.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -11998,11 +12382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83869518"/>
-        <c:axId val="47483447"/>
+        <c:axId val="90499455"/>
+        <c:axId val="92947996"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83869518"/>
+        <c:axId val="90499455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12068,7 +12452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47483447"/>
+        <c:crossAx val="92947996"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12076,7 +12460,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47483447"/>
+        <c:axId val="92947996"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12152,7 +12536,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83869518"/>
+        <c:crossAx val="90499455"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12253,7 +12637,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12303,9 +12687,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12314,16 +12698,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$53:$B$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>174.72</c:v>
                 </c:pt>
@@ -12331,6 +12718,9 @@
                   <c:v>174.72</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>174.72</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>174.72</c:v>
                 </c:pt>
               </c:numCache>
@@ -12343,7 +12733,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12393,9 +12783,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12404,16 +12794,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$53:$C$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>194.76</c:v>
                 </c:pt>
@@ -12421,6 +12814,9 @@
                   <c:v>194.76</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>194.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>194.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -12433,7 +12829,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D52</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12483,9 +12879,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$53:$A$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12494,16 +12890,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$53:$D$55</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>152.16</c:v>
                 </c:pt>
@@ -12511,6 +12910,9 @@
                   <c:v>152.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>152.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>152.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -12526,11 +12928,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="12030464"/>
-        <c:axId val="37849185"/>
+        <c:axId val="36458283"/>
+        <c:axId val="20797784"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12030464"/>
+        <c:axId val="36458283"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12596,7 +12998,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37849185"/>
+        <c:crossAx val="20797784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12604,7 +13006,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37849185"/>
+        <c:axId val="20797784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12680,7 +13082,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12030464"/>
+        <c:crossAx val="36458283"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12831,9 +13233,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12842,16 +13244,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$5:$B$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>190.22</c:v>
                 </c:pt>
@@ -12860,6 +13265,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>190.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>171.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12921,9 +13329,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12932,16 +13340,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$5:$C$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>138.36</c:v>
                 </c:pt>
@@ -12950,6 +13361,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>138.36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>124.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13011,9 +13425,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13022,16 +13436,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$5:$D$7</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>155.18</c:v>
                 </c:pt>
@@ -13040,6 +13457,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>155.18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>139.66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13054,11 +13474,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="8462167"/>
-        <c:axId val="46228431"/>
+        <c:axId val="77359126"/>
+        <c:axId val="66860533"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8462167"/>
+        <c:axId val="77359126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13124,7 +13544,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46228431"/>
+        <c:crossAx val="66860533"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13132,7 +13552,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46228431"/>
+        <c:axId val="66860533"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13208,7 +13628,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8462167"/>
+        <c:crossAx val="77359126"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13309,7 +13729,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B28</c:f>
+              <c:f>'ČSOB Poisťovňa'!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13359,7 +13779,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13373,7 +13793,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$29:$B$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$30:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13393,7 +13813,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C28</c:f>
+              <c:f>'ČSOB Poisťovňa'!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13443,7 +13863,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13457,7 +13877,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$29:$C$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$30:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13477,7 +13897,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D28</c:f>
+              <c:f>'ČSOB Poisťovňa'!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13527,7 +13947,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$29:$A$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13541,7 +13961,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$29:$D$30</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$30:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13564,11 +13984,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98214665"/>
-        <c:axId val="88490572"/>
+        <c:axId val="7569708"/>
+        <c:axId val="4333849"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98214665"/>
+        <c:axId val="7569708"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13634,7 +14054,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88490572"/>
+        <c:crossAx val="4333849"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13642,7 +14062,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88490572"/>
+        <c:axId val="4333849"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13718,7 +14138,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98214665"/>
+        <c:crossAx val="7569708"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13819,7 +14239,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B51</c:f>
+              <c:f>'ČSOB Poisťovňa'!B52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13869,9 +14289,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13880,16 +14300,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$52:$B$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$53:$B$56</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>216.18</c:v>
                 </c:pt>
@@ -13897,6 +14320,9 @@
                   <c:v>216.18</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>216.18</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>216.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -13909,7 +14335,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C51</c:f>
+              <c:f>'ČSOB Poisťovňa'!C52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13959,9 +14385,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13970,16 +14396,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$52:$C$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$53:$C$56</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>157.93</c:v>
                 </c:pt>
@@ -13987,6 +14416,9 @@
                   <c:v>157.93</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>157.93</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>157.93</c:v>
                 </c:pt>
               </c:numCache>
@@ -13999,7 +14431,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D51</c:f>
+              <c:f>'ČSOB Poisťovňa'!D52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14049,9 +14481,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$52:$A$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14060,16 +14492,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$52:$D$54</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$53:$D$56</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>176.7</c:v>
                 </c:pt>
@@ -14077,6 +14512,9 @@
                   <c:v>176.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>176.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>176.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -14092,11 +14530,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60081601"/>
-        <c:axId val="23674917"/>
+        <c:axId val="43865406"/>
+        <c:axId val="89412078"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60081601"/>
+        <c:axId val="43865406"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14162,7 +14600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23674917"/>
+        <c:crossAx val="89412078"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14170,7 +14608,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23674917"/>
+        <c:axId val="89412078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14246,7 +14684,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60081601"/>
+        <c:crossAx val="43865406"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14347,7 +14785,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B75</c:f>
+              <c:f>'ČSOB Poisťovňa'!B77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14397,9 +14835,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14408,16 +14846,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$76:$B$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$78:$B$81</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>275.68</c:v>
                 </c:pt>
@@ -14425,6 +14866,9 @@
                   <c:v>306.32</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>306.32</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>306.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -14437,7 +14881,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C75</c:f>
+              <c:f>'ČSOB Poisťovňa'!C77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14487,9 +14931,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14498,16 +14942,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$76:$C$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$78:$C$81</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>202.39</c:v>
                 </c:pt>
@@ -14515,6 +14962,9 @@
                   <c:v>224.88</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>224.88</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>224.88</c:v>
                 </c:pt>
               </c:numCache>
@@ -14527,7 +14977,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D75</c:f>
+              <c:f>'ČSOB Poisťovňa'!D77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14577,9 +15027,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$76:$A$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14588,16 +15038,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$76:$D$78</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$78:$D$81</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>225.85</c:v>
                 </c:pt>
@@ -14605,6 +15058,9 @@
                   <c:v>250.95</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>250.95</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>250.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -14620,11 +15076,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="19229011"/>
-        <c:axId val="30599641"/>
+        <c:axId val="78723410"/>
+        <c:axId val="11767295"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="19229011"/>
+        <c:axId val="78723410"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14690,7 +15146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30599641"/>
+        <c:crossAx val="11767295"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14698,7 +15154,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30599641"/>
+        <c:axId val="11767295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14774,7 +15230,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19229011"/>
+        <c:crossAx val="78723410"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14875,7 +15331,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B73</c:f>
+              <c:f>Allianz!B76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14925,28 +15381,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$74:$A$75</c:f>
+              <c:f>Allianz!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$74:$B$75</c:f>
+              <c:f>Allianz!$B$77:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>158.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>158.64</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>158.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -14959,7 +15421,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C73</c:f>
+              <c:f>Allianz!C76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15009,28 +15471,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$74:$A$75</c:f>
+              <c:f>Allianz!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$74:$C$75</c:f>
+              <c:f>Allianz!$C$77:$C$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>216.84</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>216.84</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>216.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -15043,7 +15511,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D73</c:f>
+              <c:f>Allianz!D76</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15093,28 +15561,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$74:$A$75</c:f>
+              <c:f>Allianz!$A$77:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$74:$D$75</c:f>
+              <c:f>Allianz!$D$77:$D$79</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>277.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>277.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>277.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -15130,11 +15604,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24402108"/>
-        <c:axId val="71741683"/>
+        <c:axId val="37166430"/>
+        <c:axId val="20443800"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24402108"/>
+        <c:axId val="37166430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15200,7 +15674,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71741683"/>
+        <c:crossAx val="20443800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15208,7 +15682,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71741683"/>
+        <c:axId val="20443800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15284,7 +15758,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24402108"/>
+        <c:crossAx val="37166430"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15435,9 +15909,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$7</c:f>
+              <c:f>Colonnade!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15446,16 +15920,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$5:$B$7</c:f>
+              <c:f>Colonnade!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>151.84</c:v>
                 </c:pt>
@@ -15463,6 +15940,9 @@
                   <c:v>182.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -15525,9 +16005,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$7</c:f>
+              <c:f>Colonnade!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15536,16 +16016,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$5:$C$7</c:f>
+              <c:f>Colonnade!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>207.85</c:v>
                 </c:pt>
@@ -15553,6 +16036,9 @@
                   <c:v>246.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -15615,9 +16101,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$7</c:f>
+              <c:f>Colonnade!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15626,16 +16112,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$5:$D$7</c:f>
+              <c:f>Colonnade!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>201.92</c:v>
                 </c:pt>
@@ -15643,6 +16132,9 @@
                   <c:v>240.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -15658,11 +16150,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="9645608"/>
-        <c:axId val="73666824"/>
+        <c:axId val="47253965"/>
+        <c:axId val="84779179"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9645608"/>
+        <c:axId val="47253965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15728,7 +16220,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73666824"/>
+        <c:crossAx val="84779179"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15736,7 +16228,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73666824"/>
+        <c:axId val="84779179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15812,7 +16304,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9645608"/>
+        <c:crossAx val="47253965"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15913,7 +16405,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B28</c:f>
+              <c:f>Colonnade!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15963,9 +16455,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$29:$A$31</c:f>
+              <c:f>Colonnade!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15974,16 +16466,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$29:$B$31</c:f>
+              <c:f>Colonnade!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>142.75</c:v>
                 </c:pt>
@@ -15991,6 +16486,9 @@
                   <c:v>142.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>142.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>142.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -16003,7 +16501,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C28</c:f>
+              <c:f>Colonnade!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16053,9 +16551,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$29:$A$31</c:f>
+              <c:f>Colonnade!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16064,16 +16562,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$29:$C$31</c:f>
+              <c:f>Colonnade!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>191.67</c:v>
                 </c:pt>
@@ -16081,6 +16582,9 @@
                   <c:v>191.67</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>191.67</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>191.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -16093,7 +16597,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D28</c:f>
+              <c:f>Colonnade!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16143,9 +16647,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$29:$A$31</c:f>
+              <c:f>Colonnade!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16154,16 +16658,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$29:$D$31</c:f>
+              <c:f>Colonnade!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>186.44</c:v>
                 </c:pt>
@@ -16171,6 +16678,9 @@
                   <c:v>186.44</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>186.44</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>186.44</c:v>
                 </c:pt>
               </c:numCache>
@@ -16186,11 +16696,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4284085"/>
-        <c:axId val="33837936"/>
+        <c:axId val="48729051"/>
+        <c:axId val="51468622"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4284085"/>
+        <c:axId val="48729051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16256,7 +16766,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33837936"/>
+        <c:crossAx val="51468622"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16264,7 +16774,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33837936"/>
+        <c:axId val="51468622"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16340,7 +16850,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4284085"/>
+        <c:crossAx val="48729051"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16441,7 +16951,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B52</c:f>
+              <c:f>Colonnade!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16491,9 +17001,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$53:$A$55</c:f>
+              <c:f>Colonnade!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16502,16 +17012,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$53:$B$55</c:f>
+              <c:f>Colonnade!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>182.53</c:v>
                 </c:pt>
@@ -16519,6 +17032,9 @@
                   <c:v>182.53</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -16531,7 +17047,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C52</c:f>
+              <c:f>Colonnade!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16581,9 +17097,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$53:$A$55</c:f>
+              <c:f>Colonnade!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16592,16 +17108,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$53:$C$55</c:f>
+              <c:f>Colonnade!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>246.96</c:v>
                 </c:pt>
@@ -16609,6 +17128,9 @@
                   <c:v>246.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -16621,7 +17143,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D52</c:f>
+              <c:f>Colonnade!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16671,9 +17193,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$53:$A$55</c:f>
+              <c:f>Colonnade!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16682,16 +17204,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$53:$D$55</c:f>
+              <c:f>Colonnade!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>240.14</c:v>
                 </c:pt>
@@ -16699,6 +17224,9 @@
                   <c:v>240.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -16714,11 +17242,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43876004"/>
-        <c:axId val="62408275"/>
+        <c:axId val="29093845"/>
+        <c:axId val="96675431"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43876004"/>
+        <c:axId val="29093845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16784,7 +17312,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62408275"/>
+        <c:crossAx val="96675431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16792,7 +17320,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62408275"/>
+        <c:axId val="96675431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16868,7 +17396,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43876004"/>
+        <c:crossAx val="29093845"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16969,7 +17497,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B76</c:f>
+              <c:f>Colonnade!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17019,28 +17547,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$77:$A$78</c:f>
+              <c:f>Colonnade!$A$80:$A$82</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$77:$B$78</c:f>
+              <c:f>Colonnade!$B$80:$B$82</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>254.31</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>254.31</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>254.31</c:v>
                 </c:pt>
               </c:numCache>
@@ -17053,7 +17587,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C76</c:f>
+              <c:f>Colonnade!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17103,28 +17637,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$77:$A$78</c:f>
+              <c:f>Colonnade!$A$80:$A$82</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$77:$C$78</c:f>
+              <c:f>Colonnade!$C$80:$C$82</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>347.42</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>347.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>347.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -17137,7 +17677,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D76</c:f>
+              <c:f>Colonnade!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17187,28 +17727,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$77:$A$78</c:f>
+              <c:f>Colonnade!$A$80:$A$82</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$77:$D$78</c:f>
+              <c:f>Colonnade!$D$80:$D$82</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>337.73</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>337.73</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>337.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -17224,11 +17770,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74191444"/>
-        <c:axId val="39705626"/>
+        <c:axId val="65841303"/>
+        <c:axId val="16364111"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74191444"/>
+        <c:axId val="65841303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17294,7 +17840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39705626"/>
+        <c:crossAx val="16364111"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17302,7 +17848,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39705626"/>
+        <c:axId val="16364111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17378,7 +17924,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74191444"/>
+        <c:crossAx val="65841303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17529,9 +18075,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$7</c:f>
+              <c:f>Generali!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17540,16 +18086,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$5:$B$7</c:f>
+              <c:f>Generali!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>99.41</c:v>
                 </c:pt>
@@ -17557,6 +18106,9 @@
                   <c:v>99.41</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>99.41</c:v>
                 </c:pt>
               </c:numCache>
@@ -17619,9 +18171,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$7</c:f>
+              <c:f>Generali!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17630,16 +18182,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$5:$C$7</c:f>
+              <c:f>Generali!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>114.74</c:v>
                 </c:pt>
@@ -17647,6 +18202,9 @@
                   <c:v>114.74</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>114.74</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>114.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -17709,9 +18267,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$7</c:f>
+              <c:f>Generali!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17720,16 +18278,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$5:$D$7</c:f>
+              <c:f>Generali!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>94.81</c:v>
                 </c:pt>
@@ -17737,6 +18298,9 @@
                   <c:v>94.81</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>94.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>94.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -17752,11 +18316,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="12369964"/>
-        <c:axId val="29715744"/>
+        <c:axId val="28902023"/>
+        <c:axId val="41839186"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12369964"/>
+        <c:axId val="28902023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17822,7 +18386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29715744"/>
+        <c:crossAx val="41839186"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17830,7 +18394,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29715744"/>
+        <c:axId val="41839186"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17906,7 +18470,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12369964"/>
+        <c:crossAx val="28902023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17994,14 +18558,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18009,7 +18573,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="4952880"/>
+        <a:off x="4558680" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18024,14 +18588,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18039,7 +18603,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9334440"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18054,13 +18618,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18069,7 +18633,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="13716000"/>
+        <a:off x="4558680" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18119,13 +18683,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18134,7 +18698,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18149,13 +18713,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18164,7 +18728,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18179,13 +18743,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18194,7 +18758,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14287680"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18244,13 +18808,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18259,7 +18823,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18274,13 +18838,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18289,7 +18853,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18304,13 +18868,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18319,7 +18883,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14287680"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18369,13 +18933,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18384,7 +18948,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18399,13 +18963,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18414,7 +18978,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18429,13 +18993,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18444,7 +19008,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14287680"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18494,13 +19058,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18509,7 +19073,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18524,13 +19088,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18539,7 +19103,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18554,13 +19118,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18569,7 +19133,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14287680"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18619,14 +19183,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18634,7 +19198,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="4952880"/>
+        <a:off x="3571920" y="5143680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18649,14 +19213,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18664,7 +19228,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="9334440"/>
+        <a:off x="3571920" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18679,13 +19243,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18694,7 +19258,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="13716000"/>
+        <a:off x="3571920" y="14287680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18744,13 +19308,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18759,7 +19323,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="5143680"/>
+        <a:off x="3571920" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18774,13 +19338,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18789,7 +19353,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="9715680"/>
+        <a:off x="3571920" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18804,13 +19368,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18819,7 +19383,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="14287680"/>
+        <a:off x="3571920" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18869,13 +19433,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18884,7 +19448,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18899,13 +19463,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18914,7 +19478,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18964,13 +19528,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18979,7 +19543,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18994,14 +19558,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -19009,7 +19573,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9524880"/>
+        <a:off x="4558680" y="9715680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19024,14 +19588,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -19039,7 +19603,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14096880"/>
+        <a:off x="4558680" y="14478120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19233,7 +19797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19291,42 +19855,42 @@
         <v>145.2</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>145.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>93.24</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>119.52</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>49.36</v>
@@ -19338,97 +19902,153 @@
         <v>119.52</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>119.52</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>5</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>119.52</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>117.24</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>206.64</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>117.24</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>159</v>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>206.64</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>158.64</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>216.84</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>277.2</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>206.64</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>158.64</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>216.84</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D78" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D79" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
@@ -19449,7 +20069,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19521,42 +20141,42 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>12</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>142.75</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>191.67</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>186.44</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>142.75</v>
@@ -19570,7 +20190,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>142.75</v>
@@ -19582,56 +20202,56 @@
         <v>186.44</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>186.44</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>12</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>186.44</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>240.14</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>240.14</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>182.53</v>
@@ -19643,50 +20263,106 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>8</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>12</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>254.31</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>347.42</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>337.73</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>240.14</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B81" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D81" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D82" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
@@ -19707,7 +20383,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19779,42 +20455,42 @@
         <v>94.81</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>94.81</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>15</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>77.55</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>92.26</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>73.19</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>77.55</v>
@@ -19828,7 +20504,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>77.55</v>
@@ -19840,56 +20516,56 @@
         <v>73.19</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>73.19</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>15</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>73.19</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>147.57</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>147.57</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>152.27</v>
@@ -19901,64 +20577,120 @@
         <v>147.57</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>8</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>147.57</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>15</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>147.57</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>195.16</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>147.57</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>195.16</v>
+      <c r="A78" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>199.86</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>211.29</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D82" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D83" s="5" t="n">
         <v>195.16</v>
       </c>
     </row>
@@ -19979,7 +20711,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20051,42 +20783,42 @@
         <v>86.02</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>121.09</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>86.02</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>19</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>95.79</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>79.6</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>69.52</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>95.79</v>
@@ -20100,7 +20832,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>95.79</v>
@@ -20112,56 +20844,56 @@
         <v>69.52</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>69.52</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>19</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>69.52</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>92.59</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>92.59</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>145.65</v>
@@ -20173,64 +20905,120 @@
         <v>92.59</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>8</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>92.59</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>19</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>92.59</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>132.4</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>92.59</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>132.4</v>
+      <c r="A78" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>213.4</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>165.4</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D82" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D83" s="5" t="n">
         <v>132.4</v>
       </c>
     </row>
@@ -20251,7 +21039,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20323,42 +21111,42 @@
         <v>93.73</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>93.73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>21</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>73.49</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>106.3</v>
@@ -20372,7 +21160,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>106.3</v>
@@ -20384,56 +21172,56 @@
         <v>73.49</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>73.49</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>21</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>73.49</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>109.23</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>109.23</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>167.04</v>
@@ -20445,64 +21233,120 @@
         <v>109.23</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>8</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>109.23</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>21</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>109.23</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>148.98</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>109.23</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>148.98</v>
+      <c r="A78" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>233.26</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>177.26</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D82" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D83" s="5" t="n">
         <v>148.98</v>
       </c>
     </row>
@@ -20523,7 +21367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -20572,36 +21416,36 @@
         <v>174.58</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>174.58</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>24</v>
+      <c r="A27" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>164.09</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>139.42</v>
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>164.09</v>
@@ -20610,79 +21454,123 @@
         <v>139.42</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>7</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>139.42</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>24</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>139.42</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>234.99</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>183.95</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>234.99</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>183.95</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>303.1</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>237.81</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>183.95</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>303.1</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C79" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
@@ -20703,7 +21591,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -20763,36 +21651,36 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>49.98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>27</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>120.23</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>39.68</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>120.23</v>
@@ -20803,56 +21691,56 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>39.68</v>
+        <v>120.23</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>39.68</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>27</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>39.68</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>68.04</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>68.04</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>206.12</v>
@@ -20861,52 +21749,96 @@
         <v>68.04</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>8</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>68.04</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>27</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>68.04</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>94.53</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>68.04</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>94.53</v>
+      <c r="A78" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>286.39</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C83" s="5" t="n">
         <v>94.53</v>
       </c>
     </row>
@@ -20927,7 +21859,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20999,42 +21931,42 @@
         <v>126.12</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>126.12</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>15</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>100.08</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>114.96</v>
@@ -21048,7 +21980,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>114.96</v>
@@ -21060,56 +21992,56 @@
         <v>100.08</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>7</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>100.08</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>15</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>100.08</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>152.16</v>
+      <c r="A53" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>152.16</v>
+      <c r="A54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>174.72</v>
@@ -21121,13 +22053,55 @@
         <v>152.16</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
         <v>31</v>
       </c>
     </row>
@@ -21148,7 +22122,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -21220,89 +22194,89 @@
         <v>155.18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>124.53</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>139.66</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>34</v>
+      <c r="A28" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>145.44</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>118.54</v>
+      <c r="A29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>145.44</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>118.54</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B31" s="5" t="n">
         <v>130.89</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C31" s="5" t="n">
         <v>95.05</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D31" s="5" t="n">
         <v>106.69</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>34</v>
+      <c r="A51" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>216.18</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>176.7</v>
+      <c r="A52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>216.18</v>
@@ -21316,7 +22290,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>216.18</v>
@@ -21328,64 +22302,106 @@
         <v>176.7</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>8</v>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>176.7</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>34</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>176.7</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>275.68</v>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>202.39</v>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>225.85</v>
+      <c r="A76" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>306.32</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>224.88</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>250.95</v>
+      <c r="A77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>275.68</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>202.39</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>225.85</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B80" s="5" t="n">
         <v>306.32</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C80" s="5" t="n">
         <v>224.88</v>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D80" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D81" s="5" t="n">
         <v>250.95</v>
       </c>
     </row>

--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -453,9 +453,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$7</c:f>
+              <c:f>Allianz!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -464,16 +464,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$5:$B$7</c:f>
+              <c:f>Allianz!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>53.8</c:v>
                 </c:pt>
@@ -481,6 +484,9 @@
                   <c:v>53.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>53.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -543,9 +549,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$7</c:f>
+              <c:f>Allianz!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -554,16 +560,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$5:$C$7</c:f>
+              <c:f>Allianz!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>112.32</c:v>
                 </c:pt>
@@ -571,6 +580,9 @@
                   <c:v>112.32</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>112.32</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>112.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -633,9 +645,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$7</c:f>
+              <c:f>Allianz!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -644,16 +656,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$5:$D$7</c:f>
+              <c:f>Allianz!$D$5:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>145.2</c:v>
                 </c:pt>
@@ -661,6 +676,9 @@
                   <c:v>145.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>145.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>145.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -676,11 +694,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23082319"/>
-        <c:axId val="4146747"/>
+        <c:axId val="64081150"/>
+        <c:axId val="49899346"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="23082319"/>
+        <c:axId val="64081150"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -746,7 +764,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4146747"/>
+        <c:crossAx val="49899346"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -754,7 +772,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4146747"/>
+        <c:axId val="49899346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -830,7 +848,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23082319"/>
+        <c:crossAx val="64081150"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -931,7 +949,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B29</c:f>
+              <c:f>Generali!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -981,9 +999,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$30:$A$33</c:f>
+              <c:f>Generali!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -995,16 +1013,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$30:$B$33</c:f>
+              <c:f>Generali!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>77.55</c:v>
                 </c:pt>
@@ -1015,6 +1036,9 @@
                   <c:v>77.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>77.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>77.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -1027,7 +1051,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C29</c:f>
+              <c:f>Generali!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1077,9 +1101,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$30:$A$33</c:f>
+              <c:f>Generali!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1091,16 +1115,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$30:$C$33</c:f>
+              <c:f>Generali!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>92.26</c:v>
                 </c:pt>
@@ -1111,6 +1138,9 @@
                   <c:v>92.26</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>92.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -1123,7 +1153,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D29</c:f>
+              <c:f>Generali!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1173,9 +1203,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$30:$A$33</c:f>
+              <c:f>Generali!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1187,16 +1217,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$30:$D$33</c:f>
+              <c:f>Generali!$D$31:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>73.19</c:v>
                 </c:pt>
@@ -1207,6 +1240,9 @@
                   <c:v>73.19</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>73.19</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>73.19</c:v>
                 </c:pt>
               </c:numCache>
@@ -1222,11 +1258,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="523889"/>
-        <c:axId val="94057214"/>
+        <c:axId val="38558382"/>
+        <c:axId val="95306167"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="523889"/>
+        <c:axId val="38558382"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1292,7 +1328,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94057214"/>
+        <c:crossAx val="95306167"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1300,7 +1336,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94057214"/>
+        <c:axId val="95306167"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1376,7 +1412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523889"/>
+        <c:crossAx val="38558382"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1477,7 +1513,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B54</c:f>
+              <c:f>Generali!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1527,9 +1563,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$55:$A$58</c:f>
+              <c:f>Generali!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1541,16 +1577,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$55:$B$58</c:f>
+              <c:f>Generali!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>152.27</c:v>
                 </c:pt>
@@ -1561,6 +1600,9 @@
                   <c:v>152.27</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>152.27</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>152.27</c:v>
                 </c:pt>
               </c:numCache>
@@ -1573,7 +1615,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C54</c:f>
+              <c:f>Generali!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1623,9 +1665,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$55:$A$58</c:f>
+              <c:f>Generali!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1637,16 +1679,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$55:$C$58</c:f>
+              <c:f>Generali!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>163.7</c:v>
                 </c:pt>
@@ -1657,6 +1702,9 @@
                   <c:v>163.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>163.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>163.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1669,7 +1717,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D54</c:f>
+              <c:f>Generali!D56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1719,9 +1767,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$55:$A$58</c:f>
+              <c:f>Generali!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1733,16 +1781,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$55:$D$58</c:f>
+              <c:f>Generali!$D$57:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>147.57</c:v>
                 </c:pt>
@@ -1753,6 +1804,9 @@
                   <c:v>147.57</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>147.57</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>147.57</c:v>
                 </c:pt>
               </c:numCache>
@@ -1768,11 +1822,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="63323059"/>
-        <c:axId val="26802725"/>
+        <c:axId val="42361312"/>
+        <c:axId val="12590956"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63323059"/>
+        <c:axId val="42361312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1838,7 +1892,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26802725"/>
+        <c:crossAx val="12590956"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1846,7 +1900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26802725"/>
+        <c:axId val="12590956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1922,7 +1976,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63323059"/>
+        <c:crossAx val="42361312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2023,7 +2077,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B79</c:f>
+              <c:f>Generali!B82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2073,9 +2127,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$80:$A$83</c:f>
+              <c:f>Generali!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2087,16 +2141,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$80:$B$83</c:f>
+              <c:f>Generali!$B$83:$B$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>199.86</c:v>
                 </c:pt>
@@ -2107,6 +2164,9 @@
                   <c:v>199.86</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>199.86</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>199.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2119,7 +2179,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C79</c:f>
+              <c:f>Generali!C82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2169,9 +2229,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$80:$A$83</c:f>
+              <c:f>Generali!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2183,16 +2243,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$80:$C$83</c:f>
+              <c:f>Generali!$C$83:$C$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>211.29</c:v>
                 </c:pt>
@@ -2203,6 +2266,9 @@
                   <c:v>211.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>211.29</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>211.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -2215,7 +2281,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D79</c:f>
+              <c:f>Generali!D82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2265,9 +2331,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$80:$A$83</c:f>
+              <c:f>Generali!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2279,16 +2345,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$80:$D$83</c:f>
+              <c:f>Generali!$D$83:$D$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>195.16</c:v>
                 </c:pt>
@@ -2299,6 +2368,9 @@
                   <c:v>195.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>195.16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>195.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -2314,11 +2386,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="14601181"/>
-        <c:axId val="60417954"/>
+        <c:axId val="21346246"/>
+        <c:axId val="6603783"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="14601181"/>
+        <c:axId val="21346246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2384,7 +2456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60417954"/>
+        <c:crossAx val="6603783"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2392,7 +2464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60417954"/>
+        <c:axId val="6603783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2468,7 +2540,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14601181"/>
+        <c:crossAx val="21346246"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2619,9 +2691,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2633,16 +2705,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>121.09</c:v>
                 </c:pt>
@@ -2653,6 +2728,9 @@
                   <c:v>121.09</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>121.09</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>121.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -2715,9 +2793,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2729,16 +2807,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>98.77</c:v>
                 </c:pt>
@@ -2749,6 +2830,9 @@
                   <c:v>98.77</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>98.77</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>98.77</c:v>
                 </c:pt>
               </c:numCache>
@@ -2811,9 +2895,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2825,16 +2909,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$8</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>86.02</c:v>
                 </c:pt>
@@ -2845,6 +2932,9 @@
                   <c:v>86.02</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>86.02</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>86.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -2860,11 +2950,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18049871"/>
-        <c:axId val="89079058"/>
+        <c:axId val="56578209"/>
+        <c:axId val="53682205"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18049871"/>
+        <c:axId val="56578209"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2930,7 +3020,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89079058"/>
+        <c:crossAx val="53682205"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2938,7 +3028,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89079058"/>
+        <c:axId val="53682205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3014,7 +3104,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18049871"/>
+        <c:crossAx val="56578209"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3115,7 +3205,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3165,9 +3255,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3179,16 +3269,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$30:$B$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>95.79</c:v>
                 </c:pt>
@@ -3199,6 +3292,9 @@
                   <c:v>95.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>95.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -3211,7 +3307,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3261,9 +3357,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3275,16 +3371,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$30:$C$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>79.6</c:v>
                 </c:pt>
@@ -3295,6 +3394,9 @@
                   <c:v>79.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>79.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>79.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3307,7 +3409,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D29</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3357,9 +3459,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$30:$A$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3371,16 +3473,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$30:$D$33</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$31:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>69.52</c:v>
                 </c:pt>
@@ -3391,6 +3496,9 @@
                   <c:v>69.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>69.52</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>69.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -3406,11 +3514,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82009558"/>
-        <c:axId val="96464905"/>
+        <c:axId val="96467811"/>
+        <c:axId val="86593568"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82009558"/>
+        <c:axId val="96467811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3476,7 +3584,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96464905"/>
+        <c:crossAx val="86593568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3484,7 +3592,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96464905"/>
+        <c:axId val="86593568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3560,7 +3668,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82009558"/>
+        <c:crossAx val="96467811"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3661,7 +3769,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B54</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3711,9 +3819,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3725,16 +3833,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$55:$B$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>145.65</c:v>
                 </c:pt>
@@ -3745,6 +3856,9 @@
                   <c:v>145.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>145.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>145.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -3757,7 +3871,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C54</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3807,9 +3921,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3821,16 +3935,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$55:$C$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>115.11</c:v>
                 </c:pt>
@@ -3841,6 +3958,9 @@
                   <c:v>115.11</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>115.11</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>115.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -3853,7 +3973,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D54</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3903,9 +4023,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$55:$A$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3917,16 +4037,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$55:$D$58</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$57:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>92.59</c:v>
                 </c:pt>
@@ -3937,6 +4060,9 @@
                   <c:v>92.59</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>92.59</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>92.59</c:v>
                 </c:pt>
               </c:numCache>
@@ -3952,11 +4078,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="27922393"/>
-        <c:axId val="50716858"/>
+        <c:axId val="89477049"/>
+        <c:axId val="72341184"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27922393"/>
+        <c:axId val="89477049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4022,7 +4148,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50716858"/>
+        <c:crossAx val="72341184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4030,7 +4156,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50716858"/>
+        <c:axId val="72341184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4106,7 +4232,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27922393"/>
+        <c:crossAx val="89477049"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4207,7 +4333,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4257,9 +4383,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4271,16 +4397,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$80:$B$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$83:$B$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>213.4</c:v>
                 </c:pt>
@@ -4291,6 +4420,9 @@
                   <c:v>213.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>213.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4303,7 +4435,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4353,9 +4485,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4367,16 +4499,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$80:$C$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$83:$C$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>165.4</c:v>
                 </c:pt>
@@ -4387,6 +4522,9 @@
                   <c:v>165.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>165.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>165.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4399,7 +4537,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D79</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4449,9 +4587,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$80:$A$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4463,16 +4601,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$80:$D$83</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$83:$D$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>132.4</c:v>
                 </c:pt>
@@ -4483,6 +4624,9 @@
                   <c:v>132.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>132.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4498,11 +4642,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16414795"/>
-        <c:axId val="60859991"/>
+        <c:axId val="43473221"/>
+        <c:axId val="87634197"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16414795"/>
+        <c:axId val="43473221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4568,7 +4712,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60859991"/>
+        <c:crossAx val="87634197"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4576,7 +4720,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60859991"/>
+        <c:axId val="87634197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4652,7 +4796,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16414795"/>
+        <c:crossAx val="43473221"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4803,9 +4947,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4817,16 +4961,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>138.66</c:v>
                 </c:pt>
@@ -4837,6 +4984,9 @@
                   <c:v>138.66</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>138.66</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>138.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -4899,9 +5049,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4913,16 +5063,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>108.81</c:v>
                 </c:pt>
@@ -4933,6 +5086,9 @@
                   <c:v>108.81</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>108.81</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>108.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -4995,9 +5151,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5009,16 +5165,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$8</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>93.73</c:v>
                 </c:pt>
@@ -5029,6 +5188,9 @@
                   <c:v>93.73</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>93.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -5044,11 +5206,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66113197"/>
-        <c:axId val="79943059"/>
+        <c:axId val="78949017"/>
+        <c:axId val="60465400"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="66113197"/>
+        <c:axId val="78949017"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5114,7 +5276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79943059"/>
+        <c:crossAx val="60465400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5122,7 +5284,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79943059"/>
+        <c:axId val="60465400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5198,7 +5360,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66113197"/>
+        <c:crossAx val="78949017"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5299,7 +5461,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5349,9 +5511,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5363,16 +5525,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$30:$B$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>106.3</c:v>
                 </c:pt>
@@ -5383,6 +5548,9 @@
                   <c:v>106.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>106.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -5395,7 +5563,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5445,9 +5613,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5459,16 +5627,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$30:$C$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>84.8</c:v>
                 </c:pt>
@@ -5479,6 +5650,9 @@
                   <c:v>84.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>84.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>84.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -5491,7 +5665,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D29</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5541,9 +5715,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$30:$A$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5555,16 +5729,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$30:$D$33</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$31:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>73.49</c:v>
                 </c:pt>
@@ -5575,6 +5752,9 @@
                   <c:v>73.49</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>73.49</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>73.49</c:v>
                 </c:pt>
               </c:numCache>
@@ -5590,11 +5770,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="33849121"/>
-        <c:axId val="22197276"/>
+        <c:axId val="1377143"/>
+        <c:axId val="55917101"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33849121"/>
+        <c:axId val="1377143"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5660,7 +5840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22197276"/>
+        <c:crossAx val="55917101"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5668,7 +5848,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22197276"/>
+        <c:axId val="55917101"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5744,7 +5924,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33849121"/>
+        <c:crossAx val="1377143"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5845,7 +6025,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B54</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5895,9 +6075,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5909,16 +6089,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$55:$B$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>167.04</c:v>
                 </c:pt>
@@ -5929,6 +6112,9 @@
                   <c:v>167.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>167.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>167.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -5941,7 +6127,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C54</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5991,9 +6177,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6005,16 +6191,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$55:$C$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>128.08</c:v>
                 </c:pt>
@@ -6025,6 +6214,9 @@
                   <c:v>128.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>128.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>128.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -6037,7 +6229,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D54</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6087,9 +6279,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$55:$A$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6101,16 +6293,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$55:$D$58</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$57:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>109.23</c:v>
                 </c:pt>
@@ -6121,6 +6316,9 @@
                   <c:v>109.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>109.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>109.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -6136,11 +6334,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4779098"/>
-        <c:axId val="66346110"/>
+        <c:axId val="18604727"/>
+        <c:axId val="44393433"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4779098"/>
+        <c:axId val="18604727"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6206,7 +6404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66346110"/>
+        <c:crossAx val="44393433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6214,7 +6412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66346110"/>
+        <c:axId val="44393433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6290,7 +6488,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4779098"/>
+        <c:crossAx val="18604727"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6391,7 +6589,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B28</c:f>
+              <c:f>Allianz!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6441,9 +6639,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$29:$A$31</c:f>
+              <c:f>Allianz!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6452,16 +6650,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$29:$B$31</c:f>
+              <c:f>Allianz!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>49.36</c:v>
                 </c:pt>
@@ -6469,6 +6670,9 @@
                   <c:v>49.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>49.36</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>49.36</c:v>
                 </c:pt>
               </c:numCache>
@@ -6481,7 +6685,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C28</c:f>
+              <c:f>Allianz!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6531,9 +6735,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$29:$A$31</c:f>
+              <c:f>Allianz!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6542,16 +6746,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$29:$C$31</c:f>
+              <c:f>Allianz!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>93.24</c:v>
                 </c:pt>
@@ -6559,6 +6766,9 @@
                   <c:v>93.24</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>93.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>93.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -6571,7 +6781,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D28</c:f>
+              <c:f>Allianz!D29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6621,9 +6831,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$29:$A$31</c:f>
+              <c:f>Allianz!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6632,16 +6842,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$29:$D$31</c:f>
+              <c:f>Allianz!$D$30:$D$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>119.52</c:v>
                 </c:pt>
@@ -6649,6 +6862,9 @@
                   <c:v>119.52</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>119.52</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>119.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -6664,11 +6880,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26142752"/>
-        <c:axId val="61415878"/>
+        <c:axId val="56113944"/>
+        <c:axId val="75100640"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26142752"/>
+        <c:axId val="56113944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6734,7 +6950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61415878"/>
+        <c:crossAx val="75100640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6742,7 +6958,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61415878"/>
+        <c:axId val="75100640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6818,7 +7034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26142752"/>
+        <c:crossAx val="56113944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6919,7 +7135,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6969,9 +7185,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6983,16 +7199,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$80:$B$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$83:$B$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>233.26</c:v>
                 </c:pt>
@@ -7003,6 +7222,9 @@
                   <c:v>233.26</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>233.26</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>233.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -7015,7 +7237,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7065,9 +7287,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7079,16 +7301,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$80:$C$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$83:$C$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>177.26</c:v>
                 </c:pt>
@@ -7099,6 +7324,9 @@
                   <c:v>177.26</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>177.26</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>177.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -7111,7 +7339,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D79</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7161,9 +7389,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$80:$A$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7175,16 +7403,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$80:$D$83</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$83:$D$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>148.98</c:v>
                 </c:pt>
@@ -7195,6 +7426,9 @@
                   <c:v>148.98</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>148.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>148.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -7210,11 +7444,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="6492239"/>
-        <c:axId val="407309"/>
+        <c:axId val="86590742"/>
+        <c:axId val="217606"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6492239"/>
+        <c:axId val="86590742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7280,7 +7514,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="407309"/>
+        <c:crossAx val="217606"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7288,7 +7522,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="407309"/>
+        <c:axId val="217606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7364,7 +7598,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6492239"/>
+        <c:crossAx val="86590742"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7515,9 +7749,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$7</c:f>
+              <c:f>UNIQA!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -7526,16 +7760,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$5:$B$7</c:f>
+              <c:f>UNIQA!$B$5:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>207.75</c:v>
                 </c:pt>
@@ -7543,6 +7780,9 @@
                   <c:v>207.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>207.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>207.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -7605,9 +7845,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$7</c:f>
+              <c:f>UNIQA!$A$5:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -7616,16 +7856,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$5:$C$7</c:f>
+              <c:f>UNIQA!$C$5:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>174.58</c:v>
                 </c:pt>
@@ -7633,6 +7876,9 @@
                   <c:v>174.58</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>174.58</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>174.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -7648,11 +7894,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="86683026"/>
-        <c:axId val="4134480"/>
+        <c:axId val="1753022"/>
+        <c:axId val="77596456"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="86683026"/>
+        <c:axId val="1753022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7718,7 +7964,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4134480"/>
+        <c:crossAx val="77596456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7726,7 +7972,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4134480"/>
+        <c:axId val="77596456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7802,7 +8048,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86683026"/>
+        <c:crossAx val="1753022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7903,7 +8149,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B28</c:f>
+              <c:f>UNIQA!B29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7953,9 +8199,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$29:$A$31</c:f>
+              <c:f>UNIQA!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -7964,16 +8210,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$29:$B$31</c:f>
+              <c:f>UNIQA!$B$30:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>164.09</c:v>
                 </c:pt>
@@ -7981,6 +8230,9 @@
                   <c:v>164.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>164.09</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>164.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -7993,7 +8245,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C28</c:f>
+              <c:f>UNIQA!C29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8043,9 +8295,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$29:$A$31</c:f>
+              <c:f>UNIQA!$A$30:$A$33</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -8054,16 +8306,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$29:$C$31</c:f>
+              <c:f>UNIQA!$C$30:$C$33</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>139.42</c:v>
                 </c:pt>
@@ -8071,6 +8326,9 @@
                   <c:v>139.42</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>139.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>139.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -8086,11 +8344,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="89564202"/>
-        <c:axId val="48120734"/>
+        <c:axId val="21624902"/>
+        <c:axId val="79358927"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="89564202"/>
+        <c:axId val="21624902"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8156,7 +8414,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48120734"/>
+        <c:crossAx val="79358927"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8164,7 +8422,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48120734"/>
+        <c:axId val="79358927"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8240,7 +8498,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89564202"/>
+        <c:crossAx val="21624902"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8341,7 +8599,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B52</c:f>
+              <c:f>UNIQA!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8391,9 +8649,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$53:$A$55</c:f>
+              <c:f>UNIQA!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -8402,16 +8660,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$53:$B$55</c:f>
+              <c:f>UNIQA!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>234.99</c:v>
                 </c:pt>
@@ -8419,6 +8680,9 @@
                   <c:v>234.99</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>234.99</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>234.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -8431,7 +8695,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C52</c:f>
+              <c:f>UNIQA!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8481,9 +8745,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$53:$A$55</c:f>
+              <c:f>UNIQA!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -8492,16 +8756,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$53:$C$55</c:f>
+              <c:f>UNIQA!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>183.95</c:v>
                 </c:pt>
@@ -8509,6 +8776,9 @@
                   <c:v>183.95</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>183.95</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>183.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -8524,11 +8794,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75981845"/>
-        <c:axId val="10855855"/>
+        <c:axId val="76312729"/>
+        <c:axId val="74123183"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75981845"/>
+        <c:axId val="76312729"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8594,7 +8864,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10855855"/>
+        <c:crossAx val="74123183"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8602,7 +8872,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10855855"/>
+        <c:axId val="74123183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8678,7 +8948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75981845"/>
+        <c:crossAx val="76312729"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8779,7 +9049,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B76</c:f>
+              <c:f>UNIQA!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8829,9 +9099,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$77:$A$79</c:f>
+              <c:f>UNIQA!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -8840,16 +9110,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$77:$B$79</c:f>
+              <c:f>UNIQA!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>303.1</c:v>
                 </c:pt>
@@ -8857,6 +9130,9 @@
                   <c:v>303.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>303.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>303.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8869,7 +9145,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C76</c:f>
+              <c:f>UNIQA!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8919,9 +9195,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$77:$A$79</c:f>
+              <c:f>UNIQA!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -8930,16 +9206,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$77:$C$79</c:f>
+              <c:f>UNIQA!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>237.81</c:v>
                 </c:pt>
@@ -8947,6 +9226,9 @@
                   <c:v>237.81</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>237.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>237.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -8962,11 +9244,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="63493716"/>
-        <c:axId val="23412356"/>
+        <c:axId val="35707911"/>
+        <c:axId val="73417877"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63493716"/>
+        <c:axId val="35707911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9032,7 +9314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23412356"/>
+        <c:crossAx val="73417877"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9040,7 +9322,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23412356"/>
+        <c:axId val="73417877"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9116,7 +9398,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63493716"/>
+        <c:crossAx val="35707911"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9267,9 +9549,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$8</c:f>
+              <c:f>Union!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9281,16 +9563,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$5:$B$8</c:f>
+              <c:f>Union!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>151.45</c:v>
                 </c:pt>
@@ -9301,6 +9586,9 @@
                   <c:v>151.45</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>151.45</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>151.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -9363,9 +9651,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$8</c:f>
+              <c:f>Union!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9377,16 +9665,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$5:$C$8</c:f>
+              <c:f>Union!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>49.98</c:v>
                 </c:pt>
@@ -9397,6 +9688,9 @@
                   <c:v>49.98</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>49.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>49.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -9412,11 +9706,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40049227"/>
-        <c:axId val="50826481"/>
+        <c:axId val="74116700"/>
+        <c:axId val="11705562"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40049227"/>
+        <c:axId val="74116700"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9482,7 +9776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50826481"/>
+        <c:crossAx val="11705562"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9490,7 +9784,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50826481"/>
+        <c:axId val="11705562"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9566,7 +9860,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40049227"/>
+        <c:crossAx val="74116700"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9667,7 +9961,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B29</c:f>
+              <c:f>Union!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9717,9 +10011,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$30:$A$33</c:f>
+              <c:f>Union!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9731,16 +10025,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$30:$B$33</c:f>
+              <c:f>Union!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>120.23</c:v>
                 </c:pt>
@@ -9751,6 +10048,9 @@
                   <c:v>39.68</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>120.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>120.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -9763,7 +10063,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C29</c:f>
+              <c:f>Union!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9813,9 +10113,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$30:$A$33</c:f>
+              <c:f>Union!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -9827,16 +10127,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$30:$C$33</c:f>
+              <c:f>Union!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>39.68</c:v>
                 </c:pt>
@@ -9847,6 +10150,9 @@
                   <c:v>39.68</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
@@ -9862,11 +10168,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77247242"/>
-        <c:axId val="55003750"/>
+        <c:axId val="18926236"/>
+        <c:axId val="8979301"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77247242"/>
+        <c:axId val="18926236"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9932,7 +10238,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55003750"/>
+        <c:crossAx val="8979301"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9940,7 +10246,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55003750"/>
+        <c:axId val="8979301"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10016,7 +10322,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77247242"/>
+        <c:crossAx val="18926236"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10117,7 +10423,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B54</c:f>
+              <c:f>Union!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10167,9 +10473,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$55:$A$58</c:f>
+              <c:f>Union!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10181,16 +10487,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$55:$B$58</c:f>
+              <c:f>Union!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>206.12</c:v>
                 </c:pt>
@@ -10201,6 +10510,9 @@
                   <c:v>206.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>206.12</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>206.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -10213,7 +10525,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C54</c:f>
+              <c:f>Union!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10263,9 +10575,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$55:$A$58</c:f>
+              <c:f>Union!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10277,16 +10589,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$55:$C$58</c:f>
+              <c:f>Union!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>68.04</c:v>
                 </c:pt>
@@ -10297,6 +10612,9 @@
                   <c:v>68.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>68.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>68.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -10312,11 +10630,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30214398"/>
-        <c:axId val="55481567"/>
+        <c:axId val="58206801"/>
+        <c:axId val="74633484"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30214398"/>
+        <c:axId val="58206801"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10382,7 +10700,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55481567"/>
+        <c:crossAx val="74633484"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10390,7 +10708,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55481567"/>
+        <c:axId val="74633484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10466,7 +10784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30214398"/>
+        <c:crossAx val="58206801"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10567,7 +10885,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B79</c:f>
+              <c:f>Union!B82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10617,9 +10935,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$80:$A$83</c:f>
+              <c:f>Union!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10631,16 +10949,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$80:$B$83</c:f>
+              <c:f>Union!$B$83:$B$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>286.39</c:v>
                 </c:pt>
@@ -10651,6 +10972,9 @@
                   <c:v>286.39</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>286.39</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>286.39</c:v>
                 </c:pt>
               </c:numCache>
@@ -10663,7 +10987,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C79</c:f>
+              <c:f>Union!C82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10713,9 +11037,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$80:$A$83</c:f>
+              <c:f>Union!$A$83:$A$87</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10727,16 +11051,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$80:$C$83</c:f>
+              <c:f>Union!$C$83:$C$87</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>94.53</c:v>
                 </c:pt>
@@ -10747,6 +11074,9 @@
                   <c:v>94.53</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>94.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>94.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -10762,11 +11092,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69701317"/>
-        <c:axId val="76378581"/>
+        <c:axId val="71044412"/>
+        <c:axId val="36887201"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69701317"/>
+        <c:axId val="71044412"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10832,7 +11162,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76378581"/>
+        <c:crossAx val="36887201"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10840,7 +11170,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76378581"/>
+        <c:axId val="36887201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10916,7 +11246,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69701317"/>
+        <c:crossAx val="71044412"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11067,9 +11397,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11081,16 +11411,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>144.96</c:v>
                 </c:pt>
@@ -11101,6 +11434,9 @@
                   <c:v>144.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>144.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>144.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -11163,9 +11499,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11177,16 +11513,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>167.64</c:v>
                 </c:pt>
@@ -11197,6 +11536,9 @@
                   <c:v>167.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>167.64</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>167.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -11259,9 +11601,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11273,16 +11615,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$8</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>126.12</c:v>
                 </c:pt>
@@ -11293,6 +11638,9 @@
                   <c:v>126.12</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>126.12</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>126.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -11308,11 +11656,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84466916"/>
-        <c:axId val="30788573"/>
+        <c:axId val="67681192"/>
+        <c:axId val="378246"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84466916"/>
+        <c:axId val="67681192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11378,7 +11726,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30788573"/>
+        <c:crossAx val="378246"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11386,7 +11734,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30788573"/>
+        <c:axId val="378246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11462,7 +11810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84466916"/>
+        <c:crossAx val="67681192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11563,7 +11911,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B52</c:f>
+              <c:f>Allianz!B54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11613,9 +11961,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$53:$A$55</c:f>
+              <c:f>Allianz!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11624,16 +11972,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$53:$B$55</c:f>
+              <c:f>Allianz!$B$55:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>117.24</c:v>
                 </c:pt>
@@ -11641,6 +11992,9 @@
                   <c:v>117.24</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>117.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>117.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -11653,7 +12007,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C52</c:f>
+              <c:f>Allianz!C54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11703,9 +12057,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$53:$A$55</c:f>
+              <c:f>Allianz!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11714,16 +12068,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$53:$C$55</c:f>
+              <c:f>Allianz!$C$55:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>159</c:v>
                 </c:pt>
@@ -11731,6 +12088,9 @@
                   <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>159</c:v>
                 </c:pt>
               </c:numCache>
@@ -11743,7 +12103,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D52</c:f>
+              <c:f>Allianz!D54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11793,9 +12153,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$53:$A$55</c:f>
+              <c:f>Allianz!$A$55:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11804,16 +12164,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$53:$D$55</c:f>
+              <c:f>Allianz!$D$55:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>206.64</c:v>
                 </c:pt>
@@ -11821,6 +12184,9 @@
                   <c:v>206.64</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>206.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>206.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -11836,11 +12202,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68332515"/>
-        <c:axId val="96053618"/>
+        <c:axId val="27029583"/>
+        <c:axId val="35931869"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68332515"/>
+        <c:axId val="27029583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11906,7 +12272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96053618"/>
+        <c:crossAx val="35931869"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11914,7 +12280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96053618"/>
+        <c:axId val="35931869"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11990,7 +12356,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68332515"/>
+        <c:crossAx val="27029583"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12091,7 +12457,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12141,9 +12507,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12155,16 +12521,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$30:$B$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>114.96</c:v>
                 </c:pt>
@@ -12175,6 +12544,9 @@
                   <c:v>114.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>114.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>114.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -12187,7 +12559,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12237,9 +12609,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12251,16 +12623,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$30:$C$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>132.84</c:v>
                 </c:pt>
@@ -12271,6 +12646,9 @@
                   <c:v>132.84</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>132.84</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>132.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -12283,7 +12661,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D29</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12333,9 +12711,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$30:$A$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12347,16 +12725,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$30:$D$33</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$31:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>100.08</c:v>
                 </c:pt>
@@ -12367,6 +12748,9 @@
                   <c:v>100.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>100.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>100.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -12382,11 +12766,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90499455"/>
-        <c:axId val="92947996"/>
+        <c:axId val="53679471"/>
+        <c:axId val="12525180"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90499455"/>
+        <c:axId val="53679471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12452,7 +12836,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92947996"/>
+        <c:crossAx val="12525180"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12460,7 +12844,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92947996"/>
+        <c:axId val="12525180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12536,7 +12920,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90499455"/>
+        <c:crossAx val="53679471"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12637,7 +13021,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B54</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12687,9 +13071,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12701,16 +13085,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$55:$B$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>174.72</c:v>
                 </c:pt>
@@ -12721,6 +13108,9 @@
                   <c:v>174.72</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>174.72</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>174.72</c:v>
                 </c:pt>
               </c:numCache>
@@ -12733,7 +13123,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C54</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12783,9 +13173,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12797,16 +13187,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$55:$C$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>194.76</c:v>
                 </c:pt>
@@ -12817,6 +13210,9 @@
                   <c:v>194.76</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>194.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>194.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -12829,7 +13225,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D54</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12879,9 +13275,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$55:$A$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12893,16 +13289,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$55:$D$58</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$57:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>152.16</c:v>
                 </c:pt>
@@ -12913,6 +13312,9 @@
                   <c:v>152.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>152.16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>152.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -12928,11 +13330,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36458283"/>
-        <c:axId val="20797784"/>
+        <c:axId val="32229362"/>
+        <c:axId val="73642918"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36458283"/>
+        <c:axId val="32229362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12998,7 +13400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20797784"/>
+        <c:crossAx val="73642918"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13006,7 +13408,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20797784"/>
+        <c:axId val="73642918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13082,7 +13484,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36458283"/>
+        <c:crossAx val="32229362"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13233,9 +13635,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13247,16 +13649,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$5:$B$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>190.22</c:v>
                 </c:pt>
@@ -13267,6 +13672,9 @@
                   <c:v>190.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>171.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>171.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -13329,9 +13737,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13343,16 +13751,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$5:$C$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>138.36</c:v>
                 </c:pt>
@@ -13363,6 +13774,9 @@
                   <c:v>138.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>124.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>124.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -13425,9 +13839,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13439,16 +13853,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$5:$D$8</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>155.18</c:v>
                 </c:pt>
@@ -13459,6 +13876,9 @@
                   <c:v>155.18</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>139.66</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>139.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -13474,11 +13894,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77359126"/>
-        <c:axId val="66860533"/>
+        <c:axId val="20155807"/>
+        <c:axId val="36502867"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77359126"/>
+        <c:axId val="20155807"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13544,7 +13964,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66860533"/>
+        <c:crossAx val="36502867"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13552,7 +13972,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66860533"/>
+        <c:axId val="36502867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13628,7 +14048,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77359126"/>
+        <c:crossAx val="20155807"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13729,7 +14149,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B29</c:f>
+              <c:f>'ČSOB Poisťovňa'!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13779,7 +14199,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$31:$A$32</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13793,7 +14213,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$30:$B$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$31:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13813,7 +14233,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C29</c:f>
+              <c:f>'ČSOB Poisťovňa'!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13863,7 +14283,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$31:$A$32</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13877,7 +14297,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$30:$C$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$31:$C$32</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13897,7 +14317,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D29</c:f>
+              <c:f>'ČSOB Poisťovňa'!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13947,7 +14367,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$30:$A$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$31:$A$32</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -13961,7 +14381,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$30:$D$31</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$31:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -13984,11 +14404,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7569708"/>
-        <c:axId val="4333849"/>
+        <c:axId val="12188769"/>
+        <c:axId val="41334712"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7569708"/>
+        <c:axId val="12188769"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14054,7 +14474,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4333849"/>
+        <c:crossAx val="41334712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14062,7 +14482,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4333849"/>
+        <c:axId val="41334712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14138,7 +14558,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7569708"/>
+        <c:crossAx val="12188769"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14239,7 +14659,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B52</c:f>
+              <c:f>'ČSOB Poisťovňa'!B53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14289,9 +14709,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$54:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14303,16 +14723,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$53:$B$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$54:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>216.18</c:v>
                 </c:pt>
@@ -14323,6 +14746,9 @@
                   <c:v>216.18</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>216.18</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>216.18</c:v>
                 </c:pt>
               </c:numCache>
@@ -14335,7 +14761,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C52</c:f>
+              <c:f>'ČSOB Poisťovňa'!C53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14385,9 +14811,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$54:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14399,16 +14825,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$53:$C$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$54:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>157.93</c:v>
                 </c:pt>
@@ -14419,6 +14848,9 @@
                   <c:v>157.93</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>157.93</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>157.93</c:v>
                 </c:pt>
               </c:numCache>
@@ -14431,7 +14863,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D52</c:f>
+              <c:f>'ČSOB Poisťovňa'!D53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14481,9 +14913,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$53:$A$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$54:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14495,16 +14927,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$53:$D$56</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$54:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>176.7</c:v>
                 </c:pt>
@@ -14515,6 +14950,9 @@
                   <c:v>176.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>176.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>176.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -14530,11 +14968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43865406"/>
-        <c:axId val="89412078"/>
+        <c:axId val="1522802"/>
+        <c:axId val="9354615"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43865406"/>
+        <c:axId val="1522802"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14600,7 +15038,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89412078"/>
+        <c:crossAx val="9354615"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14608,7 +15046,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89412078"/>
+        <c:axId val="9354615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14684,7 +15122,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43865406"/>
+        <c:crossAx val="1522802"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14785,7 +15223,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B77</c:f>
+              <c:f>'ČSOB Poisťovňa'!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14835,9 +15273,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$80:$A$84</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14849,16 +15287,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$78:$B$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$80:$B$84</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>275.68</c:v>
                 </c:pt>
@@ -14869,6 +15310,9 @@
                   <c:v>306.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>306.32</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>306.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -14881,7 +15325,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C77</c:f>
+              <c:f>'ČSOB Poisťovňa'!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14931,9 +15375,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$80:$A$84</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14945,16 +15389,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$78:$C$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$80:$C$84</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>202.39</c:v>
                 </c:pt>
@@ -14965,6 +15412,9 @@
                   <c:v>224.88</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>224.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>224.88</c:v>
                 </c:pt>
               </c:numCache>
@@ -14977,7 +15427,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D77</c:f>
+              <c:f>'ČSOB Poisťovňa'!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15027,9 +15477,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$78:$A$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$80:$A$84</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15041,16 +15491,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$78:$D$81</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$80:$D$84</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>225.85</c:v>
                 </c:pt>
@@ -15061,6 +15514,9 @@
                   <c:v>250.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>250.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>250.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -15076,11 +15532,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78723410"/>
-        <c:axId val="11767295"/>
+        <c:axId val="42312793"/>
+        <c:axId val="48941645"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78723410"/>
+        <c:axId val="42312793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15146,7 +15602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11767295"/>
+        <c:crossAx val="48941645"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15154,7 +15610,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11767295"/>
+        <c:axId val="48941645"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15230,7 +15686,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78723410"/>
+        <c:crossAx val="42312793"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15331,7 +15787,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B76</c:f>
+              <c:f>Allianz!B79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15381,9 +15837,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$77:$A$79</c:f>
+              <c:f>Allianz!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15392,16 +15848,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$77:$B$79</c:f>
+              <c:f>Allianz!$B$80:$B$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>158.64</c:v>
                 </c:pt>
@@ -15409,6 +15868,9 @@
                   <c:v>158.64</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>158.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>158.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -15421,7 +15883,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C76</c:f>
+              <c:f>Allianz!C79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15471,9 +15933,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$77:$A$79</c:f>
+              <c:f>Allianz!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15482,16 +15944,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$77:$C$79</c:f>
+              <c:f>Allianz!$C$80:$C$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>216.84</c:v>
                 </c:pt>
@@ -15499,6 +15964,9 @@
                   <c:v>216.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>216.84</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>216.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -15511,7 +15979,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D76</c:f>
+              <c:f>Allianz!D79</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15561,9 +16029,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$77:$A$79</c:f>
+              <c:f>Allianz!$A$80:$A$83</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15572,16 +16040,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$77:$D$79</c:f>
+              <c:f>Allianz!$D$80:$D$83</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>277.2</c:v>
                 </c:pt>
@@ -15589,6 +16060,9 @@
                   <c:v>277.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>277.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>277.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -15604,11 +16078,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37166430"/>
-        <c:axId val="20443800"/>
+        <c:axId val="58963313"/>
+        <c:axId val="75652259"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37166430"/>
+        <c:axId val="58963313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15674,7 +16148,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20443800"/>
+        <c:crossAx val="75652259"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15682,7 +16156,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20443800"/>
+        <c:axId val="75652259"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15758,7 +16232,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37166430"/>
+        <c:crossAx val="58963313"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15909,9 +16383,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$8</c:f>
+              <c:f>Colonnade!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15923,16 +16397,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$5:$B$8</c:f>
+              <c:f>Colonnade!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>151.84</c:v>
                 </c:pt>
@@ -15943,6 +16420,9 @@
                   <c:v>182.53</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -16005,9 +16485,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$8</c:f>
+              <c:f>Colonnade!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16019,16 +16499,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$5:$C$8</c:f>
+              <c:f>Colonnade!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>207.85</c:v>
                 </c:pt>
@@ -16039,6 +16522,9 @@
                   <c:v>246.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -16101,9 +16587,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$5:$A$8</c:f>
+              <c:f>Colonnade!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16115,16 +16601,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$5:$D$8</c:f>
+              <c:f>Colonnade!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>201.92</c:v>
                 </c:pt>
@@ -16135,6 +16624,9 @@
                   <c:v>240.14</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -16150,11 +16642,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47253965"/>
-        <c:axId val="84779179"/>
+        <c:axId val="16830609"/>
+        <c:axId val="30908417"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47253965"/>
+        <c:axId val="16830609"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16220,7 +16712,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84779179"/>
+        <c:crossAx val="30908417"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16228,7 +16720,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84779179"/>
+        <c:axId val="30908417"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16304,7 +16796,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47253965"/>
+        <c:crossAx val="16830609"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16405,7 +16897,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B29</c:f>
+              <c:f>Colonnade!B30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16455,9 +16947,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$30:$A$33</c:f>
+              <c:f>Colonnade!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16469,16 +16961,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$30:$B$33</c:f>
+              <c:f>Colonnade!$B$31:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>142.75</c:v>
                 </c:pt>
@@ -16489,6 +16984,9 @@
                   <c:v>142.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>142.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>142.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -16501,7 +16999,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C29</c:f>
+              <c:f>Colonnade!C30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16551,9 +17049,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$30:$A$33</c:f>
+              <c:f>Colonnade!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16565,16 +17063,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$30:$C$33</c:f>
+              <c:f>Colonnade!$C$31:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>191.67</c:v>
                 </c:pt>
@@ -16585,6 +17086,9 @@
                   <c:v>191.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>191.67</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>191.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -16597,7 +17101,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D29</c:f>
+              <c:f>Colonnade!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16647,9 +17151,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$30:$A$33</c:f>
+              <c:f>Colonnade!$A$31:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16661,16 +17165,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$30:$D$33</c:f>
+              <c:f>Colonnade!$D$31:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>186.44</c:v>
                 </c:pt>
@@ -16681,6 +17188,9 @@
                   <c:v>186.44</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>186.44</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>186.44</c:v>
                 </c:pt>
               </c:numCache>
@@ -16696,11 +17206,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="48729051"/>
-        <c:axId val="51468622"/>
+        <c:axId val="58134934"/>
+        <c:axId val="21418502"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48729051"/>
+        <c:axId val="58134934"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16766,7 +17276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51468622"/>
+        <c:crossAx val="21418502"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16774,7 +17284,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51468622"/>
+        <c:axId val="21418502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16850,7 +17360,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48729051"/>
+        <c:crossAx val="58134934"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16951,7 +17461,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B54</c:f>
+              <c:f>Colonnade!B56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17001,9 +17511,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$55:$A$58</c:f>
+              <c:f>Colonnade!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17015,16 +17525,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$55:$B$58</c:f>
+              <c:f>Colonnade!$B$57:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>182.53</c:v>
                 </c:pt>
@@ -17035,6 +17548,9 @@
                   <c:v>182.53</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>182.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>182.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -17047,7 +17563,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C54</c:f>
+              <c:f>Colonnade!C56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17097,9 +17613,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$55:$A$58</c:f>
+              <c:f>Colonnade!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17111,16 +17627,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$55:$C$58</c:f>
+              <c:f>Colonnade!$C$57:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>246.96</c:v>
                 </c:pt>
@@ -17131,6 +17650,9 @@
                   <c:v>246.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>246.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>246.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -17143,7 +17665,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D54</c:f>
+              <c:f>Colonnade!D56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17193,9 +17715,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$55:$A$58</c:f>
+              <c:f>Colonnade!$A$57:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17207,16 +17729,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$55:$D$58</c:f>
+              <c:f>Colonnade!$D$57:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>240.14</c:v>
                 </c:pt>
@@ -17227,6 +17752,9 @@
                   <c:v>240.14</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>240.14</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>240.14</c:v>
                 </c:pt>
               </c:numCache>
@@ -17242,11 +17770,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29093845"/>
-        <c:axId val="96675431"/>
+        <c:axId val="59338210"/>
+        <c:axId val="89669398"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29093845"/>
+        <c:axId val="59338210"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17312,7 +17840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96675431"/>
+        <c:crossAx val="89669398"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17320,7 +17848,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96675431"/>
+        <c:axId val="89669398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17396,7 +17924,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29093845"/>
+        <c:crossAx val="59338210"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17497,7 +18025,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B79</c:f>
+              <c:f>Colonnade!B82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17547,9 +18075,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$80:$A$82</c:f>
+              <c:f>Colonnade!$A$83:$A$86</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17558,16 +18086,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$80:$B$82</c:f>
+              <c:f>Colonnade!$B$83:$B$86</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>254.31</c:v>
                 </c:pt>
@@ -17575,6 +18106,9 @@
                   <c:v>254.31</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>254.31</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>254.31</c:v>
                 </c:pt>
               </c:numCache>
@@ -17587,7 +18121,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C79</c:f>
+              <c:f>Colonnade!C82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17637,9 +18171,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$80:$A$82</c:f>
+              <c:f>Colonnade!$A$83:$A$86</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17648,16 +18182,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$80:$C$82</c:f>
+              <c:f>Colonnade!$C$83:$C$86</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>347.42</c:v>
                 </c:pt>
@@ -17665,6 +18202,9 @@
                   <c:v>347.42</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>347.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>347.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -17677,7 +18217,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D79</c:f>
+              <c:f>Colonnade!D82</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17727,9 +18267,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$80:$A$82</c:f>
+              <c:f>Colonnade!$A$83:$A$86</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17738,16 +18278,19 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$80:$D$82</c:f>
+              <c:f>Colonnade!$D$83:$D$86</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>337.73</c:v>
                 </c:pt>
@@ -17755,6 +18298,9 @@
                   <c:v>337.73</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>337.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>337.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -17770,11 +18316,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="65841303"/>
-        <c:axId val="16364111"/>
+        <c:axId val="33259682"/>
+        <c:axId val="19577254"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="65841303"/>
+        <c:axId val="33259682"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17840,7 +18386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16364111"/>
+        <c:crossAx val="19577254"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17848,7 +18394,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16364111"/>
+        <c:axId val="19577254"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17924,7 +18470,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65841303"/>
+        <c:crossAx val="33259682"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18075,9 +18621,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$8</c:f>
+              <c:f>Generali!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -18089,16 +18635,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$5:$B$8</c:f>
+              <c:f>Generali!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>99.41</c:v>
                 </c:pt>
@@ -18109,6 +18658,9 @@
                   <c:v>99.41</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>99.41</c:v>
                 </c:pt>
               </c:numCache>
@@ -18171,9 +18723,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$8</c:f>
+              <c:f>Generali!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -18185,16 +18737,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$5:$C$8</c:f>
+              <c:f>Generali!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>114.74</c:v>
                 </c:pt>
@@ -18205,6 +18760,9 @@
                   <c:v>114.74</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>114.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>114.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -18267,9 +18825,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$8</c:f>
+              <c:f>Generali!$A$5:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -18281,16 +18839,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$5:$D$8</c:f>
+              <c:f>Generali!$D$5:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>94.81</c:v>
                 </c:pt>
@@ -18301,6 +18862,9 @@
                   <c:v>94.81</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>94.81</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>94.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -18316,11 +18880,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="28902023"/>
-        <c:axId val="41839186"/>
+        <c:axId val="64756381"/>
+        <c:axId val="35696978"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28902023"/>
+        <c:axId val="64756381"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18386,7 +18950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41839186"/>
+        <c:crossAx val="35696978"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -18394,7 +18958,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41839186"/>
+        <c:axId val="35696978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18470,7 +19034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28902023"/>
+        <c:crossAx val="64756381"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18558,13 +19122,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18573,7 +19137,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5143680"/>
+        <a:off x="4558680" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18588,13 +19152,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18603,7 +19167,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18618,13 +19182,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18633,7 +19197,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14287680"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18683,13 +19247,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18698,7 +19262,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18713,14 +19277,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18728,7 +19292,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10096560"/>
+        <a:off x="4558680" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18743,13 +19307,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18758,7 +19322,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14859000"/>
+        <a:off x="4558680" y="15430680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18808,13 +19372,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18823,7 +19387,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18838,14 +19402,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18853,7 +19417,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10096560"/>
+        <a:off x="4558680" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18868,13 +19432,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18883,7 +19447,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14859000"/>
+        <a:off x="4558680" y="15430680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18933,13 +19497,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -18948,7 +19512,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18963,14 +19527,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -18978,7 +19542,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10096560"/>
+        <a:off x="4558680" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -18993,13 +19557,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19008,7 +19572,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14859000"/>
+        <a:off x="4558680" y="15430680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19058,13 +19622,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19073,7 +19637,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19088,14 +19652,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -19103,7 +19667,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10096560"/>
+        <a:off x="4558680" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19118,13 +19682,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19133,7 +19697,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14859000"/>
+        <a:off x="4558680" y="15430680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19183,13 +19747,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19198,7 +19762,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="5143680"/>
+        <a:off x="3571920" y="5334120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19213,13 +19777,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19228,7 +19792,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="9715680"/>
+        <a:off x="3571920" y="10096560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19243,13 +19807,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19258,7 +19822,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="14287680"/>
+        <a:off x="3571920" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19308,13 +19872,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19323,7 +19887,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="5334120"/>
+        <a:off x="3571920" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19338,14 +19902,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -19353,7 +19917,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="10096560"/>
+        <a:off x="3571920" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19368,13 +19932,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19383,7 +19947,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="14859000"/>
+        <a:off x="3571920" y="15430680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19433,13 +19997,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19448,7 +20012,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19463,14 +20027,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -19478,7 +20042,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10096560"/>
+        <a:off x="4558680" y="10477440"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19528,13 +20092,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19543,7 +20107,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="5334120"/>
+        <a:off x="4558680" y="5524560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19558,13 +20122,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19573,7 +20137,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="9715680"/>
+        <a:off x="4558680" y="9906120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19588,13 +20152,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -19603,7 +20167,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="14478120"/>
+        <a:off x="4558680" y="14859000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -19797,7 +20361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -19869,42 +20433,42 @@
         <v>145.2</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>145.2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>93.24</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>119.52</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>49.36</v>
@@ -19918,7 +20482,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>49.36</v>
@@ -19930,56 +20494,56 @@
         <v>119.52</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>119.52</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>119.52</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>117.24</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>206.64</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>117.24</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>206.64</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>117.24</v>
@@ -19991,64 +20555,120 @@
         <v>206.64</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B80" s="5" t="n">
         <v>158.64</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C80" s="5" t="n">
         <v>216.84</v>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D80" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B81" s="5" t="n">
         <v>158.64</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>216.84</v>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D81" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46313</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>158.64</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>216.84</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D82" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D83" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
@@ -20069,7 +20689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20155,42 +20775,42 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>142.75</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>191.67</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>186.44</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>142.75</v>
@@ -20204,7 +20824,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>142.75</v>
@@ -20218,7 +20838,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>142.75</v>
@@ -20230,56 +20850,56 @@
         <v>186.44</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>186.44</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>186.44</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>240.14</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>240.14</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>182.53</v>
@@ -20293,7 +20913,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>182.53</v>
@@ -20305,64 +20925,120 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B83" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C83" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D83" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B84" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C84" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D81" s="5" t="n">
+      <c r="D84" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
         <v>46313</v>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B85" s="5" t="n">
         <v>254.31</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C85" s="5" t="n">
         <v>347.42</v>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D85" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D86" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
@@ -20383,7 +21059,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20469,42 +21145,42 @@
         <v>94.81</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>94.81</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>77.55</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>92.26</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>73.19</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>77.55</v>
@@ -20518,7 +21194,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>77.55</v>
@@ -20532,7 +21208,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>77.55</v>
@@ -20544,56 +21220,56 @@
         <v>73.19</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>147.57</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>147.57</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>152.27</v>
@@ -20607,7 +21283,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>152.27</v>
@@ -20619,70 +21295,70 @@
         <v>147.57</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>195.16</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>195.16</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>195.16</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>199.86</v>
@@ -20691,6 +21367,62 @@
         <v>211.29</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D87" s="5" t="n">
         <v>195.16</v>
       </c>
     </row>
@@ -20711,7 +21443,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -20797,42 +21529,42 @@
         <v>86.02</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>121.09</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>86.02</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>95.79</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>79.6</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>69.52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>95.79</v>
@@ -20846,7 +21578,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>95.79</v>
@@ -20860,7 +21592,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>95.79</v>
@@ -20872,56 +21604,56 @@
         <v>69.52</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>69.52</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>69.52</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>92.59</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>92.59</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>145.65</v>
@@ -20935,7 +21667,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>145.65</v>
@@ -20947,70 +21679,70 @@
         <v>92.59</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>132.4</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>132.4</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>132.4</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>213.4</v>
@@ -21019,6 +21751,62 @@
         <v>165.4</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D87" s="5" t="n">
         <v>132.4</v>
       </c>
     </row>
@@ -21039,7 +21827,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -21125,42 +21913,42 @@
         <v>93.73</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>93.73</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>73.49</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>106.3</v>
@@ -21174,7 +21962,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>106.3</v>
@@ -21188,7 +21976,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>106.3</v>
@@ -21200,56 +21988,56 @@
         <v>73.49</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>73.49</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>73.49</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>109.23</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>109.23</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>167.04</v>
@@ -21263,7 +22051,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>167.04</v>
@@ -21275,70 +22063,70 @@
         <v>109.23</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>148.98</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>148.98</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>148.98</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>233.26</v>
@@ -21347,6 +22135,62 @@
         <v>177.26</v>
       </c>
       <c r="D83" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D87" s="5" t="n">
         <v>148.98</v>
       </c>
     </row>
@@ -21367,7 +22211,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -21427,36 +22271,36 @@
         <v>174.58</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>174.58</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>164.09</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>139.42</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>164.09</v>
@@ -21467,7 +22311,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>164.09</v>
@@ -21476,47 +22320,47 @@
         <v>139.42</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>139.42</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>139.42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>234.99</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>183.95</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>234.99</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>183.95</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>234.99</v>
@@ -21525,52 +22369,96 @@
         <v>183.95</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B80" s="5" t="n">
         <v>303.1</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C80" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
         <v>46312</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B81" s="5" t="n">
         <v>303.1</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>46313</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>303.1</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C83" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
@@ -21591,7 +22479,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -21662,36 +22550,36 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>120.23</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>39.68</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>120.23</v>
@@ -21702,10 +22590,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>39.68</v>
+        <v>120.23</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>39.68</v>
@@ -21713,56 +22601,56 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>120.23</v>
+        <v>39.68</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>39.68</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>68.04</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>68.04</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>206.12</v>
@@ -21773,7 +22661,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>206.12</v>
@@ -21782,63 +22670,107 @@
         <v>68.04</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>94.53</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>94.53</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>94.53</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>286.39</v>
       </c>
       <c r="C83" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C87" s="5" t="n">
         <v>94.53</v>
       </c>
     </row>
@@ -21859,7 +22791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -21945,42 +22877,42 @@
         <v>126.12</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>126.12</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>100.08</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>114.96</v>
@@ -21994,7 +22926,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>114.96</v>
@@ -22008,7 +22940,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>114.96</v>
@@ -22020,56 +22952,56 @@
         <v>100.08</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>152.16</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>152.16</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>174.72</v>
@@ -22083,7 +23015,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>174.72</v>
@@ -22095,13 +23027,55 @@
         <v>152.16</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
         <v>31</v>
       </c>
     </row>
@@ -22122,7 +23096,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -22208,89 +23182,89 @@
         <v>139.66</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>124.53</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>139.66</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>145.44</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>118.54</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>145.44</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>118.54</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>130.89</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="5" t="n">
         <v>95.05</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D32" s="5" t="n">
         <v>106.69</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>216.18</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>176.7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>216.18</v>
@@ -22304,7 +23278,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>216.18</v>
@@ -22318,7 +23292,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B56" s="5" t="n">
         <v>216.18</v>
@@ -22330,70 +23304,70 @@
         <v>176.7</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>275.68</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>202.39</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>225.85</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>306.32</v>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>224.88</v>
-      </c>
-      <c r="D79" s="5" t="n">
-        <v>250.95</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>306.32</v>
+        <v>275.68</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>224.88</v>
+        <v>202.39</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>250.95</v>
+        <v>225.85</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>306.32</v>
@@ -22402,6 +23376,48 @@
         <v>224.88</v>
       </c>
       <c r="D81" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D84" s="5" t="n">
         <v>250.95</v>
       </c>
     </row>

--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -453,9 +453,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$12</c:f>
+              <c:f>Allianz!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -479,16 +479,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$5:$B$12</c:f>
+              <c:f>Allianz!$B$5:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>53.8</c:v>
                 </c:pt>
@@ -511,6 +514,9 @@
                   <c:v>53.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>53.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -573,9 +579,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$12</c:f>
+              <c:f>Allianz!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -599,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$5:$C$12</c:f>
+              <c:f>Allianz!$C$5:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>112.32</c:v>
                 </c:pt>
@@ -631,6 +640,9 @@
                   <c:v>112.32</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>112.32</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>112.32</c:v>
                 </c:pt>
               </c:numCache>
@@ -693,9 +705,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$5:$A$12</c:f>
+              <c:f>Allianz!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -719,16 +731,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$5:$D$12</c:f>
+              <c:f>Allianz!$D$5:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>145.2</c:v>
                 </c:pt>
@@ -751,6 +766,9 @@
                   <c:v>145.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>145.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>145.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -766,11 +784,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82497474"/>
-        <c:axId val="16118563"/>
+        <c:axId val="64124824"/>
+        <c:axId val="62757936"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82497474"/>
+        <c:axId val="64124824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -836,7 +854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16118563"/>
+        <c:crossAx val="62757936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -844,7 +862,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16118563"/>
+        <c:axId val="62757936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -920,7 +938,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82497474"/>
+        <c:crossAx val="64124824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1021,7 +1039,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B34</c:f>
+              <c:f>Generali!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1071,9 +1089,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$35:$A$43</c:f>
+              <c:f>Generali!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1100,16 +1118,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$35:$B$43</c:f>
+              <c:f>Generali!$B$36:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>77.55</c:v>
                 </c:pt>
@@ -1135,6 +1156,9 @@
                   <c:v>77.55</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>77.55</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>77.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -1147,7 +1171,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C34</c:f>
+              <c:f>Generali!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1197,9 +1221,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$35:$A$43</c:f>
+              <c:f>Generali!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1226,16 +1250,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$35:$C$43</c:f>
+              <c:f>Generali!$C$36:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>92.26</c:v>
                 </c:pt>
@@ -1261,6 +1288,9 @@
                   <c:v>92.26</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>92.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -1273,7 +1303,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D34</c:f>
+              <c:f>Generali!D35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1323,9 +1353,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$35:$A$43</c:f>
+              <c:f>Generali!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1352,16 +1382,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$35:$D$43</c:f>
+              <c:f>Generali!$D$36:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>73.19</c:v>
                 </c:pt>
@@ -1387,6 +1420,9 @@
                   <c:v>73.19</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>73.19</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>73.19</c:v>
                 </c:pt>
               </c:numCache>
@@ -1402,11 +1438,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52098467"/>
-        <c:axId val="40947817"/>
+        <c:axId val="85384001"/>
+        <c:axId val="35329439"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52098467"/>
+        <c:axId val="85384001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1472,7 +1508,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40947817"/>
+        <c:crossAx val="35329439"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1480,7 +1516,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40947817"/>
+        <c:axId val="35329439"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1556,7 +1592,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52098467"/>
+        <c:crossAx val="85384001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1657,7 +1693,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B64</c:f>
+              <c:f>Generali!B66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1707,9 +1743,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$65:$A$73</c:f>
+              <c:f>Generali!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1736,16 +1772,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$65:$B$73</c:f>
+              <c:f>Generali!$B$67:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>152.27</c:v>
                 </c:pt>
@@ -1771,6 +1810,9 @@
                   <c:v>152.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>152.27</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>152.27</c:v>
                 </c:pt>
               </c:numCache>
@@ -1783,7 +1825,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C64</c:f>
+              <c:f>Generali!C66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1833,9 +1875,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$65:$A$73</c:f>
+              <c:f>Generali!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1862,16 +1904,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$65:$C$73</c:f>
+              <c:f>Generali!$C$67:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>163.7</c:v>
                 </c:pt>
@@ -1897,6 +1942,9 @@
                   <c:v>163.7</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>163.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>163.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1909,7 +1957,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D64</c:f>
+              <c:f>Generali!D66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1959,9 +2007,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$65:$A$73</c:f>
+              <c:f>Generali!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -1988,16 +2036,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$65:$D$73</c:f>
+              <c:f>Generali!$D$67:$D$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>147.57</c:v>
                 </c:pt>
@@ -2023,6 +2074,9 @@
                   <c:v>147.57</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>147.57</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>147.57</c:v>
                 </c:pt>
               </c:numCache>
@@ -2038,11 +2092,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39917441"/>
-        <c:axId val="23533461"/>
+        <c:axId val="49348958"/>
+        <c:axId val="47976304"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39917441"/>
+        <c:axId val="49348958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2108,7 +2162,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23533461"/>
+        <c:crossAx val="47976304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2116,7 +2170,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23533461"/>
+        <c:axId val="47976304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2192,7 +2246,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39917441"/>
+        <c:crossAx val="49348958"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2293,7 +2347,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!B94</c:f>
+              <c:f>Generali!B97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2343,9 +2397,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$95:$A$103</c:f>
+              <c:f>Generali!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2372,16 +2426,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$95:$B$103</c:f>
+              <c:f>Generali!$B$98:$B$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>199.86</c:v>
                 </c:pt>
@@ -2407,6 +2464,9 @@
                   <c:v>199.86</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>199.86</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>199.86</c:v>
                 </c:pt>
               </c:numCache>
@@ -2419,7 +2479,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!C94</c:f>
+              <c:f>Generali!C97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2469,9 +2529,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$95:$A$103</c:f>
+              <c:f>Generali!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2498,16 +2558,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$95:$C$103</c:f>
+              <c:f>Generali!$C$98:$C$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>211.29</c:v>
                 </c:pt>
@@ -2533,6 +2596,9 @@
                   <c:v>211.29</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>211.29</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>211.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -2545,7 +2611,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Generali!D94</c:f>
+              <c:f>Generali!D97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2595,9 +2661,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$95:$A$103</c:f>
+              <c:f>Generali!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -2624,16 +2690,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$95:$D$103</c:f>
+              <c:f>Generali!$D$98:$D$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>195.16</c:v>
                 </c:pt>
@@ -2659,6 +2728,9 @@
                   <c:v>195.16</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>195.16</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>195.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -2674,11 +2746,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83438028"/>
-        <c:axId val="3044851"/>
+        <c:axId val="53040419"/>
+        <c:axId val="24870864"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83438028"/>
+        <c:axId val="53040419"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2744,7 +2816,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3044851"/>
+        <c:crossAx val="24870864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2752,7 +2824,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3044851"/>
+        <c:axId val="24870864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2828,7 +2900,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83438028"/>
+        <c:crossAx val="53040419"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2979,9 +3051,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3008,16 +3080,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>121.09</c:v>
                 </c:pt>
@@ -3043,6 +3118,9 @@
                   <c:v>121.09</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>121.09</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>121.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -3105,9 +3183,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3134,16 +3212,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>98.77</c:v>
                 </c:pt>
@@ -3169,6 +3250,9 @@
                   <c:v>98.77</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>98.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>98.77</c:v>
                 </c:pt>
               </c:numCache>
@@ -3231,9 +3315,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3260,16 +3344,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$13</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$5:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>86.02</c:v>
                 </c:pt>
@@ -3295,6 +3382,9 @@
                   <c:v>86.02</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>86.02</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>86.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -3310,11 +3400,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="59369693"/>
-        <c:axId val="75124079"/>
+        <c:axId val="98760531"/>
+        <c:axId val="15717325"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="59369693"/>
+        <c:axId val="98760531"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3380,7 +3470,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75124079"/>
+        <c:crossAx val="15717325"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3388,7 +3478,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75124079"/>
+        <c:axId val="15717325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3464,7 +3554,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59369693"/>
+        <c:crossAx val="98760531"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3565,7 +3655,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B34</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3615,9 +3705,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$35:$A$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3644,16 +3734,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$35:$B$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$36:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>95.79</c:v>
                 </c:pt>
@@ -3679,6 +3772,9 @@
                   <c:v>95.79</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>95.79</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>95.79</c:v>
                 </c:pt>
               </c:numCache>
@@ -3691,7 +3787,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C34</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3741,9 +3837,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$35:$A$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3770,16 +3866,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$35:$C$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$36:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>79.6</c:v>
                 </c:pt>
@@ -3805,6 +3904,9 @@
                   <c:v>79.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>79.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>79.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3817,7 +3919,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D34</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3867,9 +3969,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$35:$A$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -3896,16 +3998,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$35:$D$43</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$36:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>69.52</c:v>
                 </c:pt>
@@ -3931,6 +4036,9 @@
                   <c:v>69.52</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>69.52</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>69.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -3946,11 +4054,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="13862246"/>
-        <c:axId val="64662131"/>
+        <c:axId val="73198260"/>
+        <c:axId val="1693915"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="13862246"/>
+        <c:axId val="73198260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4016,7 +4124,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64662131"/>
+        <c:crossAx val="1693915"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4024,7 +4132,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64662131"/>
+        <c:axId val="1693915"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4100,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13862246"/>
+        <c:crossAx val="73198260"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4201,7 +4309,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B64</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4251,9 +4359,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$65:$A$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4280,16 +4388,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$65:$B$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$67:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>145.65</c:v>
                 </c:pt>
@@ -4315,6 +4426,9 @@
                   <c:v>145.65</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>145.65</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>145.65</c:v>
                 </c:pt>
               </c:numCache>
@@ -4327,7 +4441,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C64</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4377,9 +4491,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$65:$A$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4406,16 +4520,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$65:$C$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$67:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>115.11</c:v>
                 </c:pt>
@@ -4441,6 +4558,9 @@
                   <c:v>115.11</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>115.11</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>115.11</c:v>
                 </c:pt>
               </c:numCache>
@@ -4453,7 +4573,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D64</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4503,9 +4623,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$65:$A$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4532,16 +4652,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$65:$D$73</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$67:$D$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>92.59</c:v>
                 </c:pt>
@@ -4567,6 +4690,9 @@
                   <c:v>92.59</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>92.59</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>92.59</c:v>
                 </c:pt>
               </c:numCache>
@@ -4582,11 +4708,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="65059524"/>
-        <c:axId val="33026495"/>
+        <c:axId val="11531830"/>
+        <c:axId val="74479039"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="65059524"/>
+        <c:axId val="11531830"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4652,7 +4778,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33026495"/>
+        <c:crossAx val="74479039"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4660,7 +4786,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33026495"/>
+        <c:axId val="74479039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4736,7 +4862,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65059524"/>
+        <c:crossAx val="11531830"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4837,7 +4963,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!B94</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!B97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4887,9 +5013,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$95:$A$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -4916,16 +5042,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$B$95:$B$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$B$98:$B$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>213.4</c:v>
                 </c:pt>
@@ -4951,6 +5080,9 @@
                   <c:v>213.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>213.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4963,7 +5095,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!C94</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!C97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5013,9 +5145,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$95:$A$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5042,16 +5174,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$C$95:$C$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$C$98:$C$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>165.4</c:v>
                 </c:pt>
@@ -5077,6 +5212,9 @@
                   <c:v>165.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>165.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>165.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -5089,7 +5227,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!D94</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!D97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5139,9 +5277,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$A$95:$A$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5168,16 +5306,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'KOMUNÁLNA poisťovňa'!$D$95:$D$103</c:f>
+              <c:f>'KOMUNÁLNA poisťovňa'!$D$98:$D$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>132.4</c:v>
                 </c:pt>
@@ -5203,6 +5344,9 @@
                   <c:v>132.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>132.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>132.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -5218,11 +5362,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40064580"/>
-        <c:axId val="37131012"/>
+        <c:axId val="48867841"/>
+        <c:axId val="96104077"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40064580"/>
+        <c:axId val="48867841"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5288,7 +5432,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37131012"/>
+        <c:crossAx val="96104077"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5296,7 +5440,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37131012"/>
+        <c:axId val="96104077"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5372,7 +5516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40064580"/>
+        <c:crossAx val="48867841"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5523,9 +5667,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5552,16 +5696,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>138.66</c:v>
                 </c:pt>
@@ -5587,6 +5734,9 @@
                   <c:v>138.66</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>138.66</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>138.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -5649,9 +5799,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5678,16 +5828,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>108.81</c:v>
                 </c:pt>
@@ -5713,6 +5866,9 @@
                   <c:v>108.81</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>108.81</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>108.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -5775,9 +5931,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -5804,16 +5960,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$13</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$5:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>93.73</c:v>
                 </c:pt>
@@ -5839,6 +5998,9 @@
                   <c:v>93.73</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>93.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>93.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -5854,11 +6016,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="27897726"/>
-        <c:axId val="24708341"/>
+        <c:axId val="71787011"/>
+        <c:axId val="21806921"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27897726"/>
+        <c:axId val="71787011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5924,7 +6086,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24708341"/>
+        <c:crossAx val="21806921"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5932,7 +6094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24708341"/>
+        <c:axId val="21806921"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6008,7 +6170,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27897726"/>
+        <c:crossAx val="71787011"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6109,7 +6271,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B34</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6159,9 +6321,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$35:$A$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6188,16 +6350,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$35:$B$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$36:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>106.3</c:v>
                 </c:pt>
@@ -6223,6 +6388,9 @@
                   <c:v>106.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>106.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -6235,7 +6403,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C34</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6285,9 +6453,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$35:$A$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6314,16 +6482,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$35:$C$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$36:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>84.8</c:v>
                 </c:pt>
@@ -6349,6 +6520,9 @@
                   <c:v>84.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>84.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>84.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -6361,7 +6535,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D34</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6411,9 +6585,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$35:$A$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6440,16 +6614,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$35:$D$43</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$36:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>73.49</c:v>
                 </c:pt>
@@ -6475,6 +6652,9 @@
                   <c:v>73.49</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>73.49</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>73.49</c:v>
                 </c:pt>
               </c:numCache>
@@ -6490,11 +6670,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10313735"/>
-        <c:axId val="6842859"/>
+        <c:axId val="71950523"/>
+        <c:axId val="17682495"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10313735"/>
+        <c:axId val="71950523"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6560,7 +6740,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6842859"/>
+        <c:crossAx val="17682495"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6568,7 +6748,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6842859"/>
+        <c:axId val="17682495"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6644,7 +6824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10313735"/>
+        <c:crossAx val="71950523"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6745,7 +6925,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B64</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6795,9 +6975,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$65:$A$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6824,16 +7004,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$65:$B$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$67:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>167.04</c:v>
                 </c:pt>
@@ -6856,6 +7039,9 @@
                   <c:v>167.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>167.04</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>167.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -6868,7 +7054,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C64</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6918,9 +7104,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$65:$A$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -6947,16 +7133,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$65:$C$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$67:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>128.08</c:v>
                 </c:pt>
@@ -6982,6 +7171,9 @@
                   <c:v>128.08</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>128.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>128.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -6994,7 +7186,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D64</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7044,9 +7236,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$65:$A$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7073,16 +7265,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$65:$D$73</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$67:$D$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>109.23</c:v>
                 </c:pt>
@@ -7108,6 +7303,9 @@
                   <c:v>109.23</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>109.23</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>109.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -7123,11 +7321,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="460397"/>
-        <c:axId val="81093901"/>
+        <c:axId val="43978017"/>
+        <c:axId val="99884225"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="460397"/>
+        <c:axId val="43978017"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7193,7 +7391,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81093901"/>
+        <c:crossAx val="99884225"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7201,7 +7399,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81093901"/>
+        <c:axId val="99884225"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7277,7 +7475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460397"/>
+        <c:crossAx val="43978017"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7378,7 +7576,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B33</c:f>
+              <c:f>Allianz!B34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7428,9 +7626,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$34:$A$41</c:f>
+              <c:f>Allianz!$A$35:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7454,16 +7652,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$34:$B$41</c:f>
+              <c:f>Allianz!$B$35:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>49.36</c:v>
                 </c:pt>
@@ -7486,6 +7687,9 @@
                   <c:v>49.36</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>49.36</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>49.36</c:v>
                 </c:pt>
               </c:numCache>
@@ -7498,7 +7702,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C33</c:f>
+              <c:f>Allianz!C34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7548,9 +7752,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$34:$A$41</c:f>
+              <c:f>Allianz!$A$35:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7574,16 +7778,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$34:$C$41</c:f>
+              <c:f>Allianz!$C$35:$C$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>93.24</c:v>
                 </c:pt>
@@ -7606,6 +7813,9 @@
                   <c:v>93.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>93.24</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>93.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -7618,7 +7828,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D33</c:f>
+              <c:f>Allianz!D34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7668,9 +7878,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$34:$A$41</c:f>
+              <c:f>Allianz!$A$35:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -7694,16 +7904,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$34:$D$41</c:f>
+              <c:f>Allianz!$D$35:$D$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>119.52</c:v>
                 </c:pt>
@@ -7726,6 +7939,9 @@
                   <c:v>119.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>119.52</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>119.52</c:v>
                 </c:pt>
               </c:numCache>
@@ -7741,11 +7957,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82594453"/>
-        <c:axId val="31738588"/>
+        <c:axId val="79114488"/>
+        <c:axId val="55846871"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82594453"/>
+        <c:axId val="79114488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7811,7 +8027,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31738588"/>
+        <c:crossAx val="55846871"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7819,7 +8035,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31738588"/>
+        <c:axId val="55846871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7895,7 +8111,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82594453"/>
+        <c:crossAx val="79114488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7996,7 +8212,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!B94</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!B97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8046,9 +8262,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$95:$A$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -8075,16 +8291,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$B$95:$B$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$B$98:$B$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>233.26</c:v>
                 </c:pt>
@@ -8110,6 +8329,9 @@
                   <c:v>233.26</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>233.26</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>233.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -8122,7 +8344,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!C94</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!C97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8172,9 +8394,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$95:$A$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -8201,16 +8423,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$C$95:$C$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$C$98:$C$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>177.26</c:v>
                 </c:pt>
@@ -8236,6 +8461,9 @@
                   <c:v>177.26</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>177.26</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>177.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -8248,7 +8476,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!D94</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!D97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8298,9 +8526,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$A$95:$A$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -8327,16 +8555,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Kooperativa (Bezstarostný domov'!$D$95:$D$103</c:f>
+              <c:f>'Kooperativa (Bezstarostný domov'!$D$98:$D$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>148.98</c:v>
                 </c:pt>
@@ -8362,6 +8593,9 @@
                   <c:v>148.98</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>148.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>148.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -8377,11 +8611,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31235091"/>
-        <c:axId val="9131562"/>
+        <c:axId val="49406054"/>
+        <c:axId val="72334092"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31235091"/>
+        <c:axId val="49406054"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8447,7 +8681,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9131562"/>
+        <c:crossAx val="72334092"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8455,7 +8689,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9131562"/>
+        <c:axId val="72334092"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8531,7 +8765,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31235091"/>
+        <c:crossAx val="49406054"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8875,11 +9109,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58909648"/>
-        <c:axId val="56335503"/>
+        <c:axId val="53499428"/>
+        <c:axId val="3591430"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58909648"/>
+        <c:axId val="53499428"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8945,7 +9179,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56335503"/>
+        <c:crossAx val="3591430"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8953,7 +9187,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56335503"/>
+        <c:axId val="3591430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9029,7 +9263,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58909648"/>
+        <c:crossAx val="53499428"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9373,11 +9607,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54533535"/>
-        <c:axId val="38355584"/>
+        <c:axId val="24204703"/>
+        <c:axId val="42134120"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54533535"/>
+        <c:axId val="24204703"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9443,7 +9677,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38355584"/>
+        <c:crossAx val="42134120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9451,7 +9685,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38355584"/>
+        <c:axId val="42134120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9527,7 +9761,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54533535"/>
+        <c:crossAx val="24204703"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9871,11 +10105,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2822962"/>
-        <c:axId val="25028585"/>
+        <c:axId val="58594743"/>
+        <c:axId val="22838269"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2822962"/>
+        <c:axId val="58594743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9941,7 +10175,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25028585"/>
+        <c:crossAx val="22838269"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9949,7 +10183,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25028585"/>
+        <c:axId val="22838269"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10025,7 +10259,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2822962"/>
+        <c:crossAx val="58594743"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10369,11 +10603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="33467914"/>
-        <c:axId val="77914452"/>
+        <c:axId val="34566499"/>
+        <c:axId val="43517902"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33467914"/>
+        <c:axId val="34566499"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10439,7 +10673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77914452"/>
+        <c:crossAx val="43517902"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10447,7 +10681,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77914452"/>
+        <c:axId val="43517902"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10523,7 +10757,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33467914"/>
+        <c:crossAx val="34566499"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10674,9 +10908,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$13</c:f>
+              <c:f>Union!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10703,16 +10937,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$5:$B$13</c:f>
+              <c:f>Union!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>151.45</c:v>
                 </c:pt>
@@ -10738,6 +10975,9 @@
                   <c:v>151.45</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>151.45</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>151.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -10800,9 +11040,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$5:$A$13</c:f>
+              <c:f>Union!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -10829,16 +11069,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$5:$C$13</c:f>
+              <c:f>Union!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>49.98</c:v>
                 </c:pt>
@@ -10864,6 +11107,9 @@
                   <c:v>49.98</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>49.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>49.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -10879,11 +11125,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47059580"/>
-        <c:axId val="8316025"/>
+        <c:axId val="40934802"/>
+        <c:axId val="67393465"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47059580"/>
+        <c:axId val="40934802"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10949,7 +11195,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8316025"/>
+        <c:crossAx val="67393465"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10957,7 +11203,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8316025"/>
+        <c:axId val="67393465"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11033,7 +11279,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47059580"/>
+        <c:crossAx val="40934802"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11134,7 +11380,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B34</c:f>
+              <c:f>Union!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11184,9 +11430,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$35:$A$43</c:f>
+              <c:f>Union!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11213,16 +11459,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$35:$B$43</c:f>
+              <c:f>Union!$B$36:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>120.23</c:v>
                 </c:pt>
@@ -11248,6 +11497,9 @@
                   <c:v>120.23</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>120.23</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>120.23</c:v>
                 </c:pt>
               </c:numCache>
@@ -11260,7 +11512,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C34</c:f>
+              <c:f>Union!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11310,9 +11562,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$35:$A$43</c:f>
+              <c:f>Union!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11339,16 +11591,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$35:$C$43</c:f>
+              <c:f>Union!$C$36:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>39.68</c:v>
                 </c:pt>
@@ -11374,6 +11629,9 @@
                   <c:v>39.68</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>39.68</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>39.68</c:v>
                 </c:pt>
               </c:numCache>
@@ -11389,11 +11647,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10374778"/>
-        <c:axId val="8680126"/>
+        <c:axId val="52525750"/>
+        <c:axId val="98926405"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10374778"/>
+        <c:axId val="52525750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11459,7 +11717,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8680126"/>
+        <c:crossAx val="98926405"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11467,7 +11725,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8680126"/>
+        <c:axId val="98926405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11543,7 +11801,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10374778"/>
+        <c:crossAx val="52525750"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11644,7 +11902,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B64</c:f>
+              <c:f>Union!B66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11694,9 +11952,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$65:$A$73</c:f>
+              <c:f>Union!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11723,16 +11981,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$65:$B$73</c:f>
+              <c:f>Union!$B$67:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>206.12</c:v>
                 </c:pt>
@@ -11758,6 +12019,9 @@
                   <c:v>206.12</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>206.12</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>206.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -11770,7 +12034,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C64</c:f>
+              <c:f>Union!C66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11820,9 +12084,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$65:$A$73</c:f>
+              <c:f>Union!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -11849,16 +12113,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$65:$C$73</c:f>
+              <c:f>Union!$C$67:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>68.04</c:v>
                 </c:pt>
@@ -11884,6 +12151,9 @@
                   <c:v>68.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>68.04</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>68.04</c:v>
                 </c:pt>
               </c:numCache>
@@ -11899,11 +12169,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58842912"/>
-        <c:axId val="65884701"/>
+        <c:axId val="64165753"/>
+        <c:axId val="383171"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58842912"/>
+        <c:axId val="64165753"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11969,7 +12239,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65884701"/>
+        <c:crossAx val="383171"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11977,7 +12247,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65884701"/>
+        <c:axId val="383171"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12053,7 +12323,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58842912"/>
+        <c:crossAx val="64165753"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12154,7 +12424,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!B94</c:f>
+              <c:f>Union!B97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12204,9 +12474,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$95:$A$103</c:f>
+              <c:f>Union!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12233,16 +12503,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$B$95:$B$103</c:f>
+              <c:f>Union!$B$98:$B$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>286.39</c:v>
                 </c:pt>
@@ -12268,6 +12541,9 @@
                   <c:v>286.39</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>286.39</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>286.39</c:v>
                 </c:pt>
               </c:numCache>
@@ -12280,7 +12556,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Union!C94</c:f>
+              <c:f>Union!C97</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12330,9 +12606,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Union!$A$95:$A$103</c:f>
+              <c:f>Union!$A$98:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12359,16 +12635,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Union!$C$95:$C$103</c:f>
+              <c:f>Union!$C$98:$C$107</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>94.53</c:v>
                 </c:pt>
@@ -12394,6 +12673,9 @@
                   <c:v>94.53</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>94.53</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>94.53</c:v>
                 </c:pt>
               </c:numCache>
@@ -12409,11 +12691,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="93580909"/>
-        <c:axId val="38301115"/>
+        <c:axId val="93428456"/>
+        <c:axId val="81371530"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="93580909"/>
+        <c:axId val="93428456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12479,7 +12761,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38301115"/>
+        <c:crossAx val="81371530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12487,7 +12769,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38301115"/>
+        <c:axId val="81371530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12563,7 +12845,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93580909"/>
+        <c:crossAx val="93428456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12714,9 +12996,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12743,16 +13025,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>144.96</c:v>
                 </c:pt>
@@ -12778,6 +13063,9 @@
                   <c:v>144.96</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>144.96</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>144.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -12840,9 +13128,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12869,16 +13157,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>167.64</c:v>
                 </c:pt>
@@ -12904,6 +13195,9 @@
                   <c:v>167.64</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>167.64</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>167.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -12966,9 +13260,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -12995,16 +13289,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$13</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$5:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>126.12</c:v>
                 </c:pt>
@@ -13030,6 +13327,9 @@
                   <c:v>126.12</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>126.12</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>126.12</c:v>
                 </c:pt>
               </c:numCache>
@@ -13045,11 +13345,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78309642"/>
-        <c:axId val="88594282"/>
+        <c:axId val="649275"/>
+        <c:axId val="90516359"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78309642"/>
+        <c:axId val="649275"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13115,7 +13415,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88594282"/>
+        <c:crossAx val="90516359"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13123,7 +13423,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88594282"/>
+        <c:axId val="90516359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13199,7 +13499,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78309642"/>
+        <c:crossAx val="649275"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13300,7 +13600,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B62</c:f>
+              <c:f>Allianz!B64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13350,9 +13650,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$63:$A$70</c:f>
+              <c:f>Allianz!$A$65:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13376,16 +13676,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$63:$B$70</c:f>
+              <c:f>Allianz!$B$65:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>117.24</c:v>
                 </c:pt>
@@ -13408,6 +13711,9 @@
                   <c:v>117.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>117.24</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>117.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -13420,7 +13726,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C62</c:f>
+              <c:f>Allianz!C64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13470,9 +13776,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$63:$A$70</c:f>
+              <c:f>Allianz!$A$65:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13496,16 +13802,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$63:$C$70</c:f>
+              <c:f>Allianz!$C$65:$C$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>159</c:v>
                 </c:pt>
@@ -13528,6 +13837,9 @@
                   <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>159</c:v>
                 </c:pt>
               </c:numCache>
@@ -13540,7 +13852,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D62</c:f>
+              <c:f>Allianz!D64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13590,9 +13902,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$63:$A$70</c:f>
+              <c:f>Allianz!$A$65:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13616,16 +13928,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$63:$D$70</c:f>
+              <c:f>Allianz!$D$65:$D$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>206.64</c:v>
                 </c:pt>
@@ -13648,6 +13963,9 @@
                   <c:v>206.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>206.64</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>206.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -13663,11 +13981,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47401593"/>
-        <c:axId val="99750265"/>
+        <c:axId val="9878536"/>
+        <c:axId val="6432404"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47401593"/>
+        <c:axId val="9878536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13733,7 +14051,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99750265"/>
+        <c:crossAx val="6432404"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13741,7 +14059,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99750265"/>
+        <c:axId val="6432404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13817,7 +14135,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47401593"/>
+        <c:crossAx val="9878536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13918,7 +14236,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B34</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13968,9 +14286,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$35:$A$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -13997,16 +14315,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$35:$B$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$36:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>114.96</c:v>
                 </c:pt>
@@ -14032,6 +14353,9 @@
                   <c:v>114.96</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>114.96</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>114.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -14044,7 +14368,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C34</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14094,9 +14418,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$35:$A$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14123,16 +14447,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$35:$C$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$36:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>132.84</c:v>
                 </c:pt>
@@ -14158,6 +14485,9 @@
                   <c:v>132.84</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>132.84</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>132.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -14170,7 +14500,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D34</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14220,9 +14550,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$35:$A$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$36:$A$45</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14249,16 +14579,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$35:$D$43</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$36:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>100.08</c:v>
                 </c:pt>
@@ -14284,6 +14617,9 @@
                   <c:v>100.08</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>100.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>100.08</c:v>
                 </c:pt>
               </c:numCache>
@@ -14299,11 +14635,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="70652716"/>
-        <c:axId val="90397390"/>
+        <c:axId val="37234870"/>
+        <c:axId val="43833977"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70652716"/>
+        <c:axId val="37234870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14369,7 +14705,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90397390"/>
+        <c:crossAx val="43833977"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14377,7 +14713,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90397390"/>
+        <c:axId val="43833977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14453,7 +14789,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70652716"/>
+        <c:crossAx val="37234870"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14554,7 +14890,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!B64</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!B66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14604,9 +14940,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$65:$A$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14633,16 +14969,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$B$65:$B$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$B$67:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>174.72</c:v>
                 </c:pt>
@@ -14668,6 +15007,9 @@
                   <c:v>174.72</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>174.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>174.72</c:v>
                 </c:pt>
               </c:numCache>
@@ -14680,7 +15022,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!C64</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!C66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14730,9 +15072,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$65:$A$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14759,16 +15101,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$C$65:$C$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$C$67:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>194.76</c:v>
                 </c:pt>
@@ -14794,6 +15139,9 @@
                   <c:v>194.76</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>194.76</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>194.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -14806,7 +15154,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!D64</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!D66</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14856,9 +15204,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$A$65:$A$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$A$67:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -14885,16 +15233,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wüstenrot (W dobrom domov)'!$D$65:$D$73</c:f>
+              <c:f>'Wüstenrot (W dobrom domov)'!$D$67:$D$76</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>152.16</c:v>
                 </c:pt>
@@ -14920,6 +15271,9 @@
                   <c:v>152.16</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>152.16</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>152.16</c:v>
                 </c:pt>
               </c:numCache>
@@ -14935,11 +15289,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71033584"/>
-        <c:axId val="29042011"/>
+        <c:axId val="69553090"/>
+        <c:axId val="63227931"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71033584"/>
+        <c:axId val="69553090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15005,7 +15359,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29042011"/>
+        <c:crossAx val="63227931"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15013,7 +15367,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29042011"/>
+        <c:axId val="63227931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15089,7 +15443,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71033584"/>
+        <c:crossAx val="69553090"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15240,9 +15594,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15269,16 +15623,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$5:$B$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>190.22</c:v>
                 </c:pt>
@@ -15305,6 +15662,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>171.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>190.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15366,9 +15726,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15395,16 +15755,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$5:$C$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>138.36</c:v>
                 </c:pt>
@@ -15431,6 +15794,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>124.53</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>138.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15492,9 +15858,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$5:$A$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -15521,16 +15887,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$5:$D$13</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$5:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>155.18</c:v>
                 </c:pt>
@@ -15557,6 +15926,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>139.66</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>155.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15571,11 +15943,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="17534773"/>
-        <c:axId val="6440856"/>
+        <c:axId val="29007971"/>
+        <c:axId val="56883310"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="17534773"/>
+        <c:axId val="29007971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15641,7 +16013,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6440856"/>
+        <c:crossAx val="56883310"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15649,7 +16021,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6440856"/>
+        <c:axId val="56883310"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15725,7 +16097,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17534773"/>
+        <c:crossAx val="29007971"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15826,7 +16198,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B34</c:f>
+              <c:f>'ČSOB Poisťovňa'!B35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15876,7 +16248,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$35:$A$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$36:$A$37</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -15890,7 +16262,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$35:$B$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$36:$B$37</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -15910,7 +16282,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C34</c:f>
+              <c:f>'ČSOB Poisťovňa'!C35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15960,7 +16332,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$35:$A$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$36:$A$37</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -15974,7 +16346,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$35:$C$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$36:$C$37</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -15994,7 +16366,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D34</c:f>
+              <c:f>'ČSOB Poisťovňa'!D35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16044,7 +16416,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$35:$A$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$36:$A$37</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -16058,7 +16430,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$35:$D$36</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$36:$D$37</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
@@ -16081,11 +16453,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="17416382"/>
-        <c:axId val="21009290"/>
+        <c:axId val="15882314"/>
+        <c:axId val="34429537"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="17416382"/>
+        <c:axId val="15882314"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16151,7 +16523,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21009290"/>
+        <c:crossAx val="34429537"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16159,7 +16531,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21009290"/>
+        <c:axId val="34429537"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16235,7 +16607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17416382"/>
+        <c:crossAx val="15882314"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16336,7 +16708,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B57</c:f>
+              <c:f>'ČSOB Poisťovňa'!B58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16386,9 +16758,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$58:$A$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$59:$A$68</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16415,16 +16787,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$58:$B$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$59:$B$68</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>216.18</c:v>
                 </c:pt>
@@ -16451,6 +16826,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>216.18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>194.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16462,7 +16840,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C57</c:f>
+              <c:f>'ČSOB Poisťovňa'!C58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16512,9 +16890,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$58:$A$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$59:$A$68</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16541,16 +16919,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$58:$C$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$59:$C$68</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>157.93</c:v>
                 </c:pt>
@@ -16577,6 +16958,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>157.93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>142.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16588,7 +16972,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D57</c:f>
+              <c:f>'ČSOB Poisťovňa'!D58</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -16638,9 +17022,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$58:$A$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$59:$A$68</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -16667,16 +17051,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$58:$D$66</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$59:$D$68</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>176.7</c:v>
                 </c:pt>
@@ -16703,6 +17090,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>176.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>159.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16717,11 +17107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61592427"/>
-        <c:axId val="78954340"/>
+        <c:axId val="14737107"/>
+        <c:axId val="59881843"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61592427"/>
+        <c:axId val="14737107"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16787,7 +17177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78954340"/>
+        <c:crossAx val="59881843"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16795,7 +17185,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78954340"/>
+        <c:axId val="59881843"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16871,7 +17261,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61592427"/>
+        <c:crossAx val="14737107"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16972,7 +17362,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!B87</c:f>
+              <c:f>'ČSOB Poisťovňa'!B89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17022,9 +17412,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$88:$A$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$90:$A$99</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17051,16 +17441,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$B$88:$B$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$B$90:$B$99</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>275.68</c:v>
                 </c:pt>
@@ -17086,6 +17479,9 @@
                   <c:v>306.32</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>275.68</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>275.68</c:v>
                 </c:pt>
               </c:numCache>
@@ -17098,7 +17494,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!C87</c:f>
+              <c:f>'ČSOB Poisťovňa'!C89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17148,9 +17544,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$88:$A$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$90:$A$99</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17177,16 +17573,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$C$88:$C$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$C$90:$C$99</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>202.39</c:v>
                 </c:pt>
@@ -17212,6 +17611,9 @@
                   <c:v>224.88</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>202.39</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>202.39</c:v>
                 </c:pt>
               </c:numCache>
@@ -17224,7 +17626,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!D87</c:f>
+              <c:f>'ČSOB Poisťovňa'!D89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17274,9 +17676,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'ČSOB Poisťovňa'!$A$88:$A$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$A$90:$A$99</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17303,16 +17705,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ČSOB Poisťovňa'!$D$88:$D$96</c:f>
+              <c:f>'ČSOB Poisťovňa'!$D$90:$D$99</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>225.85</c:v>
                 </c:pt>
@@ -17338,6 +17743,9 @@
                   <c:v>250.95</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>225.85</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>225.85</c:v>
                 </c:pt>
               </c:numCache>
@@ -17353,11 +17761,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40502525"/>
-        <c:axId val="32543893"/>
+        <c:axId val="79822599"/>
+        <c:axId val="94089597"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40502525"/>
+        <c:axId val="79822599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17423,7 +17831,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32543893"/>
+        <c:crossAx val="94089597"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17431,7 +17839,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32543893"/>
+        <c:axId val="94089597"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17507,7 +17915,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40502525"/>
+        <c:crossAx val="79822599"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17608,7 +18016,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!B91</c:f>
+              <c:f>Allianz!B94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17658,9 +18066,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$92:$A$99</c:f>
+              <c:f>Allianz!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17684,16 +18092,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$B$92:$B$99</c:f>
+              <c:f>Allianz!$B$95:$B$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>158.64</c:v>
                 </c:pt>
@@ -17716,6 +18127,9 @@
                   <c:v>158.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>158.64</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>158.64</c:v>
                 </c:pt>
               </c:numCache>
@@ -17728,7 +18142,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!C91</c:f>
+              <c:f>Allianz!C94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17778,9 +18192,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$92:$A$99</c:f>
+              <c:f>Allianz!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17804,16 +18218,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$C$92:$C$99</c:f>
+              <c:f>Allianz!$C$95:$C$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>216.84</c:v>
                 </c:pt>
@@ -17836,6 +18253,9 @@
                   <c:v>216.84</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>216.84</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>216.84</c:v>
                 </c:pt>
               </c:numCache>
@@ -17848,7 +18268,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Allianz!D91</c:f>
+              <c:f>Allianz!D94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -17898,9 +18318,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Allianz!$A$92:$A$99</c:f>
+              <c:f>Allianz!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -17924,16 +18344,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Allianz!$D$92:$D$99</c:f>
+              <c:f>Allianz!$D$95:$D$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>277.2</c:v>
                 </c:pt>
@@ -17956,6 +18379,9 @@
                   <c:v>277.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>277.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>277.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -17971,11 +18397,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31557757"/>
-        <c:axId val="70172394"/>
+        <c:axId val="53432435"/>
+        <c:axId val="64367136"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31557757"/>
+        <c:axId val="53432435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18041,7 +18467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70172394"/>
+        <c:crossAx val="64367136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -18049,7 +18475,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70172394"/>
+        <c:axId val="64367136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18125,7 +18551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31557757"/>
+        <c:crossAx val="53432435"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18589,11 +19015,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="11856855"/>
-        <c:axId val="65729651"/>
+        <c:axId val="21801137"/>
+        <c:axId val="49784390"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11856855"/>
+        <c:axId val="21801137"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18659,7 +19085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65729651"/>
+        <c:crossAx val="49784390"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -18667,7 +19093,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65729651"/>
+        <c:axId val="49784390"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18743,7 +19169,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11856855"/>
+        <c:crossAx val="21801137"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18894,9 +19320,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$34:$A$42</c:f>
+              <c:f>Colonnade!$A$34:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -18923,16 +19349,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$34:$B$42</c:f>
+              <c:f>Colonnade!$B$34:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>142.75</c:v>
                 </c:pt>
@@ -18958,6 +19387,9 @@
                   <c:v>142.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>142.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>142.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -19020,9 +19452,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$34:$A$42</c:f>
+              <c:f>Colonnade!$A$34:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -19049,16 +19481,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$34:$C$42</c:f>
+              <c:f>Colonnade!$C$34:$C$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>191.67</c:v>
                 </c:pt>
@@ -19084,6 +19519,9 @@
                   <c:v>191.67</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>191.67</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>191.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -19146,9 +19584,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$34:$A$42</c:f>
+              <c:f>Colonnade!$A$34:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -19175,16 +19613,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$34:$D$42</c:f>
+              <c:f>Colonnade!$D$34:$D$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>186.44</c:v>
                 </c:pt>
@@ -19210,6 +19651,9 @@
                   <c:v>186.44</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>186.44</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>186.44</c:v>
                 </c:pt>
               </c:numCache>
@@ -19225,11 +19669,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="45031029"/>
-        <c:axId val="76581895"/>
+        <c:axId val="39520039"/>
+        <c:axId val="70940808"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="45031029"/>
+        <c:axId val="39520039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19295,7 +19739,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76581895"/>
+        <c:crossAx val="70940808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19303,7 +19747,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76581895"/>
+        <c:axId val="70940808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19379,7 +19823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45031029"/>
+        <c:crossAx val="39520039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19480,7 +19924,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B63</c:f>
+              <c:f>Colonnade!B64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -19530,7 +19974,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$64:$A$72</c:f>
+              <c:f>Colonnade!$A$65:$A$73</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -19565,7 +20009,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$64:$B$72</c:f>
+              <c:f>Colonnade!$B$65:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="9"/>
@@ -19606,7 +20050,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C63</c:f>
+              <c:f>Colonnade!C64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -19656,7 +20100,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$64:$A$72</c:f>
+              <c:f>Colonnade!$A$65:$A$73</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -19691,7 +20135,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$64:$C$72</c:f>
+              <c:f>Colonnade!$C$65:$C$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="9"/>
@@ -19732,7 +20176,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D63</c:f>
+              <c:f>Colonnade!D64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -19782,7 +20226,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$64:$A$72</c:f>
+              <c:f>Colonnade!$A$65:$A$73</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -19817,7 +20261,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$64:$D$72</c:f>
+              <c:f>Colonnade!$D$65:$D$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="9"/>
@@ -19861,11 +20305,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="1798856"/>
-        <c:axId val="58127399"/>
+        <c:axId val="8642444"/>
+        <c:axId val="42107394"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1798856"/>
+        <c:axId val="8642444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19931,7 +20375,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58127399"/>
+        <c:crossAx val="42107394"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19939,7 +20383,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58127399"/>
+        <c:axId val="42107394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20015,7 +20459,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1798856"/>
+        <c:crossAx val="8642444"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20116,7 +20560,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!B93</c:f>
+              <c:f>Colonnade!B94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -20166,9 +20610,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$94:$A$101</c:f>
+              <c:f>Colonnade!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -20192,16 +20636,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$B$94:$B$101</c:f>
+              <c:f>Colonnade!$B$95:$B$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>254.31</c:v>
                 </c:pt>
@@ -20224,6 +20671,9 @@
                   <c:v>254.31</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>254.31</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>254.31</c:v>
                 </c:pt>
               </c:numCache>
@@ -20236,7 +20686,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!C93</c:f>
+              <c:f>Colonnade!C94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -20286,9 +20736,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$94:$A$101</c:f>
+              <c:f>Colonnade!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -20312,16 +20762,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$C$94:$C$101</c:f>
+              <c:f>Colonnade!$C$95:$C$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>347.42</c:v>
                 </c:pt>
@@ -20344,6 +20797,9 @@
                   <c:v>347.42</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>347.42</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>347.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -20356,7 +20812,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Colonnade!D93</c:f>
+              <c:f>Colonnade!D94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -20406,9 +20862,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Colonnade!$A$94:$A$101</c:f>
+              <c:f>Colonnade!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -20432,16 +20888,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Colonnade!$D$94:$D$101</c:f>
+              <c:f>Colonnade!$D$95:$D$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>337.73</c:v>
                 </c:pt>
@@ -20464,6 +20923,9 @@
                   <c:v>337.73</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>337.73</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>337.73</c:v>
                 </c:pt>
               </c:numCache>
@@ -20479,11 +20941,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24018091"/>
-        <c:axId val="74371482"/>
+        <c:axId val="19861238"/>
+        <c:axId val="21534618"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24018091"/>
+        <c:axId val="19861238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20549,7 +21011,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74371482"/>
+        <c:crossAx val="21534618"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20557,7 +21019,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74371482"/>
+        <c:axId val="21534618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20633,7 +21095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24018091"/>
+        <c:crossAx val="19861238"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20784,9 +21246,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$13</c:f>
+              <c:f>Generali!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -20813,16 +21275,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$B$5:$B$13</c:f>
+              <c:f>Generali!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>99.41</c:v>
                 </c:pt>
@@ -20848,6 +21313,9 @@
                   <c:v>99.41</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>99.41</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>99.41</c:v>
                 </c:pt>
               </c:numCache>
@@ -20910,9 +21378,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$13</c:f>
+              <c:f>Generali!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -20939,16 +21407,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$C$5:$C$13</c:f>
+              <c:f>Generali!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>114.74</c:v>
                 </c:pt>
@@ -20974,6 +21445,9 @@
                   <c:v>114.74</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>114.74</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>114.74</c:v>
                 </c:pt>
               </c:numCache>
@@ -21036,9 +21510,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Generali!$A$5:$A$13</c:f>
+              <c:f>Generali!$A$5:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>15.10.2026</c:v>
                 </c:pt>
@@ -21065,16 +21539,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Generali!$D$5:$D$13</c:f>
+              <c:f>Generali!$D$5:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>94.81</c:v>
                 </c:pt>
@@ -21100,6 +21577,9 @@
                   <c:v>94.81</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>94.81</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>94.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -21115,11 +21595,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="87248321"/>
-        <c:axId val="24753642"/>
+        <c:axId val="93212134"/>
+        <c:axId val="5166403"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="87248321"/>
+        <c:axId val="93212134"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21185,7 +21665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24753642"/>
+        <c:crossAx val="5166403"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -21193,7 +21673,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24753642"/>
+        <c:axId val="5166403"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21269,7 +21749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87248321"/>
+        <c:crossAx val="93212134"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21357,14 +21837,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -21372,7 +21852,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6095880"/>
+        <a:off x="4558680" y="6286680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21387,14 +21867,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -21402,7 +21882,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="11620440"/>
+        <a:off x="4558680" y="12001680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21417,13 +21897,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21432,7 +21912,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="17145000"/>
+        <a:off x="4558680" y="17716680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21512,14 +21992,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -21527,7 +22007,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="11810880"/>
+        <a:off x="4558680" y="12001680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21542,14 +22022,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -21557,7 +22037,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="17525880"/>
+        <a:off x="4558680" y="17716680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21607,13 +22087,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21622,7 +22102,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6286680"/>
+        <a:off x="4558680" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21637,13 +22117,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21652,7 +22132,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="12001680"/>
+        <a:off x="4558680" y="12382560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21667,13 +22147,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21682,7 +22162,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="17716680"/>
+        <a:off x="4558680" y="18288000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21732,13 +22212,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21747,7 +22227,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6286680"/>
+        <a:off x="4558680" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21762,13 +22242,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21777,7 +22257,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="12001680"/>
+        <a:off x="4558680" y="12382560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21792,13 +22272,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21807,7 +22287,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="17716680"/>
+        <a:off x="4558680" y="18288000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21857,13 +22337,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21872,7 +22352,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6286680"/>
+        <a:off x="4558680" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21887,13 +22367,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21902,7 +22382,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="12001680"/>
+        <a:off x="4558680" y="12382560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -21917,13 +22397,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -21932,7 +22412,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="17716680"/>
+        <a:off x="4558680" y="18288000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22107,13 +22587,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22122,7 +22602,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="6286680"/>
+        <a:off x="3571920" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22137,13 +22617,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22152,7 +22632,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="12001680"/>
+        <a:off x="3571920" y="12382560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22167,13 +22647,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22182,7 +22662,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="17716680"/>
+        <a:off x="3571920" y="18288000"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22232,13 +22712,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22247,7 +22727,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6286680"/>
+        <a:off x="4558680" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22262,13 +22742,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22277,7 +22757,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="12001680"/>
+        <a:off x="4558680" y="12382560"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22327,13 +22807,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -22342,7 +22822,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="6286680"/>
+        <a:off x="4558680" y="6477120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22357,14 +22837,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -22372,7 +22852,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="10667880"/>
+        <a:off x="4558680" y="10858680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22387,14 +22867,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -22402,7 +22882,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4558680" y="16382880"/>
+        <a:off x="4558680" y="16764120"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -22596,7 +23076,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -22738,42 +23218,42 @@
         <v>145.2</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>145.2</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>93.24</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>119.52</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>49.36</v>
@@ -22787,7 +23267,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>49.36</v>
@@ -22801,7 +23281,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>49.36</v>
@@ -22815,7 +23295,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>49.36</v>
@@ -22829,7 +23309,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>49.36</v>
@@ -22843,7 +23323,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>49.36</v>
@@ -22857,7 +23337,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>49.36</v>
@@ -22869,56 +23349,56 @@
         <v>119.52</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>119.52</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>93.24</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>119.52</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B64" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>117.24</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>206.64</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>117.24</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>206.64</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>117.24</v>
@@ -22932,7 +23412,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>117.24</v>
@@ -22946,7 +23426,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>117.24</v>
@@ -22960,7 +23440,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>117.24</v>
@@ -22974,7 +23454,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>117.24</v>
@@ -22988,7 +23468,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>117.24</v>
@@ -23000,70 +23480,70 @@
         <v>206.64</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>117.24</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>206.64</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>158.64</v>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>216.84</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>277.2</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>158.64</v>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>216.84</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>277.2</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>158.64</v>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>216.84</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>277.2</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>158.64</v>
@@ -23077,7 +23557,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>158.64</v>
@@ -23091,7 +23571,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>158.64</v>
@@ -23105,7 +23585,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>158.64</v>
@@ -23119,7 +23599,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>158.64</v>
@@ -23128,6 +23608,62 @@
         <v>216.84</v>
       </c>
       <c r="D99" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>158.64</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="D103" s="5" t="n">
         <v>277.2</v>
       </c>
     </row>
@@ -23148,7 +23684,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -23435,42 +23971,42 @@
         <v>186.44</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>186.44</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B64" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>246.96</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>240.14</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>182.53</v>
@@ -23484,7 +24020,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>182.53</v>
@@ -23498,7 +24034,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>182.53</v>
@@ -23512,7 +24048,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>182.53</v>
@@ -23526,7 +24062,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>182.53</v>
@@ -23540,7 +24076,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>182.53</v>
@@ -23554,7 +24090,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>182.53</v>
@@ -23568,7 +24104,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>182.53</v>
@@ -23580,42 +24116,42 @@
         <v>240.14</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>246.96</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>240.14</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="s">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>254.31</v>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>347.42</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>337.73</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>254.31</v>
@@ -23629,7 +24165,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>254.31</v>
@@ -23643,7 +24179,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>254.31</v>
@@ -23657,7 +24193,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>254.31</v>
@@ -23671,7 +24207,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>254.31</v>
@@ -23685,7 +24221,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>254.31</v>
@@ -23699,7 +24235,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>254.31</v>
@@ -23708,6 +24244,34 @@
         <v>347.42</v>
       </c>
       <c r="D101" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>337.73</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="D103" s="5" t="n">
         <v>337.73</v>
       </c>
     </row>
@@ -23728,7 +24292,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -23884,42 +24448,42 @@
         <v>94.81</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>94.81</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>77.55</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>92.26</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>73.19</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>77.55</v>
@@ -23933,7 +24497,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>77.55</v>
@@ -23947,7 +24511,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>77.55</v>
@@ -23961,7 +24525,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>77.55</v>
@@ -23975,7 +24539,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>77.55</v>
@@ -23989,7 +24553,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>77.55</v>
@@ -24003,7 +24567,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>77.55</v>
@@ -24017,7 +24581,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>77.55</v>
@@ -24029,56 +24593,56 @@
         <v>73.19</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>147.57</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>152.27</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>147.57</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>152.27</v>
@@ -24092,7 +24656,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>152.27</v>
@@ -24106,7 +24670,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>152.27</v>
@@ -24120,7 +24684,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>152.27</v>
@@ -24134,7 +24698,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>152.27</v>
@@ -24148,7 +24712,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>152.27</v>
@@ -24162,7 +24726,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>152.27</v>
@@ -24174,70 +24738,70 @@
         <v>147.57</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>152.27</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>147.57</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>195.16</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>195.16</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>199.86</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>211.29</v>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>195.16</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>199.86</v>
@@ -24251,7 +24815,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>199.86</v>
@@ -24265,7 +24829,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>199.86</v>
@@ -24279,7 +24843,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>199.86</v>
@@ -24293,7 +24857,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>199.86</v>
@@ -24307,7 +24871,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>199.86</v>
@@ -24316,6 +24880,62 @@
         <v>211.29</v>
       </c>
       <c r="D103" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>195.16</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>211.29</v>
+      </c>
+      <c r="D107" s="5" t="n">
         <v>195.16</v>
       </c>
     </row>
@@ -24336,7 +24956,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -24492,42 +25112,42 @@
         <v>86.02</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>121.09</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>86.02</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>95.79</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>79.6</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>69.52</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>95.79</v>
@@ -24541,7 +25161,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>95.79</v>
@@ -24555,7 +25175,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>95.79</v>
@@ -24569,7 +25189,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>95.79</v>
@@ -24583,7 +25203,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>95.79</v>
@@ -24597,7 +25217,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>95.79</v>
@@ -24611,7 +25231,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>95.79</v>
@@ -24625,7 +25245,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>95.79</v>
@@ -24637,56 +25257,56 @@
         <v>69.52</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>69.52</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>95.79</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>79.6</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>69.52</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>92.59</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>145.65</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>115.11</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>92.59</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>145.65</v>
@@ -24700,7 +25320,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>145.65</v>
@@ -24714,7 +25334,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>145.65</v>
@@ -24728,7 +25348,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>145.65</v>
@@ -24742,7 +25362,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>145.65</v>
@@ -24756,7 +25376,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>145.65</v>
@@ -24770,7 +25390,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>145.65</v>
@@ -24782,70 +25402,70 @@
         <v>92.59</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>115.11</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>92.59</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>132.4</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>132.4</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>132.4</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>213.4</v>
@@ -24859,7 +25479,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>213.4</v>
@@ -24873,7 +25493,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>213.4</v>
@@ -24887,7 +25507,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>213.4</v>
@@ -24901,7 +25521,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>213.4</v>
@@ -24915,7 +25535,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>213.4</v>
@@ -24924,6 +25544,62 @@
         <v>165.4</v>
       </c>
       <c r="D103" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="D107" s="5" t="n">
         <v>132.4</v>
       </c>
     </row>
@@ -24944,7 +25620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -25100,42 +25776,42 @@
         <v>93.73</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>93.73</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>73.49</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>106.3</v>
@@ -25149,7 +25825,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>106.3</v>
@@ -25163,7 +25839,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>106.3</v>
@@ -25177,7 +25853,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>106.3</v>
@@ -25191,7 +25867,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>106.3</v>
@@ -25205,7 +25881,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>106.3</v>
@@ -25219,7 +25895,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>106.3</v>
@@ -25233,7 +25909,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>106.3</v>
@@ -25245,56 +25921,56 @@
         <v>73.49</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>73.49</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>73.49</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>109.23</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>167.04</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>128.08</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>109.23</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>167.04</v>
@@ -25308,7 +25984,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>167.04</v>
@@ -25322,7 +25998,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>167.04</v>
@@ -25336,7 +26012,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>167.04</v>
       </c>
       <c r="C70" s="5" t="n">
         <v>128.08</v>
@@ -25347,7 +26026,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>167.04</v>
@@ -25361,10 +26040,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>167.04</v>
+        <v>46315</v>
       </c>
       <c r="C72" s="5" t="n">
         <v>128.08</v>
@@ -25375,7 +26051,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>167.04</v>
@@ -25387,70 +26063,70 @@
         <v>109.23</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>167.04</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>128.08</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>109.23</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>148.98</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>148.98</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>233.26</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>177.26</v>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>148.98</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>233.26</v>
@@ -25464,7 +26140,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>233.26</v>
@@ -25478,7 +26154,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>233.26</v>
@@ -25492,7 +26168,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>233.26</v>
@@ -25506,7 +26182,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>233.26</v>
@@ -25520,7 +26196,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>233.26</v>
@@ -25529,6 +26205,62 @@
         <v>177.26</v>
       </c>
       <c r="D103" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>148.98</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="D107" s="5" t="n">
         <v>148.98</v>
       </c>
     </row>
@@ -25993,7 +26725,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -26119,36 +26851,36 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>120.23</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>39.68</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>120.23</v>
@@ -26159,10 +26891,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>39.68</v>
+        <v>120.23</v>
       </c>
       <c r="C37" s="5" t="n">
         <v>39.68</v>
@@ -26170,10 +26902,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>120.23</v>
+        <v>39.68</v>
       </c>
       <c r="C38" s="5" t="n">
         <v>39.68</v>
@@ -26181,7 +26913,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>120.23</v>
@@ -26192,7 +26924,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>120.23</v>
@@ -26203,7 +26935,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>120.23</v>
@@ -26214,7 +26946,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>120.23</v>
@@ -26225,7 +26957,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>120.23</v>
@@ -26234,47 +26966,47 @@
         <v>39.68</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>68.04</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>206.12</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>68.04</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>206.12</v>
@@ -26285,7 +27017,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>206.12</v>
@@ -26296,7 +27028,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>206.12</v>
@@ -26307,7 +27039,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>206.12</v>
@@ -26318,7 +27050,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>206.12</v>
@@ -26329,7 +27061,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>206.12</v>
@@ -26340,7 +27072,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>206.12</v>
@@ -26349,58 +27081,58 @@
         <v>68.04</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>206.12</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>68.04</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>94.53</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>94.53</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>286.39</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>94.53</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46313</v>
+        <v>46310</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>286.39</v>
@@ -26411,7 +27143,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>286.39</v>
@@ -26422,7 +27154,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>286.39</v>
@@ -26433,10 +27165,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>94.53</v>
+        <v>286.39</v>
       </c>
       <c r="C101" s="5" t="n">
         <v>94.53</v>
@@ -26444,7 +27176,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>286.39</v>
@@ -26455,12 +27187,56 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>286.39</v>
       </c>
       <c r="C103" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>94.53</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="C107" s="5" t="n">
         <v>94.53</v>
       </c>
     </row>
@@ -26481,7 +27257,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -26637,42 +27413,42 @@
         <v>126.12</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>167.64</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>126.12</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>114.96</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>100.08</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>114.96</v>
@@ -26686,7 +27462,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>114.96</v>
@@ -26700,7 +27476,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>114.96</v>
@@ -26714,7 +27490,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>114.96</v>
@@ -26728,7 +27504,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>114.96</v>
@@ -26742,7 +27518,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>114.96</v>
@@ -26756,7 +27532,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>114.96</v>
@@ -26770,7 +27546,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>114.96</v>
@@ -26782,56 +27558,56 @@
         <v>100.08</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>114.96</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>100.08</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>152.16</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>174.72</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>194.76</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>152.16</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>174.72</v>
@@ -26845,7 +27621,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>174.72</v>
@@ -26859,7 +27635,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>174.72</v>
@@ -26873,7 +27649,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>174.72</v>
@@ -26887,7 +27663,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>174.72</v>
@@ -26901,7 +27677,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>174.72</v>
@@ -26915,7 +27691,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>174.72</v>
@@ -26927,13 +27703,55 @@
         <v>152.16</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>152.16</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
         <v>31</v>
       </c>
     </row>
@@ -26954,7 +27772,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="14"/>
@@ -27110,89 +27928,89 @@
         <v>139.66</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>138.36</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>155.18</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>145.44</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>118.54</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>145.44</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>118.54</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B37" s="5" t="n">
         <v>130.89</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C37" s="5" t="n">
         <v>95.05</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D37" s="5" t="n">
         <v>106.69</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>216.18</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>176.7</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>216.18</v>
@@ -27206,7 +28024,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B60" s="5" t="n">
         <v>216.18</v>
@@ -27220,7 +28038,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B61" s="5" t="n">
         <v>216.18</v>
@@ -27234,7 +28052,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B62" s="5" t="n">
         <v>216.18</v>
@@ -27248,7 +28066,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>216.18</v>
@@ -27262,35 +28080,35 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>194.56</v>
+        <v>216.18</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>142.15</v>
+        <v>157.93</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>159.03</v>
+        <v>176.7</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>216.18</v>
+        <v>194.56</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>157.93</v>
+        <v>142.15</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>176.7</v>
+        <v>159.03</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>216.18</v>
@@ -27302,70 +28120,70 @@
         <v>176.7</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>194.56</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>142.15</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>159.03</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B88" s="5" t="n">
-        <v>275.68</v>
-      </c>
-      <c r="C88" s="5" t="n">
-        <v>202.39</v>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>225.85</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B89" s="5" t="n">
-        <v>306.32</v>
-      </c>
-      <c r="C89" s="5" t="n">
-        <v>224.88</v>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>250.95</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>306.32</v>
+        <v>275.68</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>224.88</v>
+        <v>202.39</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>250.95</v>
+        <v>225.85</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>306.32</v>
@@ -27379,7 +28197,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>306.32</v>
@@ -27393,7 +28211,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>306.32</v>
@@ -27407,7 +28225,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B94" s="5" t="n">
         <v>306.32</v>
@@ -27421,7 +28239,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>306.32</v>
@@ -27435,15 +28253,57 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>224.88</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>250.95</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
         <v>46318</v>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B98" s="5" t="n">
         <v>275.68</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C98" s="5" t="n">
         <v>202.39</v>
       </c>
-      <c r="D96" s="5" t="n">
+      <c r="D98" s="5" t="n">
+        <v>225.85</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>275.68</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>202.39</v>
+      </c>
+      <c r="D99" s="5" t="n">
         <v>225.85</v>
       </c>
     </row>

--- a/data/dashboard/Prehlad_cien_poistovne.xlsx
+++ b/data/dashboard/Prehlad_cien_poistovne.xlsx
@@ -820,11 +820,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="89059045"/>
-        <c:axId val="30463631"/>
+        <c:axId val="80083535"/>
+        <c:axId val="55997221"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="89059045"/>
+        <c:axId val="80083535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -890,7 +890,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30463631"/>
+        <c:crossAx val="55997221"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -898,7 +898,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30463631"/>
+        <c:axId val="55997221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -974,7 +974,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89059045"/>
+        <c:crossAx val="80083535"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1510,11 +1510,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="94931664"/>
-        <c:axId val="71971339"/>
+        <c:axId val="78162765"/>
+        <c:axId val="64423522"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="94931664"/>
+        <c:axId val="78162765"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1580,7 +1580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71971339"/>
+        <c:crossAx val="64423522"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1588,7 +1588,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71971339"/>
+        <c:axId val="64423522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1664,7 +1664,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94931664"/>
+        <c:crossAx val="78162765"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2200,11 +2200,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98469858"/>
-        <c:axId val="85508832"/>
+        <c:axId val="53349309"/>
+        <c:axId val="98477447"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98469858"/>
+        <c:axId val="53349309"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2270,7 +2270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85508832"/>
+        <c:crossAx val="98477447"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2278,7 +2278,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85508832"/>
+        <c:axId val="98477447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2354,7 +2354,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98469858"/>
+        <c:crossAx val="53349309"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2890,11 +2890,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="95678424"/>
-        <c:axId val="90300304"/>
+        <c:axId val="25644534"/>
+        <c:axId val="63196812"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="95678424"/>
+        <c:axId val="25644534"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2960,7 +2960,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90300304"/>
+        <c:crossAx val="63196812"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2968,7 +2968,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90300304"/>
+        <c:axId val="63196812"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3044,7 +3044,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95678424"/>
+        <c:crossAx val="25644534"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3580,11 +3580,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54120680"/>
-        <c:axId val="78548303"/>
+        <c:axId val="8507041"/>
+        <c:axId val="17636685"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54120680"/>
+        <c:axId val="8507041"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3650,7 +3650,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78548303"/>
+        <c:crossAx val="17636685"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3658,7 +3658,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78548303"/>
+        <c:axId val="17636685"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3734,7 +3734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54120680"/>
+        <c:crossAx val="8507041"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4270,11 +4270,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40078922"/>
-        <c:axId val="11375987"/>
+        <c:axId val="80919890"/>
+        <c:axId val="78361203"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40078922"/>
+        <c:axId val="80919890"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4340,7 +4340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11375987"/>
+        <c:crossAx val="78361203"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4348,7 +4348,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11375987"/>
+        <c:axId val="78361203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4424,7 +4424,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40078922"/>
+        <c:crossAx val="80919890"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4960,11 +4960,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="67042699"/>
-        <c:axId val="16805622"/>
+        <c:axId val="61131351"/>
+        <c:axId val="90605209"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67042699"/>
+        <c:axId val="61131351"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5030,7 +5030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16805622"/>
+        <c:crossAx val="90605209"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5038,7 +5038,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16805622"/>
+        <c:axId val="90605209"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5114,7 +5114,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67042699"/>
+        <c:crossAx val="61131351"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5650,11 +5650,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="67483289"/>
-        <c:axId val="12598181"/>
+        <c:axId val="34144595"/>
+        <c:axId val="90919651"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67483289"/>
+        <c:axId val="34144595"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5720,7 +5720,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12598181"/>
+        <c:crossAx val="90919651"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5728,7 +5728,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12598181"/>
+        <c:axId val="90919651"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5804,7 +5804,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67483289"/>
+        <c:crossAx val="34144595"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6340,11 +6340,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="41305908"/>
-        <c:axId val="51227381"/>
+        <c:axId val="48996824"/>
+        <c:axId val="12920549"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="41305908"/>
+        <c:axId val="48996824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6410,7 +6410,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51227381"/>
+        <c:crossAx val="12920549"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6418,7 +6418,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51227381"/>
+        <c:axId val="12920549"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6494,7 +6494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41305908"/>
+        <c:crossAx val="48996824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7030,11 +7030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24754448"/>
-        <c:axId val="13876753"/>
+        <c:axId val="4483979"/>
+        <c:axId val="24641874"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24754448"/>
+        <c:axId val="4483979"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7100,7 +7100,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13876753"/>
+        <c:crossAx val="24641874"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7108,7 +7108,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13876753"/>
+        <c:axId val="24641874"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7184,7 +7184,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24754448"/>
+        <c:crossAx val="4483979"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7717,11 +7717,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="86259521"/>
-        <c:axId val="69117673"/>
+        <c:axId val="53101554"/>
+        <c:axId val="45514622"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="86259521"/>
+        <c:axId val="53101554"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7787,7 +7787,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69117673"/>
+        <c:crossAx val="45514622"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7795,7 +7795,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69117673"/>
+        <c:axId val="45514622"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7871,7 +7871,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86259521"/>
+        <c:crossAx val="53101554"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8389,11 +8389,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="34811767"/>
-        <c:axId val="93579315"/>
+        <c:axId val="15303577"/>
+        <c:axId val="33241002"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="34811767"/>
+        <c:axId val="15303577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8459,7 +8459,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93579315"/>
+        <c:crossAx val="33241002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8467,7 +8467,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93579315"/>
+        <c:axId val="33241002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8543,7 +8543,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34811767"/>
+        <c:crossAx val="15303577"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9079,11 +9079,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52437206"/>
-        <c:axId val="77162922"/>
+        <c:axId val="11585780"/>
+        <c:axId val="66576832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52437206"/>
+        <c:axId val="11585780"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9149,7 +9149,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77162922"/>
+        <c:crossAx val="66576832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9157,7 +9157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77162922"/>
+        <c:axId val="66576832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9233,7 +9233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52437206"/>
+        <c:crossAx val="11585780"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9384,9 +9384,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$12</c:f>
+              <c:f>UNIQA!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -9410,16 +9410,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$5:$B$12</c:f>
+              <c:f>UNIQA!$B$5:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>207.75</c:v>
                 </c:pt>
@@ -9442,6 +9445,9 @@
                   <c:v>207.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>207.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>207.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -9504,9 +9510,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$5:$A$12</c:f>
+              <c:f>UNIQA!$A$5:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -9530,16 +9536,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$5:$C$12</c:f>
+              <c:f>UNIQA!$C$5:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>174.58</c:v>
                 </c:pt>
@@ -9562,6 +9571,9 @@
                   <c:v>174.58</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>174.58</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>174.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -9577,11 +9589,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="6307453"/>
-        <c:axId val="85687093"/>
+        <c:axId val="25844280"/>
+        <c:axId val="28732619"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6307453"/>
+        <c:axId val="25844280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9647,7 +9659,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85687093"/>
+        <c:crossAx val="28732619"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9655,7 +9667,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85687093"/>
+        <c:axId val="28732619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9731,7 +9743,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6307453"/>
+        <c:crossAx val="25844280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9832,7 +9844,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B33</c:f>
+              <c:f>UNIQA!B34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9882,9 +9894,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$34:$A$41</c:f>
+              <c:f>UNIQA!$A$35:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -9908,16 +9920,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$34:$B$41</c:f>
+              <c:f>UNIQA!$B$35:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>164.09</c:v>
                 </c:pt>
@@ -9940,6 +9955,9 @@
                   <c:v>164.09</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>164.09</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>164.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -9952,7 +9970,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C33</c:f>
+              <c:f>UNIQA!C34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10002,9 +10020,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$34:$A$41</c:f>
+              <c:f>UNIQA!$A$35:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -10028,16 +10046,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$34:$C$41</c:f>
+              <c:f>UNIQA!$C$35:$C$43</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>139.42</c:v>
                 </c:pt>
@@ -10060,6 +10081,9 @@
                   <c:v>139.42</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>139.42</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>139.42</c:v>
                 </c:pt>
               </c:numCache>
@@ -10075,11 +10099,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="25219277"/>
-        <c:axId val="88466783"/>
+        <c:axId val="91752115"/>
+        <c:axId val="21334950"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="25219277"/>
+        <c:axId val="91752115"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10145,7 +10169,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88466783"/>
+        <c:crossAx val="21334950"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10153,7 +10177,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88466783"/>
+        <c:axId val="21334950"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10229,7 +10253,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25219277"/>
+        <c:crossAx val="91752115"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10330,7 +10354,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B62</c:f>
+              <c:f>UNIQA!B64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10380,9 +10404,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$63:$A$70</c:f>
+              <c:f>UNIQA!$A$65:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -10406,16 +10430,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$63:$B$70</c:f>
+              <c:f>UNIQA!$B$65:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>234.99</c:v>
                 </c:pt>
@@ -10438,6 +10465,9 @@
                   <c:v>234.99</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>234.99</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>234.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -10450,7 +10480,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C62</c:f>
+              <c:f>UNIQA!C64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10500,9 +10530,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$63:$A$70</c:f>
+              <c:f>UNIQA!$A$65:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -10526,16 +10556,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$63:$C$70</c:f>
+              <c:f>UNIQA!$C$65:$C$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>183.95</c:v>
                 </c:pt>
@@ -10558,6 +10591,9 @@
                   <c:v>183.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>183.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>183.95</c:v>
                 </c:pt>
               </c:numCache>
@@ -10573,11 +10609,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="84133411"/>
-        <c:axId val="26468531"/>
+        <c:axId val="78687728"/>
+        <c:axId val="67677145"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84133411"/>
+        <c:axId val="78687728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10643,7 +10679,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26468531"/>
+        <c:crossAx val="67677145"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10651,7 +10687,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26468531"/>
+        <c:axId val="67677145"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10727,7 +10763,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84133411"/>
+        <c:crossAx val="78687728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10828,7 +10864,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!B91</c:f>
+              <c:f>UNIQA!B94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10878,9 +10914,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$92:$A$99</c:f>
+              <c:f>UNIQA!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -10904,16 +10940,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$B$92:$B$99</c:f>
+              <c:f>UNIQA!$B$95:$B$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>303.1</c:v>
                 </c:pt>
@@ -10936,6 +10975,9 @@
                   <c:v>303.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>303.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>303.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -10948,7 +10990,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>UNIQA!C91</c:f>
+              <c:f>UNIQA!C94</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -10998,9 +11040,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>UNIQA!$A$92:$A$99</c:f>
+              <c:f>UNIQA!$A$95:$A$103</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>16.10.2026</c:v>
                 </c:pt>
@@ -11024,16 +11066,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23.10.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.10.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>UNIQA!$C$92:$C$99</c:f>
+              <c:f>UNIQA!$C$95:$C$103</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00" €"</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>237.81</c:v>
                 </c:pt>
@@ -11056,6 +11101,9 @@
                   <c:v>237.81</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>237.81</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>237.81</c:v>
                 </c:pt>
               </c:numCache>
@@ -11071,11 +11119,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="19282038"/>
-        <c:axId val="9881158"/>
+        <c:axId val="23779346"/>
+        <c:axId val="85448483"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="19282038"/>
+        <c:axId val="23779346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11141,7 +11189,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9881158"/>
+        <c:crossAx val="85448483"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11149,7 +11197,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9881158"/>
+        <c:axId val="85448483"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11225,7 +11273,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19282038"/>
+        <c:crossAx val="23779346"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11617,11 +11665,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64895018"/>
-        <c:axId val="24901495"/>
+        <c:axId val="77241623"/>
+        <c:axId val="7546485"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="64895018"/>
+        <c:axId val="77241623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11687,7 +11735,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24901495"/>
+        <c:crossAx val="7546485"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11695,7 +11743,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24901495"/>
+        <c:axId val="7546485"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11771,7 +11819,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64895018"/>
+        <c:crossAx val="77241623"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12163,11 +12211,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="55899008"/>
-        <c:axId val="39405512"/>
+        <c:axId val="69097349"/>
+        <c:axId val="59215811"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="55899008"/>
+        <c:axId val="69097349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12233,7 +12281,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39405512"/>
+        <c:crossAx val="59215811"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12241,7 +12289,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39405512"/>
+        <c:axId val="59215811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12317,7 +12365,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55899008"/>
+        <c:crossAx val="69097349"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12709,11 +12757,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54930311"/>
-        <c:axId val="82477828"/>
+        <c:axId val="88214908"/>
+        <c:axId val="52278063"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54930311"/>
+        <c:axId val="88214908"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12779,7 +12827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82477828"/>
+        <c:crossAx val="52278063"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12787,7 +12835,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82477828"/>
+        <c:axId val="52278063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12863,7 +12911,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54930311"/>
+        <c:crossAx val="88214908"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13255,11 +13303,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74324788"/>
-        <c:axId val="27641651"/>
+        <c:axId val="50408189"/>
+        <c:axId val="10754435"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74324788"/>
+        <c:axId val="50408189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13325,7 +13373,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27641651"/>
+        <c:crossAx val="10754435"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13333,7 +13381,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27641651"/>
+        <c:axId val="10754435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13409,7 +13457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74324788"/>
+        <c:crossAx val="50408189"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13945,11 +13993,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82503217"/>
-        <c:axId val="66652472"/>
+        <c:axId val="79053862"/>
+        <c:axId val="9831268"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82503217"/>
+        <c:axId val="79053862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14015,7 +14063,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66652472"/>
+        <c:crossAx val="9831268"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14023,7 +14071,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66652472"/>
+        <c:axId val="9831268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14099,7 +14147,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82503217"/>
+        <c:crossAx val="79053862"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14617,11 +14665,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="5266715"/>
-        <c:axId val="91764327"/>
+        <c:axId val="67570434"/>
+        <c:axId val="50640218"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="5266715"/>
+        <c:axId val="67570434"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14687,7 +14735,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91764327"/>
+        <c:crossAx val="50640218"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14695,7 +14743,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91764327"/>
+        <c:axId val="50640218"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14771,7 +14819,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5266715"/>
+        <c:crossAx val="67570434"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15307,11 +15355,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83117937"/>
-        <c:axId val="76951399"/>
+        <c:axId val="41109609"/>
+        <c:axId val="94638353"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83117937"/>
+        <c:axId val="41109609"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15377,7 +15425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76951399"/>
+        <c:crossAx val="94638353"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15385,7 +15433,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76951399"/>
+        <c:axId val="94638353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15461,7 +15509,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83117937"/>
+        <c:crossAx val="41109609"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15997,11 +16045,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77035722"/>
-        <c:axId val="2231312"/>
+        <c:axId val="72922305"/>
+        <c:axId val="66117435"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77035722"/>
+        <c:axId val="72922305"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16067,7 +16115,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2231312"/>
+        <c:crossAx val="66117435"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16075,7 +16123,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2231312"/>
+        <c:axId val="66117435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16151,7 +16199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77035722"/>
+        <c:crossAx val="72922305"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16687,11 +16735,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73638119"/>
-        <c:axId val="85233595"/>
+        <c:axId val="30604038"/>
+        <c:axId val="34160543"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73638119"/>
+        <c:axId val="30604038"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16757,7 +16805,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85233595"/>
+        <c:crossAx val="34160543"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16765,7 +16813,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85233595"/>
+        <c:axId val="34160543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16841,7 +16889,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73638119"/>
+        <c:crossAx val="30604038"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17197,11 +17245,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82508853"/>
-        <c:axId val="67899373"/>
+        <c:axId val="98238869"/>
+        <c:axId val="51487840"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82508853"/>
+        <c:axId val="98238869"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17267,7 +17315,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67899373"/>
+        <c:crossAx val="51487840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17275,7 +17323,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67899373"/>
+        <c:axId val="51487840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17351,7 +17399,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82508853"/>
+        <c:crossAx val="98238869"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17887,11 +17935,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47014808"/>
-        <c:axId val="39402970"/>
+        <c:axId val="22889364"/>
+        <c:axId val="34247832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47014808"/>
+        <c:axId val="22889364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17957,7 +18005,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39402970"/>
+        <c:crossAx val="34247832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -17965,7 +18013,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39402970"/>
+        <c:axId val="34247832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18041,7 +18089,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47014808"/>
+        <c:crossAx val="22889364"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18577,11 +18625,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18007485"/>
-        <c:axId val="99135629"/>
+        <c:axId val="22230364"/>
+        <c:axId val="32309020"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18007485"/>
+        <c:axId val="22230364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18647,7 +18695,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99135629"/>
+        <c:crossAx val="32309020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -18655,7 +18703,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99135629"/>
+        <c:axId val="32309020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18731,7 +18779,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18007485"/>
+        <c:crossAx val="22230364"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19249,11 +19297,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90040256"/>
-        <c:axId val="13772195"/>
+        <c:axId val="94629736"/>
+        <c:axId val="56057094"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90040256"/>
+        <c:axId val="94629736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19319,7 +19367,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13772195"/>
+        <c:crossAx val="56057094"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19327,7 +19375,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13772195"/>
+        <c:axId val="56057094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19403,7 +19451,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90040256"/>
+        <c:crossAx val="94629736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19903,11 +19951,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39537604"/>
-        <c:axId val="14717407"/>
+        <c:axId val="52259918"/>
+        <c:axId val="43925133"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39537604"/>
+        <c:axId val="52259918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19973,7 +20021,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14717407"/>
+        <c:crossAx val="43925133"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -19981,7 +20029,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14717407"/>
+        <c:axId val="43925133"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20057,7 +20105,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39537604"/>
+        <c:crossAx val="52259918"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20593,11 +20641,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31958989"/>
-        <c:axId val="35590434"/>
+        <c:axId val="32730296"/>
+        <c:axId val="41460664"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31958989"/>
+        <c:axId val="32730296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20663,7 +20711,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35590434"/>
+        <c:crossAx val="41460664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -20671,7 +20719,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35590434"/>
+        <c:axId val="41460664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20747,7 +20795,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31958989"/>
+        <c:crossAx val="32730296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21265,11 +21313,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="46888191"/>
-        <c:axId val="64345385"/>
+        <c:axId val="14256844"/>
+        <c:axId val="20171939"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="46888191"/>
+        <c:axId val="14256844"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21335,7 +21383,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64345385"/>
+        <c:crossAx val="20171939"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -21343,7 +21391,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64345385"/>
+        <c:axId val="20171939"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -21419,7 +21467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46888191"/>
+        <c:crossAx val="14256844"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -21937,11 +21985,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29805967"/>
-        <c:axId val="46460798"/>
+        <c:axId val="18450743"/>
+        <c:axId val="56858450"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29805967"/>
+        <c:axId val="18450743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22007,7 +22055,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46460798"/>
+        <c:crossAx val="56858450"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22015,7 +22063,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46460798"/>
+        <c:axId val="56858450"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22091,7 +22139,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29805967"/>
+        <c:crossAx val="18450743"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -22627,11 +22675,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="31216546"/>
-        <c:axId val="31750818"/>
+        <c:axId val="56648498"/>
+        <c:axId val="90802044"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31216546"/>
+        <c:axId val="56648498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22697,7 +22745,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31750818"/>
+        <c:crossAx val="90802044"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -22705,7 +22753,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31750818"/>
+        <c:axId val="90802044"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -22781,7 +22829,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31216546"/>
+        <c:crossAx val="56648498"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -23494,14 +23542,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -23509,7 +23557,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="6095880"/>
+        <a:off x="3571920" y="6286680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -23524,14 +23572,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -23539,7 +23587,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="11620440"/>
+        <a:off x="3571920" y="12001680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -23554,13 +23602,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -23569,7 +23617,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3571920" y="17145000"/>
+        <a:off x="3571920" y="17716680"/>
         <a:ext cx="7199640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -27873,7 +27921,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
@@ -27988,36 +28036,36 @@
         <v>174.58</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>207.75</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>174.58</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>164.09</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>139.42</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>164.09</v>
@@ -28028,7 +28076,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>164.09</v>
@@ -28039,7 +28087,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>164.09</v>
@@ -28050,7 +28098,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>164.09</v>
@@ -28061,7 +28109,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>164.09</v>
@@ -28072,7 +28120,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>164.09</v>
@@ -28083,7 +28131,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>164.09</v>
@@ -28092,47 +28140,47 @@
         <v>139.42</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>139.42</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>139.42</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B64" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>234.99</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>183.95</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>234.99</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>183.95</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>234.99</v>
@@ -28143,7 +28191,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>234.99</v>
@@ -28154,7 +28202,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
-        <v>46315</v>
+        <v>46313</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>234.99</v>
@@ -28165,7 +28213,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>234.99</v>
@@ -28176,7 +28224,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>234.99</v>
@@ -28187,7 +28235,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>234.99</v>
@@ -28196,58 +28244,58 @@
         <v>183.95</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>234.99</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>183.95</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>303.1</v>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>237.81</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>303.1</v>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>237.81</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>303.1</v>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>237.81</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>303.1</v>
@@ -28258,7 +28306,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>303.1</v>
@@ -28269,7 +28317,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
-        <v>46316</v>
+        <v>46313</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>303.1</v>
@@ -28280,7 +28328,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>303.1</v>
@@ -28291,12 +28339,56 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>46318</v>
+        <v>46315</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>303.1</v>
       </c>
       <c r="C99" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>237.81</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="C103" s="5" t="n">
         <v>237.81</v>
       </c>
     </row>
